--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14020"/>
+    <workbookView windowHeight="18640"/>
   </bookViews>
   <sheets>
     <sheet name="premier_league_players_merged_f" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1000">
   <si>
     <t>player_id</t>
   </si>
@@ -1730,6 +1730,9 @@
     <t>Nick Pope</t>
   </si>
   <si>
+    <t>Newcastle United;Burnley</t>
+  </si>
+  <si>
     <t>Noel Whelan</t>
   </si>
   <si>
@@ -1859,6 +1862,9 @@
     <t>Leandro Trossard</t>
   </si>
   <si>
+    <t>Arsenal;Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
     <t>Michael Gray</t>
   </si>
   <si>
@@ -1913,6 +1919,9 @@
     <t>Harvey Barnes</t>
   </si>
   <si>
+    <t>Newcastle United;Leicester City</t>
+  </si>
+  <si>
     <t>Matthew Lowton</t>
   </si>
   <si>
@@ -1998,9 +2007,6 @@
   </si>
   <si>
     <t>Ayoze Pérez</t>
-  </si>
-  <si>
-    <t>Newcastle United;Leicester City</t>
   </si>
   <si>
     <t>Tomás Soucek</t>
@@ -7748,7 +7754,7 @@
         <v>566</v>
       </c>
       <c r="C325" t="s">
-        <v>304</v>
+        <v>567</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -7756,10 +7762,10 @@
         <v>245</v>
       </c>
       <c r="B326" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C326" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -7767,10 +7773,10 @@
         <v>1335</v>
       </c>
       <c r="B327" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C327" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -7778,7 +7784,7 @@
         <v>4123</v>
       </c>
       <c r="B328" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C328" t="s">
         <v>145</v>
@@ -7789,7 +7795,7 @@
         <v>523</v>
       </c>
       <c r="B329" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C329" t="s">
         <v>202</v>
@@ -7800,10 +7806,10 @@
         <v>3448</v>
       </c>
       <c r="B330" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C330" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -7811,7 +7817,7 @@
         <v>2289</v>
       </c>
       <c r="B331" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C331" t="s">
         <v>216</v>
@@ -7822,10 +7828,10 @@
         <v>2991</v>
       </c>
       <c r="B332" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C332" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -7833,7 +7839,7 @@
         <v>3404</v>
       </c>
       <c r="B333" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C333" t="s">
         <v>20</v>
@@ -7844,7 +7850,7 @@
         <v>1497</v>
       </c>
       <c r="B334" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C334" t="s">
         <v>282</v>
@@ -7855,7 +7861,7 @@
         <v>4403</v>
       </c>
       <c r="B335" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C335" t="s">
         <v>315</v>
@@ -7866,7 +7872,7 @@
         <v>22542</v>
       </c>
       <c r="B336" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C336" t="s">
         <v>325</v>
@@ -7877,10 +7883,10 @@
         <v>2845</v>
       </c>
       <c r="B337" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C337" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -7888,7 +7894,7 @@
         <v>3807</v>
       </c>
       <c r="B338" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C338" t="s">
         <v>378</v>
@@ -7899,7 +7905,7 @@
         <v>19680</v>
       </c>
       <c r="B339" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C339" t="s">
         <v>177</v>
@@ -7910,10 +7916,10 @@
         <v>8245</v>
       </c>
       <c r="B340" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C340" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -7921,7 +7927,7 @@
         <v>79</v>
       </c>
       <c r="B341" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C341" t="s">
         <v>308</v>
@@ -7932,7 +7938,7 @@
         <v>1505</v>
       </c>
       <c r="B342" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C342" t="s">
         <v>534</v>
@@ -7943,10 +7949,10 @@
         <v>1909</v>
       </c>
       <c r="B343" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C343" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -7954,10 +7960,10 @@
         <v>3982</v>
       </c>
       <c r="B344" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C344" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -7965,7 +7971,7 @@
         <v>4286</v>
       </c>
       <c r="B345" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C345" t="s">
         <v>202</v>
@@ -7976,10 +7982,10 @@
         <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C346" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -7987,10 +7993,10 @@
         <v>5865</v>
       </c>
       <c r="B347" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C347" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -7998,7 +8004,7 @@
         <v>3394</v>
       </c>
       <c r="B348" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C348" t="s">
         <v>302</v>
@@ -8009,10 +8015,10 @@
         <v>329</v>
       </c>
       <c r="B349" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C349" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -8020,10 +8026,10 @@
         <v>1045</v>
       </c>
       <c r="B350" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C350" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -8031,10 +8037,10 @@
         <v>755</v>
       </c>
       <c r="B351" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C351" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -8042,7 +8048,7 @@
         <v>2522</v>
       </c>
       <c r="B352" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C352" t="s">
         <v>8</v>
@@ -8053,7 +8059,7 @@
         <v>2072</v>
       </c>
       <c r="B353" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C353" t="s">
         <v>444</v>
@@ -8064,7 +8070,7 @@
         <v>1558</v>
       </c>
       <c r="B354" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C354" t="s">
         <v>129</v>
@@ -8075,7 +8081,7 @@
         <v>1217</v>
       </c>
       <c r="B355" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C355" t="s">
         <v>8</v>
@@ -8086,10 +8092,10 @@
         <v>20486</v>
       </c>
       <c r="B356" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C356" t="s">
-        <v>256</v>
+        <v>611</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -8097,7 +8103,7 @@
         <v>1253</v>
       </c>
       <c r="B357" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C357" t="s">
         <v>479</v>
@@ -8108,10 +8114,10 @@
         <v>4252</v>
       </c>
       <c r="B358" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C358" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -8119,10 +8125,10 @@
         <v>293</v>
       </c>
       <c r="B359" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C359" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -8130,10 +8136,10 @@
         <v>2980</v>
       </c>
       <c r="B360" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C360" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -8141,7 +8147,7 @@
         <v>2024</v>
       </c>
       <c r="B361" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C361" t="s">
         <v>308</v>
@@ -8152,10 +8158,10 @@
         <v>2047</v>
       </c>
       <c r="B362" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C362" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -8163,7 +8169,7 @@
         <v>8868</v>
       </c>
       <c r="B363" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C363" t="s">
         <v>79</v>
@@ -8174,7 +8180,7 @@
         <v>2012</v>
       </c>
       <c r="B364" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C364" t="s">
         <v>232</v>
@@ -8185,7 +8191,7 @@
         <v>4666</v>
       </c>
       <c r="B365" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C365" t="s">
         <v>145</v>
@@ -8196,10 +8202,10 @@
         <v>448</v>
       </c>
       <c r="B366" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C366" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -8207,10 +8213,10 @@
         <v>1495</v>
       </c>
       <c r="B367" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C367" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -8218,10 +8224,10 @@
         <v>14716</v>
       </c>
       <c r="B368" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C368" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -8229,7 +8235,7 @@
         <v>4487</v>
       </c>
       <c r="B369" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C369" t="s">
         <v>369</v>
@@ -8240,10 +8246,10 @@
         <v>128</v>
       </c>
       <c r="B370" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C370" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -8251,10 +8257,10 @@
         <v>8707</v>
       </c>
       <c r="B371" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C371" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -8262,7 +8268,7 @@
         <v>4148</v>
       </c>
       <c r="B372" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C372" t="s">
         <v>277</v>
@@ -8273,7 +8279,7 @@
         <v>14164</v>
       </c>
       <c r="B373" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C373" t="s">
         <v>79</v>
@@ -8284,10 +8290,10 @@
         <v>1096</v>
       </c>
       <c r="B374" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C374" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -8295,7 +8301,7 @@
         <v>1151</v>
       </c>
       <c r="B375" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C375" t="s">
         <v>167</v>
@@ -8306,10 +8312,10 @@
         <v>3247</v>
       </c>
       <c r="B376" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C376" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -8317,10 +8323,10 @@
         <v>1205</v>
       </c>
       <c r="B377" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C377" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -8328,10 +8334,10 @@
         <v>603</v>
       </c>
       <c r="B378" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C378" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -8339,7 +8345,7 @@
         <v>11071</v>
       </c>
       <c r="B379" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C379" t="s">
         <v>302</v>
@@ -8350,7 +8356,7 @@
         <v>51423</v>
       </c>
       <c r="B380" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C380" t="s">
         <v>232</v>
@@ -8361,7 +8367,7 @@
         <v>2239</v>
       </c>
       <c r="B381" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C381" t="s">
         <v>129</v>
@@ -8372,10 +8378,10 @@
         <v>13492</v>
       </c>
       <c r="B382" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C382" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -8383,7 +8389,7 @@
         <v>13274</v>
       </c>
       <c r="B383" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C383" t="s">
         <v>232</v>
@@ -8394,7 +8400,7 @@
         <v>2705</v>
       </c>
       <c r="B384" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C384" t="s">
         <v>129</v>
@@ -8405,10 +8411,10 @@
         <v>1740</v>
       </c>
       <c r="B385" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C385" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -8416,7 +8422,7 @@
         <v>4821</v>
       </c>
       <c r="B386" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C386" t="s">
         <v>340</v>
@@ -8427,7 +8433,7 @@
         <v>23396</v>
       </c>
       <c r="B387" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C387" t="s">
         <v>8</v>
@@ -8438,7 +8444,7 @@
         <v>401</v>
       </c>
       <c r="B388" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C388" t="s">
         <v>181</v>
@@ -8449,10 +8455,10 @@
         <v>10487</v>
       </c>
       <c r="B389" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C389" t="s">
-        <v>657</v>
+        <v>630</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -8460,7 +8466,7 @@
         <v>25183</v>
       </c>
       <c r="B390" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C390" t="s">
         <v>79</v>
@@ -8471,7 +8477,7 @@
         <v>174</v>
       </c>
       <c r="B391" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C391" t="s">
         <v>129</v>
@@ -8482,7 +8488,7 @@
         <v>4245</v>
       </c>
       <c r="B392" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C392" t="s">
         <v>232</v>
@@ -8493,10 +8499,10 @@
         <v>388</v>
       </c>
       <c r="B393" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C393" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -8504,7 +8510,7 @@
         <v>49481</v>
       </c>
       <c r="B394" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C394" t="s">
         <v>256</v>
@@ -8515,7 +8521,7 @@
         <v>3905</v>
       </c>
       <c r="B395" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C395" t="s">
         <v>304</v>
@@ -8526,10 +8532,10 @@
         <v>3169</v>
       </c>
       <c r="B396" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C396" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -8537,7 +8543,7 @@
         <v>8456</v>
       </c>
       <c r="B397" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C397" t="s">
         <v>145</v>
@@ -8548,10 +8554,10 @@
         <v>1080</v>
       </c>
       <c r="B398" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C398" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -8559,10 +8565,10 @@
         <v>3029</v>
       </c>
       <c r="B399" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C399" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -8570,10 +8576,10 @@
         <v>2669</v>
       </c>
       <c r="B400" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C400" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -8581,7 +8587,7 @@
         <v>5101</v>
       </c>
       <c r="B401" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C401" t="s">
         <v>277</v>
@@ -8592,10 +8598,10 @@
         <v>272</v>
       </c>
       <c r="B402" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C402" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -8603,10 +8609,10 @@
         <v>3983</v>
       </c>
       <c r="B403" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C403" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -8614,10 +8620,10 @@
         <v>3546</v>
       </c>
       <c r="B404" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C404" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -8625,7 +8631,7 @@
         <v>20479</v>
       </c>
       <c r="B405" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C405" t="s">
         <v>181</v>
@@ -8636,7 +8642,7 @@
         <v>2385</v>
       </c>
       <c r="B406" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C406" t="s">
         <v>378</v>
@@ -8647,10 +8653,10 @@
         <v>193</v>
       </c>
       <c r="B407" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C407" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -8658,7 +8664,7 @@
         <v>14805</v>
       </c>
       <c r="B408" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C408" t="s">
         <v>277</v>
@@ -8669,10 +8675,10 @@
         <v>179</v>
       </c>
       <c r="B409" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C409" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -8680,7 +8686,7 @@
         <v>3613</v>
       </c>
       <c r="B410" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C410" t="s">
         <v>262</v>
@@ -8691,10 +8697,10 @@
         <v>929</v>
       </c>
       <c r="B411" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C411" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -8702,10 +8708,10 @@
         <v>3154</v>
       </c>
       <c r="B412" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C412" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -8713,10 +8719,10 @@
         <v>2393</v>
       </c>
       <c r="B413" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C413" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -8724,7 +8730,7 @@
         <v>3121</v>
       </c>
       <c r="B414" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C414" t="s">
         <v>302</v>
@@ -8735,7 +8741,7 @@
         <v>75</v>
       </c>
       <c r="B415" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C415" t="s">
         <v>308</v>
@@ -8746,10 +8752,10 @@
         <v>7114</v>
       </c>
       <c r="B416" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C416" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -8757,10 +8763,10 @@
         <v>167</v>
       </c>
       <c r="B417" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C417" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -8768,10 +8774,10 @@
         <v>768</v>
       </c>
       <c r="B418" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C418" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -8779,10 +8785,10 @@
         <v>1382</v>
       </c>
       <c r="B419" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C419" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -8790,10 +8796,10 @@
         <v>954</v>
       </c>
       <c r="B420" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C420" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -8801,10 +8807,10 @@
         <v>112</v>
       </c>
       <c r="B421" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C421" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -8812,7 +8818,7 @@
         <v>8658</v>
       </c>
       <c r="B422" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C422" t="s">
         <v>232</v>
@@ -8823,7 +8829,7 @@
         <v>3562</v>
       </c>
       <c r="B423" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C423" t="s">
         <v>361</v>
@@ -8834,10 +8840,10 @@
         <v>3524</v>
       </c>
       <c r="B424" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C424" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -8845,10 +8851,10 @@
         <v>757</v>
       </c>
       <c r="B425" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C425" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -8856,7 +8862,7 @@
         <v>2550</v>
       </c>
       <c r="B426" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C426" t="s">
         <v>534</v>
@@ -8867,7 +8873,7 @@
         <v>3388</v>
       </c>
       <c r="B427" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C427" t="s">
         <v>153</v>
@@ -8878,10 +8884,10 @@
         <v>3362</v>
       </c>
       <c r="B428" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C428" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -8889,7 +8895,7 @@
         <v>29</v>
       </c>
       <c r="B429" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C429" t="s">
         <v>282</v>
@@ -8900,10 +8906,10 @@
         <v>3157</v>
       </c>
       <c r="B430" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C430" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -8911,7 +8917,7 @@
         <v>4100</v>
       </c>
       <c r="B431" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C431" t="s">
         <v>56</v>
@@ -8922,10 +8928,10 @@
         <v>2279</v>
       </c>
       <c r="B432" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C432" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -8933,10 +8939,10 @@
         <v>3420</v>
       </c>
       <c r="B433" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C433" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -8944,10 +8950,10 @@
         <v>1017</v>
       </c>
       <c r="B434" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C434" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -8955,10 +8961,10 @@
         <v>9662</v>
       </c>
       <c r="B435" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C435" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -8966,10 +8972,10 @@
         <v>509</v>
       </c>
       <c r="B436" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C436" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -8977,7 +8983,7 @@
         <v>3680</v>
       </c>
       <c r="B437" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C437" t="s">
         <v>304</v>
@@ -8988,7 +8994,7 @@
         <v>1866</v>
       </c>
       <c r="B438" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C438" t="s">
         <v>167</v>
@@ -8999,7 +9005,7 @@
         <v>8589</v>
       </c>
       <c r="B439" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C439" t="s">
         <v>294</v>
@@ -9010,7 +9016,7 @@
         <v>2530</v>
       </c>
       <c r="B440" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C440" t="s">
         <v>534</v>
@@ -9021,7 +9027,7 @@
         <v>1455</v>
       </c>
       <c r="B441" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C441" t="s">
         <v>202</v>
@@ -9032,7 +9038,7 @@
         <v>5220</v>
       </c>
       <c r="B442" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C442" t="s">
         <v>304</v>
@@ -9043,7 +9049,7 @@
         <v>2935</v>
       </c>
       <c r="B443" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -9054,7 +9060,7 @@
         <v>20607</v>
       </c>
       <c r="B444" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C444" t="s">
         <v>304</v>
@@ -9065,7 +9071,7 @@
         <v>4260</v>
       </c>
       <c r="B445" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C445" t="s">
         <v>510</v>
@@ -9076,10 +9082,10 @@
         <v>1426</v>
       </c>
       <c r="B446" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C446" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -9087,7 +9093,7 @@
         <v>11272</v>
       </c>
       <c r="B447" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C447" t="s">
         <v>8</v>
@@ -9098,10 +9104,10 @@
         <v>1282</v>
       </c>
       <c r="B448" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C448" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -9109,7 +9115,7 @@
         <v>172</v>
       </c>
       <c r="B449" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C449" t="s">
         <v>129</v>
@@ -9120,7 +9126,7 @@
         <v>3135</v>
       </c>
       <c r="B450" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C450" t="s">
         <v>20</v>
@@ -9131,7 +9137,7 @@
         <v>5066</v>
       </c>
       <c r="B451" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C451" t="s">
         <v>232</v>
@@ -9142,10 +9148,10 @@
         <v>495</v>
       </c>
       <c r="B452" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C452" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -9153,10 +9159,10 @@
         <v>43</v>
       </c>
       <c r="B453" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C453" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -9167,7 +9173,7 @@
         <v>126</v>
       </c>
       <c r="C454" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -9175,7 +9181,7 @@
         <v>4081</v>
       </c>
       <c r="B455" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C455" t="s">
         <v>378</v>
@@ -9186,7 +9192,7 @@
         <v>8246</v>
       </c>
       <c r="B456" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C456" t="s">
         <v>296</v>
@@ -9197,7 +9203,7 @@
         <v>32</v>
       </c>
       <c r="B457" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C457" t="s">
         <v>232</v>
@@ -9208,7 +9214,7 @@
         <v>12520</v>
       </c>
       <c r="B458" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C458" t="s">
         <v>277</v>
@@ -9219,10 +9225,10 @@
         <v>3015</v>
       </c>
       <c r="B459" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C459" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -9230,10 +9236,10 @@
         <v>4000</v>
       </c>
       <c r="B460" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C460" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -9241,7 +9247,7 @@
         <v>2905</v>
       </c>
       <c r="B461" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C461" t="s">
         <v>334</v>
@@ -9252,10 +9258,10 @@
         <v>394</v>
       </c>
       <c r="B462" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C462" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -9263,10 +9269,10 @@
         <v>3799</v>
       </c>
       <c r="B463" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C463" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -9274,10 +9280,10 @@
         <v>809</v>
       </c>
       <c r="B464" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C464" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -9285,7 +9291,7 @@
         <v>3820</v>
       </c>
       <c r="B465" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C465" t="s">
         <v>432</v>
@@ -9296,10 +9302,10 @@
         <v>3926</v>
       </c>
       <c r="B466" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C466" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -9307,7 +9313,7 @@
         <v>785</v>
       </c>
       <c r="B467" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C467" t="s">
         <v>79</v>
@@ -9318,10 +9324,10 @@
         <v>4084</v>
       </c>
       <c r="B468" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C468" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -9329,7 +9335,7 @@
         <v>1030</v>
       </c>
       <c r="B469" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C469" t="s">
         <v>361</v>
@@ -9340,7 +9346,7 @@
         <v>2925</v>
       </c>
       <c r="B470" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C470" t="s">
         <v>232</v>
@@ -9351,7 +9357,7 @@
         <v>363</v>
       </c>
       <c r="B471" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C471" t="s">
         <v>565</v>
@@ -9362,7 +9368,7 @@
         <v>4437</v>
       </c>
       <c r="B472" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C472" t="s">
         <v>456</v>
@@ -9373,10 +9379,10 @@
         <v>1898</v>
       </c>
       <c r="B473" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C473" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -9384,10 +9390,10 @@
         <v>395</v>
       </c>
       <c r="B474" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C474" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -9395,10 +9401,10 @@
         <v>3507</v>
       </c>
       <c r="B475" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C475" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -9406,7 +9412,7 @@
         <v>2080</v>
       </c>
       <c r="B476" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C476" t="s">
         <v>534</v>
@@ -9417,10 +9423,10 @@
         <v>5514</v>
       </c>
       <c r="B477" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C477" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -9428,10 +9434,10 @@
         <v>3281</v>
       </c>
       <c r="B478" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C478" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -9439,10 +9445,10 @@
         <v>2120</v>
       </c>
       <c r="B479" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C479" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -9450,10 +9456,10 @@
         <v>3734</v>
       </c>
       <c r="B480" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C480" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -9461,10 +9467,10 @@
         <v>1193</v>
       </c>
       <c r="B481" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C481" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -9472,10 +9478,10 @@
         <v>1082</v>
       </c>
       <c r="B482" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C482" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -9483,10 +9489,10 @@
         <v>269</v>
       </c>
       <c r="B483" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C483" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -9494,7 +9500,7 @@
         <v>4916</v>
       </c>
       <c r="B484" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C484" t="s">
         <v>517</v>
@@ -9505,10 +9511,10 @@
         <v>7946</v>
       </c>
       <c r="B485" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C485" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -9516,7 +9522,7 @@
         <v>24334</v>
       </c>
       <c r="B486" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C486" t="s">
         <v>294</v>
@@ -9527,10 +9533,10 @@
         <v>4615</v>
       </c>
       <c r="B487" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C487" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -9538,7 +9544,7 @@
         <v>2007</v>
       </c>
       <c r="B488" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C488" t="s">
         <v>325</v>
@@ -9549,7 +9555,7 @@
         <v>1196</v>
       </c>
       <c r="B489" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C489" t="s">
         <v>181</v>
@@ -9560,10 +9566,10 @@
         <v>5672</v>
       </c>
       <c r="B490" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C490" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -9571,7 +9577,7 @@
         <v>4413</v>
       </c>
       <c r="B491" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C491" t="s">
         <v>315</v>
@@ -9582,7 +9588,7 @@
         <v>50245</v>
       </c>
       <c r="B492" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C492" t="s">
         <v>145</v>
@@ -9593,10 +9599,10 @@
         <v>4136</v>
       </c>
       <c r="B493" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C493" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -9604,10 +9610,10 @@
         <v>87</v>
       </c>
       <c r="B494" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C494" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -9615,7 +9621,7 @@
         <v>522</v>
       </c>
       <c r="B495" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C495" t="s">
         <v>202</v>
@@ -9626,7 +9632,7 @@
         <v>1835</v>
       </c>
       <c r="B496" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C496" t="s">
         <v>256</v>
@@ -9637,10 +9643,10 @@
         <v>4183</v>
       </c>
       <c r="B497" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C497" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -9648,10 +9654,10 @@
         <v>3508</v>
       </c>
       <c r="B498" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C498" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -9659,7 +9665,7 @@
         <v>63633</v>
       </c>
       <c r="B499" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C499" t="s">
         <v>20</v>
@@ -9670,10 +9676,10 @@
         <v>2634</v>
       </c>
       <c r="B500" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C500" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -9681,10 +9687,10 @@
         <v>2867</v>
       </c>
       <c r="B501" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C501" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -9692,7 +9698,7 @@
         <v>886</v>
       </c>
       <c r="B502" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C502" t="s">
         <v>216</v>
@@ -9703,10 +9709,10 @@
         <v>248</v>
       </c>
       <c r="B503" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C503" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -9714,10 +9720,10 @@
         <v>967</v>
       </c>
       <c r="B504" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C504" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -9725,10 +9731,10 @@
         <v>3244</v>
       </c>
       <c r="B505" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C505" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -9736,10 +9742,10 @@
         <v>13554</v>
       </c>
       <c r="B506" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C506" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -9747,10 +9753,10 @@
         <v>60</v>
       </c>
       <c r="B507" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C507" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -9758,7 +9764,7 @@
         <v>5682</v>
       </c>
       <c r="B508" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C508" t="s">
         <v>56</v>
@@ -9769,10 +9775,10 @@
         <v>9</v>
       </c>
       <c r="B509" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C509" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -9780,10 +9786,10 @@
         <v>1163</v>
       </c>
       <c r="B510" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C510" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -9791,10 +9797,10 @@
         <v>38</v>
       </c>
       <c r="B511" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C511" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -9802,10 +9808,10 @@
         <v>3719</v>
       </c>
       <c r="B512" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C512" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -9813,10 +9819,10 @@
         <v>1083</v>
       </c>
       <c r="B513" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C513" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -9824,10 +9830,10 @@
         <v>2796</v>
       </c>
       <c r="B514" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C514" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -9835,10 +9841,10 @@
         <v>1848</v>
       </c>
       <c r="B515" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C515" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -9846,10 +9852,10 @@
         <v>558</v>
       </c>
       <c r="B516" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C516" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -9857,7 +9863,7 @@
         <v>16286</v>
       </c>
       <c r="B517" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C517" t="s">
         <v>277</v>
@@ -9868,7 +9874,7 @@
         <v>2323</v>
       </c>
       <c r="B518" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C518" t="s">
         <v>304</v>
@@ -9879,7 +9885,7 @@
         <v>13703</v>
       </c>
       <c r="B519" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C519" t="s">
         <v>304</v>
@@ -9890,10 +9896,10 @@
         <v>2066</v>
       </c>
       <c r="B520" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C520" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -9901,7 +9907,7 @@
         <v>3821</v>
       </c>
       <c r="B521" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C521" t="s">
         <v>361</v>
@@ -9912,7 +9918,7 @@
         <v>26151</v>
       </c>
       <c r="B522" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C522" t="s">
         <v>302</v>
@@ -9923,7 +9929,7 @@
         <v>6451</v>
       </c>
       <c r="B523" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C523" t="s">
         <v>296</v>
@@ -9934,10 +9940,10 @@
         <v>918</v>
       </c>
       <c r="B524" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C524" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -9945,10 +9951,10 @@
         <v>3013</v>
       </c>
       <c r="B525" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C525" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -9956,7 +9962,7 @@
         <v>9167</v>
       </c>
       <c r="B526" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C526" t="s">
         <v>145</v>
@@ -9967,10 +9973,10 @@
         <v>1756</v>
       </c>
       <c r="B527" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C527" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -9978,10 +9984,10 @@
         <v>714</v>
       </c>
       <c r="B528" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C528" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -9989,7 +9995,7 @@
         <v>4525</v>
       </c>
       <c r="B529" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C529" t="s">
         <v>317</v>
@@ -10000,7 +10006,7 @@
         <v>2435</v>
       </c>
       <c r="B530" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C530" t="s">
         <v>296</v>
@@ -10011,7 +10017,7 @@
         <v>24626</v>
       </c>
       <c r="B531" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C531" t="s">
         <v>232</v>
@@ -10022,10 +10028,10 @@
         <v>256</v>
       </c>
       <c r="B532" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C532" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -10033,7 +10039,7 @@
         <v>8171</v>
       </c>
       <c r="B533" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C533" t="s">
         <v>325</v>
@@ -10044,7 +10050,7 @@
         <v>122</v>
       </c>
       <c r="B534" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C534" t="s">
         <v>529</v>
@@ -10055,7 +10061,7 @@
         <v>2837</v>
       </c>
       <c r="B535" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C535" t="s">
         <v>282</v>
@@ -10066,10 +10072,10 @@
         <v>19758</v>
       </c>
       <c r="B536" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C536" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -10077,10 +10083,10 @@
         <v>1095</v>
       </c>
       <c r="B537" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C537" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -10088,10 +10094,10 @@
         <v>1451</v>
       </c>
       <c r="B538" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C538" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -10099,10 +10105,10 @@
         <v>3713</v>
       </c>
       <c r="B539" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C539" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -10110,10 +10116,10 @@
         <v>775</v>
       </c>
       <c r="B540" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C540" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -10121,10 +10127,10 @@
         <v>1754</v>
       </c>
       <c r="B541" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C541" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -10132,10 +10138,10 @@
         <v>4229</v>
       </c>
       <c r="B542" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C542" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -10143,10 +10149,10 @@
         <v>3850</v>
       </c>
       <c r="B543" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C543" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -10154,10 +10160,10 @@
         <v>1359</v>
       </c>
       <c r="B544" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C544" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -10165,7 +10171,7 @@
         <v>14897</v>
       </c>
       <c r="B545" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C545" t="s">
         <v>216</v>
@@ -10176,10 +10182,10 @@
         <v>452</v>
       </c>
       <c r="B546" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C546" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -10187,10 +10193,10 @@
         <v>2728</v>
       </c>
       <c r="B547" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C547" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -10198,10 +10204,10 @@
         <v>3390</v>
       </c>
       <c r="B548" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C548" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -10209,7 +10215,7 @@
         <v>10766</v>
       </c>
       <c r="B549" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C549" t="s">
         <v>519</v>
@@ -10220,10 +10226,10 @@
         <v>2695</v>
       </c>
       <c r="B550" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C550" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -10231,10 +10237,10 @@
         <v>4656</v>
       </c>
       <c r="B551" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C551" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -10242,7 +10248,7 @@
         <v>66104</v>
       </c>
       <c r="B552" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C552" t="s">
         <v>256</v>
@@ -10253,7 +10259,7 @@
         <v>4472</v>
       </c>
       <c r="B553" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C553" t="s">
         <v>256</v>
@@ -10264,10 +10270,10 @@
         <v>1355</v>
       </c>
       <c r="B554" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C554" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -10275,10 +10281,10 @@
         <v>2569</v>
       </c>
       <c r="B555" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C555" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -10286,7 +10292,7 @@
         <v>54312</v>
       </c>
       <c r="B556" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C556" t="s">
         <v>304</v>
@@ -10297,7 +10303,7 @@
         <v>50234</v>
       </c>
       <c r="B557" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C557" t="s">
         <v>256</v>
@@ -10308,7 +10314,7 @@
         <v>15259</v>
       </c>
       <c r="B558" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C558" t="s">
         <v>345</v>
@@ -10319,7 +10325,7 @@
         <v>13522</v>
       </c>
       <c r="B559" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C559" t="s">
         <v>79</v>
@@ -10330,10 +10336,10 @@
         <v>973</v>
       </c>
       <c r="B560" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C560" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -10341,7 +10347,7 @@
         <v>37776</v>
       </c>
       <c r="B561" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C561" t="s">
         <v>294</v>
@@ -10352,10 +10358,10 @@
         <v>953</v>
       </c>
       <c r="B562" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C562" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -10363,10 +10369,10 @@
         <v>530</v>
       </c>
       <c r="B563" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C563" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -10374,7 +10380,7 @@
         <v>8900</v>
       </c>
       <c r="B564" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C564" t="s">
         <v>232</v>
@@ -10385,7 +10391,7 @@
         <v>3063</v>
       </c>
       <c r="B565" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C565" t="s">
         <v>232</v>
@@ -10396,10 +10402,10 @@
         <v>723</v>
       </c>
       <c r="B566" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C566" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -10407,10 +10413,10 @@
         <v>194</v>
       </c>
       <c r="B567" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C567" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -10418,10 +10424,10 @@
         <v>423</v>
       </c>
       <c r="B568" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C568" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -10429,7 +10435,7 @@
         <v>4714</v>
       </c>
       <c r="B569" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C569" t="s">
         <v>256</v>
@@ -10440,10 +10446,10 @@
         <v>599</v>
       </c>
       <c r="B570" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C570" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -10451,7 +10457,7 @@
         <v>3934</v>
       </c>
       <c r="B571" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C571" t="s">
         <v>378</v>
@@ -10462,7 +10468,7 @@
         <v>1831</v>
       </c>
       <c r="B572" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C572" t="s">
         <v>444</v>
@@ -10473,7 +10479,7 @@
         <v>2009</v>
       </c>
       <c r="B573" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C573" t="s">
         <v>145</v>
@@ -10484,7 +10490,7 @@
         <v>19589</v>
       </c>
       <c r="B574" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C574" t="s">
         <v>202</v>
@@ -10495,10 +10501,10 @@
         <v>4823</v>
       </c>
       <c r="B575" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C575" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -10506,7 +10512,7 @@
         <v>4474</v>
       </c>
       <c r="B576" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C576" t="s">
         <v>256</v>
@@ -10517,10 +10523,10 @@
         <v>3160</v>
       </c>
       <c r="B577" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C577" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -10528,10 +10534,10 @@
         <v>903</v>
       </c>
       <c r="B578" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C578" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -10539,7 +10545,7 @@
         <v>5859</v>
       </c>
       <c r="B579" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C579" t="s">
         <v>294</v>
@@ -10550,10 +10556,10 @@
         <v>4337</v>
       </c>
       <c r="B580" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C580" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -10561,7 +10567,7 @@
         <v>3547</v>
       </c>
       <c r="B581" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C581" t="s">
         <v>519</v>
@@ -10572,7 +10578,7 @@
         <v>3471</v>
       </c>
       <c r="B582" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C582" t="s">
         <v>534</v>
@@ -10583,10 +10589,10 @@
         <v>1037</v>
       </c>
       <c r="B583" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C583" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -10594,10 +10600,10 @@
         <v>1177</v>
       </c>
       <c r="B584" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C584" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -10605,7 +10611,7 @@
         <v>807</v>
       </c>
       <c r="B585" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C585" t="s">
         <v>563</v>
@@ -10616,7 +10622,7 @@
         <v>33135</v>
       </c>
       <c r="B586" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C586" t="s">
         <v>460</v>
@@ -10627,10 +10633,10 @@
         <v>938</v>
       </c>
       <c r="B587" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C587" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -10638,10 +10644,10 @@
         <v>8052</v>
       </c>
       <c r="B588" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C588" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -10649,10 +10655,10 @@
         <v>4620</v>
       </c>
       <c r="B589" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C589" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -10660,10 +10666,10 @@
         <v>4843</v>
       </c>
       <c r="B590" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C590" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -10671,10 +10677,10 @@
         <v>8045</v>
       </c>
       <c r="B591" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C591" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -10682,10 +10688,10 @@
         <v>3046</v>
       </c>
       <c r="B592" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C592" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -10693,7 +10699,7 @@
         <v>1242</v>
       </c>
       <c r="B593" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C593" t="s">
         <v>216</v>
@@ -10704,10 +10710,10 @@
         <v>2056</v>
       </c>
       <c r="B594" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C594" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -10715,7 +10721,7 @@
         <v>328</v>
       </c>
       <c r="B595" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C595" t="s">
         <v>8</v>
@@ -10726,7 +10732,7 @@
         <v>16431</v>
       </c>
       <c r="B596" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C596" t="s">
         <v>277</v>
@@ -10737,7 +10743,7 @@
         <v>3513</v>
       </c>
       <c r="B597" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C597" t="s">
         <v>145</v>
@@ -10748,10 +10754,10 @@
         <v>7975</v>
       </c>
       <c r="B598" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C598" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -10759,7 +10765,7 @@
         <v>337</v>
       </c>
       <c r="B599" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C599" t="s">
         <v>8</v>
@@ -10770,7 +10776,7 @@
         <v>1533</v>
       </c>
       <c r="B600" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C600" t="s">
         <v>167</v>
@@ -10781,7 +10787,7 @@
         <v>342</v>
       </c>
       <c r="B601" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C601" t="s">
         <v>8</v>
@@ -10792,7 +10798,7 @@
         <v>2940</v>
       </c>
       <c r="B602" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C602" t="s">
         <v>8</v>
@@ -10803,7 +10809,7 @@
         <v>1210</v>
       </c>
       <c r="B603" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C603" t="s">
         <v>8</v>
@@ -10814,7 +10820,7 @@
         <v>19620</v>
       </c>
       <c r="B604" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C604" t="s">
         <v>277</v>
@@ -10825,7 +10831,7 @@
         <v>2117</v>
       </c>
       <c r="B605" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C605" t="s">
         <v>8</v>
@@ -10836,10 +10842,10 @@
         <v>319</v>
       </c>
       <c r="B606" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C606" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -10847,7 +10853,7 @@
         <v>3447</v>
       </c>
       <c r="B607" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C607" t="s">
         <v>8</v>
@@ -10858,7 +10864,7 @@
         <v>5110</v>
       </c>
       <c r="B608" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C608" t="s">
         <v>107</v>
@@ -10869,7 +10875,7 @@
         <v>2654</v>
       </c>
       <c r="B609" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C609" t="s">
         <v>167</v>
@@ -10880,7 +10886,7 @@
         <v>2653</v>
       </c>
       <c r="B610" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C610" t="s">
         <v>167</v>
@@ -10891,7 +10897,7 @@
         <v>3543</v>
       </c>
       <c r="B611" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C611" t="s">
         <v>256</v>
@@ -10902,7 +10908,7 @@
         <v>65970</v>
       </c>
       <c r="B612" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C612" t="s">
         <v>277</v>
@@ -10913,7 +10919,7 @@
         <v>4911</v>
       </c>
       <c r="B613" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C613" t="s">
         <v>167</v>
@@ -10924,7 +10930,7 @@
         <v>1072</v>
       </c>
       <c r="B614" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C614" t="s">
         <v>565</v>
@@ -10935,7 +10941,7 @@
         <v>11044</v>
       </c>
       <c r="B615" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C615" t="s">
         <v>277</v>
@@ -10946,7 +10952,7 @@
         <v>4138</v>
       </c>
       <c r="B616" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C616" t="s">
         <v>20</v>
@@ -10957,7 +10963,7 @@
         <v>3664</v>
       </c>
       <c r="B617" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C617" t="s">
         <v>8</v>
@@ -10968,7 +10974,7 @@
         <v>3446</v>
       </c>
       <c r="B618" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C618" t="s">
         <v>8</v>
@@ -10979,7 +10985,7 @@
         <v>5051</v>
       </c>
       <c r="B619" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C619" t="s">
         <v>277</v>
@@ -10990,10 +10996,10 @@
         <v>16723</v>
       </c>
       <c r="B620" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C620" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -11001,7 +11007,7 @@
         <v>1580</v>
       </c>
       <c r="B621" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C621" t="s">
         <v>8</v>
@@ -11012,10 +11018,10 @@
         <v>2818</v>
       </c>
       <c r="B622" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C622" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -11023,7 +11029,7 @@
         <v>5575</v>
       </c>
       <c r="B623" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C623" t="s">
         <v>277</v>

--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18640"/>
+    <workbookView windowWidth="28260" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="premier_league_players_merged_f" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1001">
   <si>
     <t>player_id</t>
   </si>
@@ -2964,6 +2964,9 @@
   </si>
   <si>
     <t>Oleksandr Zinchenko</t>
+  </si>
+  <si>
+    <t>Manchester City;Arsenal</t>
   </si>
   <si>
     <t>Ruud van Nistelrooij</t>
@@ -10823,7 +10826,7 @@
         <v>978</v>
       </c>
       <c r="C604" t="s">
-        <v>277</v>
+        <v>979</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -10831,7 +10834,7 @@
         <v>2117</v>
       </c>
       <c r="B605" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C605" t="s">
         <v>8</v>
@@ -10842,10 +10845,10 @@
         <v>319</v>
       </c>
       <c r="B606" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C606" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -10853,7 +10856,7 @@
         <v>3447</v>
       </c>
       <c r="B607" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C607" t="s">
         <v>8</v>
@@ -10864,7 +10867,7 @@
         <v>5110</v>
       </c>
       <c r="B608" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C608" t="s">
         <v>107</v>
@@ -10875,7 +10878,7 @@
         <v>2654</v>
       </c>
       <c r="B609" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C609" t="s">
         <v>167</v>
@@ -10886,7 +10889,7 @@
         <v>2653</v>
       </c>
       <c r="B610" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C610" t="s">
         <v>167</v>
@@ -10897,7 +10900,7 @@
         <v>3543</v>
       </c>
       <c r="B611" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C611" t="s">
         <v>256</v>
@@ -10908,7 +10911,7 @@
         <v>65970</v>
       </c>
       <c r="B612" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C612" t="s">
         <v>277</v>
@@ -10919,7 +10922,7 @@
         <v>4911</v>
       </c>
       <c r="B613" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C613" t="s">
         <v>167</v>
@@ -10930,7 +10933,7 @@
         <v>1072</v>
       </c>
       <c r="B614" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C614" t="s">
         <v>565</v>
@@ -10941,7 +10944,7 @@
         <v>11044</v>
       </c>
       <c r="B615" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C615" t="s">
         <v>277</v>
@@ -10952,7 +10955,7 @@
         <v>4138</v>
       </c>
       <c r="B616" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C616" t="s">
         <v>20</v>
@@ -10963,7 +10966,7 @@
         <v>3664</v>
       </c>
       <c r="B617" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C617" t="s">
         <v>8</v>
@@ -10974,7 +10977,7 @@
         <v>3446</v>
       </c>
       <c r="B618" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C618" t="s">
         <v>8</v>
@@ -10985,7 +10988,7 @@
         <v>5051</v>
       </c>
       <c r="B619" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C619" t="s">
         <v>277</v>
@@ -10996,10 +10999,10 @@
         <v>16723</v>
       </c>
       <c r="B620" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C620" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -11007,7 +11010,7 @@
         <v>1580</v>
       </c>
       <c r="B621" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C621" t="s">
         <v>8</v>
@@ -11018,10 +11021,10 @@
         <v>2818</v>
       </c>
       <c r="B622" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C622" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -11029,7 +11032,7 @@
         <v>5575</v>
       </c>
       <c r="B623" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C623" t="s">
         <v>277</v>

--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="13440"/>
+    <workbookView windowWidth="28260" windowHeight="15040"/>
   </bookViews>
   <sheets>
     <sheet name="premier_league_players_merged_f" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1002">
   <si>
     <t>player_id</t>
   </si>
@@ -161,1552 +161,1555 @@
     <t>Jordan Henderson</t>
   </si>
   <si>
+    <t>Sunderland;Liverpool;Brentford</t>
+  </si>
+  <si>
+    <t>Aaron Hughes</t>
+  </si>
+  <si>
+    <t>Newcastle United;Aston Villa;Fulham;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Brad Friedel</t>
+  </si>
+  <si>
+    <t>Liverpool;Blackburn Rovers;Aston Villa;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Shay Given</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Newcastle United;Manchester City;Aston Villa;Stoke City</t>
+  </si>
+  <si>
+    <t>John O'Shea</t>
+  </si>
+  <si>
+    <t>Manchester United;Sunderland</t>
+  </si>
+  <si>
+    <t>Kevin Davies</t>
+  </si>
+  <si>
+    <t>Southampton;Blackburn Rovers;Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Petr Cech</t>
+  </si>
+  <si>
+    <t>Chelsea;Arsenal</t>
+  </si>
+  <si>
+    <t>Alan Shearer</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Newcastle United</t>
+  </si>
+  <si>
+    <t>Kyle Walker</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Aston Villa;Manchester City;Burnley</t>
+  </si>
+  <si>
+    <t>Jussi Jääskeläinen</t>
+  </si>
+  <si>
+    <t>Bolton Wanderers;West Ham United</t>
+  </si>
+  <si>
+    <t>Richard Dunne</t>
+  </si>
+  <si>
+    <t>Everton;Manchester City;Aston Villa;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Gareth Southgate</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Aston Villa;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Leighton Baines</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Everton</t>
+  </si>
+  <si>
+    <t>Teddy Sheringham</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
+  </si>
+  <si>
+    <t>Danny Murphy</t>
+  </si>
+  <si>
+    <t>Liverpool;Charlton Athletic;Tottenham Hotspur;Fulham;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Aaron Lennon</t>
+  </si>
+  <si>
+    <t>Leeds United;Tottenham Hotspur;Everton;Burnley</t>
+  </si>
+  <si>
+    <t>James Ward-Prowse</t>
+  </si>
+  <si>
+    <t>Southampton;West Ham United;Burnley</t>
+  </si>
+  <si>
+    <t>David de Gea</t>
+  </si>
+  <si>
+    <t>Mark Noble</t>
+  </si>
+  <si>
+    <t>West Ham United</t>
+  </si>
+  <si>
+    <t>Andrew Cole</t>
+  </si>
+  <si>
+    <t>Newcastle United;Manchester United;Blackburn Rovers;Fulham;Manchester City;Portsmouth;Sunderland</t>
+  </si>
+  <si>
+    <t>Nicky Butt</t>
+  </si>
+  <si>
+    <t>Manchester United;Newcastle United</t>
+  </si>
+  <si>
+    <t>Stewart Downing</t>
+  </si>
+  <si>
+    <t>Middlesbrough;Aston Villa;Liverpool;West Ham United</t>
+  </si>
+  <si>
+    <t>Kevin Nolan</t>
+  </si>
+  <si>
+    <t>Bolton Wanderers;Newcastle United;West Ham United</t>
+  </si>
+  <si>
+    <t>Gary Neville</t>
+  </si>
+  <si>
+    <t>Tim Howard</t>
+  </si>
+  <si>
+    <t>Lee Bowyer</t>
+  </si>
+  <si>
+    <t>Leeds United;West Ham United;Newcastle United;Birmingham City</t>
+  </si>
+  <si>
+    <t>Theo Walcott</t>
+  </si>
+  <si>
+    <t>Arsenal;Everton;Southampton</t>
+  </si>
+  <si>
+    <t>Raheem Sterling</t>
+  </si>
+  <si>
+    <t>Liverpool;Manchester City;Chelsea;Arsenal</t>
+  </si>
+  <si>
+    <t>Danny Welbeck</t>
+  </si>
+  <si>
+    <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Gary Cahill</t>
+  </si>
+  <si>
+    <t>Aston Villa;Bolton Wanderers;Chelsea;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Damien Duff</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Chelsea;Newcastle United;Fulham</t>
+  </si>
+  <si>
+    <t>Ben Foster</t>
+  </si>
+  <si>
+    <t>Manchester United;Watford;Birmingham City;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Jonny Evans</t>
+  </si>
+  <si>
+    <t>Manchester United;West Bromwich Albion;Leicester City</t>
+  </si>
+  <si>
+    <t>Ashley Cole</t>
+  </si>
+  <si>
+    <t>Arsenal;Chelsea</t>
+  </si>
+  <si>
+    <t>George Boateng</t>
+  </si>
+  <si>
+    <t>Coventry City;Aston Villa;Middlesbrough;Hull City</t>
+  </si>
+  <si>
+    <t>Robbie Fowler</t>
+  </si>
+  <si>
+    <t>Liverpool;Leeds United;Manchester City;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Ray Parlour</t>
+  </si>
+  <si>
+    <t>Arsenal;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Luke Young</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Charlton Athletic;Middlesbrough;Aston Villa</t>
+  </si>
+  <si>
+    <t>Joe Cole</t>
+  </si>
+  <si>
+    <t>West Ham United;Chelsea;Liverpool;Aston Villa</t>
+  </si>
+  <si>
+    <t>Stephen Carr</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Newcastle United;Birmingham City</t>
+  </si>
+  <si>
+    <t>Lukasz Fabianski</t>
+  </si>
+  <si>
+    <t>Arsenal;Swansea City;West Ham United</t>
+  </si>
+  <si>
+    <t>Phil Jagielka</t>
+  </si>
+  <si>
+    <t>Sheffield United;Everton</t>
+  </si>
+  <si>
+    <t>Dwight Yorke</t>
+  </si>
+  <si>
+    <t>Aston Villa;Manchester United;Blackburn Rovers;Birmingham City;Sunderland</t>
+  </si>
+  <si>
+    <t>Paul Robinson</t>
+  </si>
+  <si>
+    <t>Leeds United;Tottenham Hotspur;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Séamus Coleman</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Nigel Martyn</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Leeds United;Everton</t>
+  </si>
+  <si>
+    <t>Scott Parker</t>
+  </si>
+  <si>
+    <t>Charlton Athletic;Chelsea;Newcastle United;West Ham United;Tottenham Hotspur;Fulham</t>
+  </si>
+  <si>
+    <t>Roy Keane</t>
+  </si>
+  <si>
+    <t>Nottingham Forest;Manchester United</t>
+  </si>
+  <si>
+    <t>Nicolas Anelka</t>
+  </si>
+  <si>
+    <t>Arsenal;Liverpool;Manchester City;Bolton Wanderers;Chelsea;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>David Unsworth</t>
+  </si>
+  <si>
+    <t>Everton;West Ham United;Aston Villa;Portsmouth;Wigan Athletic;Sheffield United</t>
+  </si>
+  <si>
+    <t>Chris Perry</t>
+  </si>
+  <si>
+    <t>Wimbledon;Tottenham Hotspur;Charlton Athletic;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Thomas Sørensen</t>
+  </si>
+  <si>
+    <t>Sunderland;Aston Villa;Stoke City</t>
+  </si>
+  <si>
+    <t>Hugo Lloris</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Trevor Sinclair</t>
+  </si>
+  <si>
+    <t>Queens Park Rangers;West Ham United;Manchester City</t>
+  </si>
+  <si>
+    <t>Rory Delap</t>
+  </si>
+  <si>
+    <t>Derby County;Southampton;Sunderland;Stoke City</t>
+  </si>
+  <si>
+    <t>Glen Johnson</t>
+  </si>
+  <si>
+    <t>West Ham United;Chelsea;Portsmouth;Liverpool;Stoke City</t>
+  </si>
+  <si>
+    <t>Jordan Pickford</t>
+  </si>
+  <si>
+    <t>Sunderland;Everton</t>
+  </si>
+  <si>
+    <t>Ugo Ehiogu</t>
+  </si>
+  <si>
+    <t>Aston Villa;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Leon Osman</t>
+  </si>
+  <si>
+    <t>Kolo Touré</t>
+  </si>
+  <si>
+    <t>Arsenal;Manchester City;Liverpool</t>
+  </si>
+  <si>
+    <t>Nigel Winterburn</t>
+  </si>
+  <si>
+    <t>Arsenal;West Ham United;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Les Ferdinand</t>
+  </si>
+  <si>
+    <t>Queens Park Rangers;Newcastle United;Tottenham Hotspur;West Ham United;Leicester City;Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Steve Watson</t>
+  </si>
+  <si>
+    <t>Newcastle United;Aston Villa;Everton;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Cesc Fàbregas</t>
+  </si>
+  <si>
+    <t>César Azpilicueta</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Robbie Keane</t>
+  </si>
+  <si>
+    <t>Coventry City;Leeds United;Tottenham Hotspur;Liverpool;West Ham United;Aston Villa</t>
+  </si>
+  <si>
+    <t>Paul Konchesky</t>
+  </si>
+  <si>
+    <t>Charlton Athletic;West Ham United;Fulham;Liverpool</t>
+  </si>
+  <si>
+    <t>Robbie Savage</t>
+  </si>
+  <si>
+    <t>Leicester City;Birmingham City;Blackburn Rovers;Derby County</t>
+  </si>
+  <si>
+    <t>Shane Long</t>
+  </si>
+  <si>
+    <t>Reading;West Bromwich Albion;Hull City;Southampton</t>
+  </si>
+  <si>
+    <t>David Seaman</t>
+  </si>
+  <si>
+    <t>Arsenal;Manchester City</t>
+  </si>
+  <si>
+    <t>Nick Barmby</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Middlesbrough;Everton;Liverpool;Leeds United</t>
+  </si>
+  <si>
+    <t>Jamie Vardy</t>
+  </si>
+  <si>
+    <t>Leicester City</t>
+  </si>
+  <si>
+    <t>Darren Fletcher</t>
+  </si>
+  <si>
+    <t>Manchester United;West Bromwich Albion;Stoke City</t>
+  </si>
+  <si>
+    <t>Tim Sherwood</t>
+  </si>
+  <si>
+    <t>Norwich City;Blackburn Rovers;Tottenham Hotspur;Portsmouth;Coventry City</t>
+  </si>
+  <si>
+    <t>Joe Hart</t>
+  </si>
+  <si>
+    <t>Manchester City;Birmingham City;West Ham United;Burnley</t>
+  </si>
+  <si>
+    <t>Steed Malbranque</t>
+  </si>
+  <si>
+    <t>Fulham;Tottenham Hotspur;Sunderland</t>
+  </si>
+  <si>
+    <t>Kenny Cunningham</t>
+  </si>
+  <si>
+    <t>Wimbledon;Birmingham City;Sunderland</t>
+  </si>
+  <si>
+    <t>James Tarkowski</t>
+  </si>
+  <si>
+    <t>Burnley;Everton</t>
+  </si>
+  <si>
+    <t>Son Heung-Min</t>
+  </si>
+  <si>
+    <t>Virgil van Dijk</t>
+  </si>
+  <si>
+    <t>Southampton;Liverpool</t>
+  </si>
+  <si>
+    <t>Hermann Hreidarsson</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Wimbledon;Ipswich Town;Charlton Athletic;Portsmouth</t>
+  </si>
+  <si>
+    <t>James Beattie</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Southampton;Everton;Stoke City</t>
+  </si>
+  <si>
+    <t>Jason Dodd</t>
+  </si>
+  <si>
+    <t>Southampton</t>
+  </si>
+  <si>
+    <t>Denis Irwin</t>
+  </si>
+  <si>
+    <t>Andy Robertson</t>
+  </si>
+  <si>
+    <t>Hull City;Liverpool</t>
+  </si>
+  <si>
+    <t>Willian</t>
+  </si>
+  <si>
+    <t>Chelsea;Arsenal;Fulham</t>
+  </si>
+  <si>
+    <t>Graeme Le Saux</t>
+  </si>
+  <si>
+    <t>Chelsea;Blackburn Rovers;Southampton</t>
+  </si>
+  <si>
+    <t>Michael Owen</t>
+  </si>
+  <si>
+    <t>Liverpool;Newcastle United;Manchester United;Stoke City</t>
+  </si>
+  <si>
+    <t>Kevin Campbell</t>
+  </si>
+  <si>
+    <t>Arsenal;Nottingham Forest;Everton</t>
+  </si>
+  <si>
+    <t>Gaël Clichy</t>
+  </si>
+  <si>
+    <t>Gary Kelly</t>
+  </si>
+  <si>
+    <t>Leeds United</t>
+  </si>
+  <si>
+    <t>Kevin Kilbane</t>
+  </si>
+  <si>
+    <t>Coventry City;Everton;Sunderland;Wigan Athletic;Hull City</t>
+  </si>
+  <si>
+    <t>Gary McAllister</t>
+  </si>
+  <si>
+    <t>Coventry City;Liverpool</t>
+  </si>
+  <si>
+    <t>Matthew Taylor</t>
+  </si>
+  <si>
+    <t>Portsmouth;Bolton Wanderers;West Ham United;Burnley</t>
+  </si>
+  <si>
+    <t>Antonio Valencia</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Manchester United</t>
+  </si>
+  <si>
+    <t>Mohamed Salah</t>
+  </si>
+  <si>
+    <t>Chelsea;Liverpool</t>
+  </si>
+  <si>
+    <t>James McArthur</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Martin Keown</t>
+  </si>
+  <si>
+    <t>Everton;Arsenal;Aston Villa</t>
+  </si>
+  <si>
+    <t>Gabriel Agbonlahor</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Robert Huth</t>
+  </si>
+  <si>
+    <t>Chelsea;Middlesbrough;Stoke City;Leicester City</t>
+  </si>
+  <si>
+    <t>William Gallas</t>
+  </si>
+  <si>
+    <t>Chelsea;Arsenal;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>John Arne Riise</t>
+  </si>
+  <si>
+    <t>Liverpool;Fulham</t>
+  </si>
+  <si>
+    <t>Harry Kane</t>
+  </si>
+  <si>
+    <t>Darren Anderton</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Birmingham City;Portsmouth</t>
+  </si>
+  <si>
+    <t>Paul Telfer</t>
+  </si>
+  <si>
+    <t>Coventry City;Southampton</t>
+  </si>
+  <si>
+    <t>Gylfi Sigurdsson</t>
+  </si>
+  <si>
+    <t>Swansea City;Tottenham Hotspur;Everton</t>
+  </si>
+  <si>
+    <t>Sami Hyypiä</t>
+  </si>
+  <si>
+    <t>Peter Atherton</t>
+  </si>
+  <si>
+    <t>Coventry City;Sheffield Wednesday;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Alex Iwobi</t>
+  </si>
+  <si>
+    <t>Arsenal;Everton;Fulham</t>
+  </si>
+  <si>
+    <t>Ben Davies</t>
+  </si>
+  <si>
+    <t>Swansea City;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Ryan Shawcross</t>
+  </si>
+  <si>
+    <t>Manchester United;Stoke City</t>
+  </si>
+  <si>
+    <t>Dennis Bergkamp</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Wayne Bridge</t>
+  </si>
+  <si>
+    <t>Southampton;Chelsea;Fulham;Manchester City;Sunderland</t>
+  </si>
+  <si>
+    <t>Shaun Wright-Phillips</t>
+  </si>
+  <si>
+    <t>Manchester City;Chelsea;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Edwin van der Sar</t>
+  </si>
+  <si>
+    <t>Fulham;Manchester United</t>
+  </si>
+  <si>
+    <t>Ian Walker</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Leicester City;Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Dion Dublin</t>
+  </si>
+  <si>
+    <t>Manchester United;Coventry City;Aston Villa;Leicester City</t>
+  </si>
+  <si>
+    <t>Aaron Cresswell</t>
+  </si>
+  <si>
+    <t>James Morrison</t>
+  </si>
+  <si>
+    <t>Middlesbrough;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Marc Albrighton</t>
+  </si>
+  <si>
+    <t>Aston Villa;Leicester City</t>
+  </si>
+  <si>
+    <t>Christian Eriksen</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Brentford;Manchester United</t>
+  </si>
+  <si>
+    <t>Peter Schmeichel</t>
+  </si>
+  <si>
+    <t>Manchester United;Aston Villa;Manchester City</t>
+  </si>
+  <si>
+    <t>David Silva</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Joel Ward</t>
+  </si>
+  <si>
+    <t>Portsmouth;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Wes Brown</t>
+  </si>
+  <si>
+    <t>Declan Rice</t>
+  </si>
+  <si>
+    <t>Arsenal;West Ham United</t>
+  </si>
+  <si>
+    <t>Patrick Vieira</t>
+  </si>
+  <si>
+    <t>Steven Davis</t>
+  </si>
+  <si>
+    <t>Aston Villa;Southampton</t>
+  </si>
+  <si>
+    <t>Paul Ince</t>
+  </si>
+  <si>
+    <t>Manchester United;Liverpool;Middlesbrough;Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Jordan Ayew</t>
+  </si>
+  <si>
+    <t>Aston Villa;Swansea City;Crystal Palace;Leicester City</t>
+  </si>
+  <si>
+    <t>Lee Dixon</t>
+  </si>
+  <si>
+    <t>Adam Lallana</t>
+  </si>
+  <si>
+    <t>Alan Wright</t>
+  </si>
+  <si>
+    <t>Wilfried Zaha</t>
+  </si>
+  <si>
+    <t>Crystal Palace</t>
+  </si>
+  <si>
+    <t>Jack Cork</t>
+  </si>
+  <si>
+    <t>Burnley</t>
+  </si>
+  <si>
+    <t>Craig Dawson</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Phil Bardsley</t>
+  </si>
+  <si>
+    <t>Manchester United;Sunderland;Stoke City;Burnley</t>
+  </si>
+  <si>
+    <t>Simon Davies</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Nolberto Solano</t>
+  </si>
+  <si>
+    <t>Newcastle United</t>
+  </si>
+  <si>
+    <t>Pablo Zabaleta</t>
+  </si>
+  <si>
+    <t>West Ham United;Manchester City</t>
+  </si>
+  <si>
+    <t>Garry Flitcroft</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Gavin McCann</t>
+  </si>
+  <si>
+    <t>Everton;Sunderland;Aston Villa;Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Ross Barkley</t>
+  </si>
+  <si>
+    <t>Aston Villa;Chelsea</t>
+  </si>
+  <si>
+    <t>Shola Ameobi</t>
+  </si>
+  <si>
+    <t>Wayne Routledge</t>
+  </si>
+  <si>
+    <t>Swansea City</t>
+  </si>
+  <si>
+    <t>Pepe Reina</t>
+  </si>
+  <si>
+    <t>Liverpool;Aston Villa</t>
+  </si>
+  <si>
+    <t>Marcus Rashford</t>
+  </si>
+  <si>
+    <t>Bernardo Silva</t>
+  </si>
+  <si>
+    <t>Mark Hughes</t>
+  </si>
+  <si>
+    <t>Manchester United;Chelsea;Southampton;Everton;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Luís Boa Morte</t>
+  </si>
+  <si>
+    <t>Arsenal;Southampton;Fulham;West Ham United</t>
+  </si>
+  <si>
+    <t>Lewis Dunk</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Jamie Redknapp</t>
+  </si>
+  <si>
+    <t>Moussa Sissoko</t>
+  </si>
+  <si>
+    <t>Newcastle United;Tottenham Hotspur;Watford</t>
+  </si>
+  <si>
+    <t>Graham Stuart</t>
+  </si>
+  <si>
+    <t>Everton;Charlton Athletic</t>
+  </si>
+  <si>
+    <t>Craig Bellamy</t>
+  </si>
+  <si>
+    <t>Coventry City;Newcastle United;Blackburn Rovers;Liverpool;West Ham United;Manchester City;Cardiff City</t>
+  </si>
+  <si>
+    <t>Titus Bramble</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Cheikhou Kouyaté</t>
+  </si>
+  <si>
+    <t>West Ham United;Crystal Palace;Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Andros Townsend</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Queens Park Rangers;Newcastle United;Crystal Palace;Everton;Luton Town</t>
+  </si>
+  <si>
+    <t>Jeff Kenna</t>
+  </si>
+  <si>
+    <t>Derby County</t>
+  </si>
+  <si>
+    <t>Claus Lundekvam</t>
+  </si>
+  <si>
+    <t>Luke Shaw</t>
+  </si>
+  <si>
+    <t>Manchester United;Southampton</t>
+  </si>
+  <si>
+    <t>Andy Impey</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Louis Saha</t>
+  </si>
+  <si>
+    <t>Newcastle United;Fulham;Manchester United;Everton;Tottenham Hotspur;Sunderland</t>
+  </si>
+  <si>
+    <t>James Tomkins</t>
+  </si>
+  <si>
+    <t>West Ham United;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Frank Sinclair</t>
+  </si>
+  <si>
+    <t>Chelsea;Leicester City</t>
+  </si>
+  <si>
+    <t>Matt Upson</t>
+  </si>
+  <si>
+    <t>Arsenal;Birmingham City;West Ham United;Stoke City;Leicester City</t>
+  </si>
+  <si>
+    <t>Steve Staunton</t>
+  </si>
+  <si>
+    <t>Coventry City;Aston Villa</t>
+  </si>
+  <si>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>Chelsea;Manchester City</t>
+  </si>
+  <si>
+    <t>Jimmy Floyd Hasselbaink</t>
+  </si>
+  <si>
+    <t>Leeds United;Chelsea;Middlesbrough;Charlton Athletic</t>
+  </si>
+  <si>
+    <t>Matthew Etherington</t>
+  </si>
+  <si>
+    <t>Stoke City</t>
+  </si>
+  <si>
+    <t>Carlton Cole</t>
+  </si>
+  <si>
+    <t>Joleon Lescott</t>
+  </si>
+  <si>
+    <t>Everton;Manchester City;West Bromwich Albion;Aston Villa;Sunderland</t>
+  </si>
+  <si>
+    <t>Tim Flowers</t>
+  </si>
+  <si>
+    <t>Southampton;Blackburn Rovers;Leicester City</t>
+  </si>
+  <si>
+    <t>Harry Maguire</t>
+  </si>
+  <si>
+    <t>Ashley Westwood</t>
+  </si>
+  <si>
+    <t>Aston Villa;Burnley</t>
+  </si>
+  <si>
+    <t>Brian Deane</t>
+  </si>
+  <si>
+    <t>Michael Dawson</t>
+  </si>
+  <si>
+    <t>Hull City;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Alan Smith</t>
+  </si>
+  <si>
+    <t>Leeds United;Manchester United;Newcastle United</t>
+  </si>
+  <si>
+    <t>Mikel Arteta</t>
+  </si>
+  <si>
+    <t>Everton;Arsenal</t>
+  </si>
+  <si>
+    <t>Zat Knight</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Riyad Mahrez</t>
+  </si>
+  <si>
+    <t>Leicester City;Manchester City</t>
+  </si>
+  <si>
+    <t>Mario Melchiot</t>
+  </si>
+  <si>
+    <t>Chelsea;Birmingham City;Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Kasper Schmeichel</t>
+  </si>
+  <si>
+    <t>Lee Carsley</t>
+  </si>
+  <si>
+    <t>Derby County;Blackburn Rovers;Coventry City;Everton;Birmingham City</t>
+  </si>
+  <si>
+    <t>Sebastian Larsson</t>
+  </si>
+  <si>
+    <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
+  </si>
+  <si>
+    <t>Charles N'Zogbia</t>
+  </si>
+  <si>
+    <t>Paul Merson</t>
+  </si>
+  <si>
+    <t>Arsenal;Middlesbrough;Aston Villa;Portsmouth</t>
+  </si>
+  <si>
+    <t>Robin van Persie</t>
+  </si>
+  <si>
+    <t>Arsenal;Manchester United</t>
+  </si>
+  <si>
+    <t>Jeffrey Schlupp</t>
+  </si>
+  <si>
+    <t>Norwich City;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Andy O'Brien</t>
+  </si>
+  <si>
+    <t>Christian Benteke</t>
+  </si>
+  <si>
+    <t>Aston Villa;Liverpool;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Robert Lee</t>
+  </si>
+  <si>
+    <t>Michael Keane</t>
+  </si>
+  <si>
+    <t>Everton;Burnley</t>
+  </si>
+  <si>
+    <t>Jermaine Jenas</t>
+  </si>
+  <si>
+    <t>Newcastle United;Tottenham Hotspur;Aston Villa;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Lucas Neill</t>
+  </si>
+  <si>
+    <t>Juan Mata</t>
+  </si>
+  <si>
+    <t>Chelsea;Manchester United</t>
+  </si>
+  <si>
+    <t>Dennis Wise</t>
+  </si>
+  <si>
+    <t>Jonjo Shelvey</t>
+  </si>
+  <si>
+    <t>Liverpool;Swansea City;Newcastle United;Nottingham Forest</t>
+  </si>
+  <si>
+    <t>James Collins</t>
+  </si>
+  <si>
+    <t>Ipswich Town;West Ham United</t>
+  </si>
+  <si>
+    <t>Romelu Lukaku</t>
+  </si>
+  <si>
+    <t>Chelsea;West Bromwich Albion;Everton;Manchester United</t>
+  </si>
+  <si>
+    <t>Patrice Evra</t>
+  </si>
+  <si>
+    <t>Abdoulaye Doucouré</t>
+  </si>
+  <si>
+    <t>Watford;Everton</t>
+  </si>
+  <si>
+    <t>Warren Barton</t>
+  </si>
+  <si>
+    <t>Wimbledon;Newcastle United;Derby County</t>
+  </si>
+  <si>
+    <t>Ben Mee</t>
+  </si>
+  <si>
+    <t>Sheffield United;Burnley</t>
+  </si>
+  <si>
+    <t>Glenn Whelan</t>
+  </si>
+  <si>
+    <t>Ederson</t>
+  </si>
+  <si>
+    <t>Nathan Redmond</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Southampton</t>
+  </si>
+  <si>
+    <t>Dominic Matteo</t>
+  </si>
+  <si>
+    <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
+  </si>
+  <si>
+    <t>Nathaniel Clyne</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Liverpool</t>
+  </si>
+  <si>
+    <t>Darren Bent</t>
+  </si>
+  <si>
+    <t>Ipswich Town;Charlton Athletic;Tottenham Hotspur;Sunderland;Aston Villa;Fulham</t>
+  </si>
+  <si>
+    <t>Sergio Agüero</t>
+  </si>
+  <si>
+    <t>Henning Berg</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Manchester United</t>
+  </si>
+  <si>
+    <t>Steve McManaman</t>
+  </si>
+  <si>
+    <t>Mikaël Silvestre</t>
+  </si>
+  <si>
+    <t>Harry Kewell</t>
+  </si>
+  <si>
+    <t>Chris Powell</t>
+  </si>
+  <si>
+    <t>Leicester City;Charlton Athletic</t>
+  </si>
+  <si>
+    <t>Eric Dier</t>
+  </si>
+  <si>
+    <t>Branislav Ivanovic</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion;Chelsea</t>
+  </si>
+  <si>
+    <t>Jason Wilcox</t>
+  </si>
+  <si>
+    <t>Leicester City;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Kanu</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>James McCarthy</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Everton;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Chris Wood</t>
+  </si>
+  <si>
+    <t>Lee Cattermole</t>
+  </si>
+  <si>
+    <t>Richarlison</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Everton</t>
+  </si>
+  <si>
+    <t>Matthew Le Tissier</t>
+  </si>
+  <si>
+    <t>Adama Traoré</t>
+  </si>
+  <si>
+    <t>West Ham United;Fulham</t>
+  </si>
+  <si>
+    <t>Joey Barton</t>
+  </si>
+  <si>
+    <t>Chris Brunt</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Duncan Ferguson</t>
+  </si>
+  <si>
+    <t>Michail Antonio</t>
+  </si>
+  <si>
+    <t>Dominic Calvert-Lewin</t>
+  </si>
+  <si>
+    <t>Leeds United;Everton</t>
+  </si>
+  <si>
+    <t>Dietmar Hamann</t>
+  </si>
+  <si>
+    <t>Ledley King</t>
+  </si>
+  <si>
+    <t>Bacary Sagna</t>
+  </si>
+  <si>
+    <t>Colin Cooper</t>
+  </si>
+  <si>
+    <t>Nottingham Forest;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Robert Green</t>
+  </si>
+  <si>
+    <t>David Batty</t>
+  </si>
+  <si>
+    <t>Leeds United;Blackburn Rovers;Newcastle United</t>
+  </si>
+  <si>
+    <t>David Beckham</t>
+  </si>
+  <si>
+    <t>Tony Hibbert</t>
+  </si>
+  <si>
+    <t>Adam Johnson</t>
+  </si>
+  <si>
+    <t>Middlesbrough;Manchester City;Sunderland</t>
+  </si>
+  <si>
+    <t>Vincent Kompany</t>
+  </si>
+  <si>
+    <t>Kieran Richardson</t>
+  </si>
+  <si>
+    <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
+  </si>
+  <si>
+    <t>Darius Vassell</t>
+  </si>
+  <si>
+    <t>Callum Wilson</t>
+  </si>
+  <si>
+    <t>Des Walker</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday</t>
+  </si>
+  <si>
+    <t>Fernandinho</t>
+  </si>
+  <si>
+    <t>Jason Euell</t>
+  </si>
+  <si>
+    <t>Wimbledon;Charlton Athletic;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Sadio Mané</t>
+  </si>
+  <si>
+    <t>Kevin Phillips</t>
+  </si>
+  <si>
+    <t>Sunderland;Southampton;Aston Villa;West Bromwich Albion;Birmingham City;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Steve Stone</t>
+  </si>
+  <si>
+    <t>Nottingham Forest;Aston Villa;Leicester City;Portsmouth</t>
+  </si>
+  <si>
+    <t>Ryan Bertrand</t>
+  </si>
+  <si>
+    <t>Aaron Ramsey</t>
+  </si>
+  <si>
+    <t>Cardiff City;Arsenal</t>
+  </si>
+  <si>
+    <t>Gary Pallister</t>
+  </si>
+  <si>
+    <t>Carlton Palmer</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday;Leeds United;Coventry City;Southampton</t>
+  </si>
+  <si>
+    <t>Craig Gardner</t>
+  </si>
+  <si>
+    <t>Aston Villa;Birmingham City;Sunderland;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Marouane Fellaini</t>
+  </si>
+  <si>
+    <t>Trent Alexander-Arnold</t>
+  </si>
+  <si>
+    <t>Morten Pedersen</t>
+  </si>
+  <si>
+    <t>Thierry Henry</t>
+  </si>
+  <si>
+    <t>Jay Rodriguez</t>
+  </si>
+  <si>
+    <t>Burnley;Southampton;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Liam Ridgewell</t>
+  </si>
+  <si>
+    <t>Aston Villa;Birmingham City;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>David Wetherall</t>
+  </si>
+  <si>
+    <t>Roberto Firmino</t>
+  </si>
+  <si>
+    <t>Asmir Begovic</t>
+  </si>
+  <si>
+    <t>Olivier Giroud</t>
+  </si>
+  <si>
+    <t>Laurent Koscielny</t>
+  </si>
+  <si>
+    <t>John Stones</t>
+  </si>
+  <si>
+    <t>Everton;Manchester City</t>
+  </si>
+  <si>
+    <t>Chris Sutton</t>
+  </si>
+  <si>
+    <t>Norwich City;Blackburn Rovers;Chelsea;Birmingham City;Aston Villa</t>
+  </si>
+  <si>
+    <t>Tony Adams</t>
+  </si>
+  <si>
+    <t>Alisson Becker</t>
+  </si>
+  <si>
+    <t>Didier Drogba</t>
+  </si>
+  <si>
+    <t>Pierre-Emile Højbjerg</t>
+  </si>
+  <si>
+    <t>Southampton;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Adam Smith</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Granit Xhaka</t>
+  </si>
+  <si>
+    <t>Sunderland;Arsenal</t>
+  </si>
+  <si>
+    <t>Richard Shaw</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Coventry City</t>
+  </si>
+  <si>
+    <t>Jonathan Greening</t>
+  </si>
+  <si>
+    <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
+  </si>
+  <si>
+    <t>Idrissa Gueye</t>
+  </si>
+  <si>
+    <t>Bobby Zamora</t>
+  </si>
+  <si>
+    <t>Yakubu</t>
+  </si>
+  <si>
+    <t>Coventry City</t>
+  </si>
+  <si>
+    <t>Lee Hendrie</t>
+  </si>
+  <si>
+    <t>Nemanja Matic</t>
+  </si>
+  <si>
+    <t>Matt Oakley</t>
+  </si>
+  <si>
+    <t>Ricardo Gardner</t>
+  </si>
+  <si>
+    <t>Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>David Dunn</t>
+  </si>
+  <si>
+    <t>Niall Quinn</t>
+  </si>
+  <si>
+    <t>Coventry City;Arsenal;Manchester City;Sunderland</t>
+  </si>
+  <si>
+    <t>Nathan Aké</t>
+  </si>
+  <si>
+    <t>Manchester City;Bournemouth</t>
+  </si>
+  <si>
+    <t>Lucas Digne</t>
+  </si>
+  <si>
+    <t>Aston Villa;Everton</t>
+  </si>
+  <si>
+    <t>John Obi Mikel</t>
+  </si>
+  <si>
+    <t>Stoke City;Chelsea</t>
+  </si>
+  <si>
+    <t>Andy Carroll</t>
+  </si>
+  <si>
+    <t>Newcastle United;Liverpool;West Ham United</t>
+  </si>
+  <si>
+    <t>Muzzy Izzet</t>
+  </si>
+  <si>
+    <t>Ian Taylor</t>
+  </si>
+  <si>
+    <t>Derby County;Aston Villa</t>
+  </si>
+  <si>
+    <t>Kurt Zouma</t>
+  </si>
+  <si>
+    <t>Chelsea;Stoke City;Everton;West Ham United</t>
+  </si>
+  <si>
+    <t>Lucas Leiva</t>
+  </si>
+  <si>
+    <t>Neil Sullivan</t>
+  </si>
+  <si>
+    <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
+  </si>
+  <si>
+    <t>Brett Emerton</t>
+  </si>
+  <si>
+    <t>Eden Hazard</t>
+  </si>
+  <si>
+    <t>Bernd Leno</t>
+  </si>
+  <si>
+    <t>Fulham;Arsenal</t>
+  </si>
+  <si>
+    <t>Dwight McNeil</t>
+  </si>
+  <si>
+    <t>Simon Mignolet</t>
+  </si>
+  <si>
     <t>Sunderland;Liverpool</t>
-  </si>
-  <si>
-    <t>Aaron Hughes</t>
-  </si>
-  <si>
-    <t>Newcastle United;Aston Villa;Fulham;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Brad Friedel</t>
-  </si>
-  <si>
-    <t>Liverpool;Blackburn Rovers;Aston Villa;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Shay Given</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Newcastle United;Manchester City;Aston Villa;Stoke City</t>
-  </si>
-  <si>
-    <t>John O'Shea</t>
-  </si>
-  <si>
-    <t>Manchester United;Sunderland</t>
-  </si>
-  <si>
-    <t>Kevin Davies</t>
-  </si>
-  <si>
-    <t>Southampton;Blackburn Rovers;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Petr Cech</t>
-  </si>
-  <si>
-    <t>Chelsea;Arsenal</t>
-  </si>
-  <si>
-    <t>Alan Shearer</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Newcastle United</t>
-  </si>
-  <si>
-    <t>Kyle Walker</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Aston Villa;Manchester City</t>
-  </si>
-  <si>
-    <t>Jussi Jääskeläinen</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers;West Ham United</t>
-  </si>
-  <si>
-    <t>Richard Dunne</t>
-  </si>
-  <si>
-    <t>Everton;Manchester City;Aston Villa;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Gareth Southgate</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Aston Villa;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Leighton Baines</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Everton</t>
-  </si>
-  <si>
-    <t>Teddy Sheringham</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Manchester United;Portsmouth;West Ham United</t>
-  </si>
-  <si>
-    <t>Danny Murphy</t>
-  </si>
-  <si>
-    <t>Liverpool;Charlton Athletic;Tottenham Hotspur;Fulham;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Aaron Lennon</t>
-  </si>
-  <si>
-    <t>Leeds United;Tottenham Hotspur;Everton;Burnley</t>
-  </si>
-  <si>
-    <t>James Ward-Prowse</t>
-  </si>
-  <si>
-    <t>Southampton;West Ham United</t>
-  </si>
-  <si>
-    <t>David de Gea</t>
-  </si>
-  <si>
-    <t>Mark Noble</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
-    <t>Andrew Cole</t>
-  </si>
-  <si>
-    <t>Newcastle United;Manchester United;Blackburn Rovers;Fulham;Manchester City;Portsmouth;Sunderland</t>
-  </si>
-  <si>
-    <t>Nicky Butt</t>
-  </si>
-  <si>
-    <t>Manchester United;Newcastle United</t>
-  </si>
-  <si>
-    <t>Stewart Downing</t>
-  </si>
-  <si>
-    <t>Middlesbrough;Aston Villa;Liverpool;West Ham United</t>
-  </si>
-  <si>
-    <t>Kevin Nolan</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers;Newcastle United;West Ham United</t>
-  </si>
-  <si>
-    <t>Gary Neville</t>
-  </si>
-  <si>
-    <t>Tim Howard</t>
-  </si>
-  <si>
-    <t>Lee Bowyer</t>
-  </si>
-  <si>
-    <t>Leeds United;West Ham United;Newcastle United;Birmingham City</t>
-  </si>
-  <si>
-    <t>Theo Walcott</t>
-  </si>
-  <si>
-    <t>Arsenal;Everton;Southampton</t>
-  </si>
-  <si>
-    <t>Raheem Sterling</t>
-  </si>
-  <si>
-    <t>Liverpool;Manchester City;Chelsea;Arsenal</t>
-  </si>
-  <si>
-    <t>Danny Welbeck</t>
-  </si>
-  <si>
-    <t>Manchester United;Arsenal;Watford;Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Gary Cahill</t>
-  </si>
-  <si>
-    <t>Aston Villa;Bolton Wanderers;Chelsea;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Damien Duff</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Chelsea;Newcastle United;Fulham</t>
-  </si>
-  <si>
-    <t>Ben Foster</t>
-  </si>
-  <si>
-    <t>Manchester United;Watford;Birmingham City;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Jonny Evans</t>
-  </si>
-  <si>
-    <t>Manchester United;West Bromwich Albion;Leicester City</t>
-  </si>
-  <si>
-    <t>Ashley Cole</t>
-  </si>
-  <si>
-    <t>Arsenal;Chelsea</t>
-  </si>
-  <si>
-    <t>George Boateng</t>
-  </si>
-  <si>
-    <t>Coventry City;Aston Villa;Middlesbrough;Hull City</t>
-  </si>
-  <si>
-    <t>Robbie Fowler</t>
-  </si>
-  <si>
-    <t>Liverpool;Leeds United;Manchester City;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Ray Parlour</t>
-  </si>
-  <si>
-    <t>Arsenal;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Luke Young</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Charlton Athletic;Middlesbrough;Aston Villa</t>
-  </si>
-  <si>
-    <t>Joe Cole</t>
-  </si>
-  <si>
-    <t>West Ham United;Chelsea;Liverpool;Aston Villa</t>
-  </si>
-  <si>
-    <t>Stephen Carr</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Newcastle United;Birmingham City</t>
-  </si>
-  <si>
-    <t>Lukasz Fabianski</t>
-  </si>
-  <si>
-    <t>Arsenal;Swansea City;West Ham United</t>
-  </si>
-  <si>
-    <t>Phil Jagielka</t>
-  </si>
-  <si>
-    <t>Sheffield United;Everton</t>
-  </si>
-  <si>
-    <t>Dwight Yorke</t>
-  </si>
-  <si>
-    <t>Aston Villa;Manchester United;Blackburn Rovers;Birmingham City;Sunderland</t>
-  </si>
-  <si>
-    <t>Paul Robinson</t>
-  </si>
-  <si>
-    <t>Leeds United;Tottenham Hotspur;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Séamus Coleman</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Nigel Martyn</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Leeds United;Everton</t>
-  </si>
-  <si>
-    <t>Scott Parker</t>
-  </si>
-  <si>
-    <t>Charlton Athletic;Chelsea;Newcastle United;West Ham United;Tottenham Hotspur;Fulham</t>
-  </si>
-  <si>
-    <t>Roy Keane</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Manchester United</t>
-  </si>
-  <si>
-    <t>Nicolas Anelka</t>
-  </si>
-  <si>
-    <t>Arsenal;Liverpool;Manchester City;Bolton Wanderers;Chelsea;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>David Unsworth</t>
-  </si>
-  <si>
-    <t>Everton;West Ham United;Aston Villa;Portsmouth;Wigan Athletic;Sheffield United</t>
-  </si>
-  <si>
-    <t>Chris Perry</t>
-  </si>
-  <si>
-    <t>Wimbledon;Tottenham Hotspur;Charlton Athletic;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Thomas Sørensen</t>
-  </si>
-  <si>
-    <t>Sunderland;Aston Villa;Stoke City</t>
-  </si>
-  <si>
-    <t>Hugo Lloris</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Trevor Sinclair</t>
-  </si>
-  <si>
-    <t>Queens Park Rangers;West Ham United;Manchester City</t>
-  </si>
-  <si>
-    <t>Rory Delap</t>
-  </si>
-  <si>
-    <t>Derby County;Southampton;Sunderland;Stoke City</t>
-  </si>
-  <si>
-    <t>Glen Johnson</t>
-  </si>
-  <si>
-    <t>West Ham United;Chelsea;Portsmouth;Liverpool;Stoke City</t>
-  </si>
-  <si>
-    <t>Jordan Pickford</t>
-  </si>
-  <si>
-    <t>Sunderland;Everton</t>
-  </si>
-  <si>
-    <t>Ugo Ehiogu</t>
-  </si>
-  <si>
-    <t>Aston Villa;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Leon Osman</t>
-  </si>
-  <si>
-    <t>Kolo Touré</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester City;Liverpool</t>
-  </si>
-  <si>
-    <t>Nigel Winterburn</t>
-  </si>
-  <si>
-    <t>Arsenal;West Ham United;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Les Ferdinand</t>
-  </si>
-  <si>
-    <t>Queens Park Rangers;Newcastle United;Tottenham Hotspur;West Ham United;Leicester City;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Steve Watson</t>
-  </si>
-  <si>
-    <t>Newcastle United;Aston Villa;Everton;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Cesc Fàbregas</t>
-  </si>
-  <si>
-    <t>César Azpilicueta</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Robbie Keane</t>
-  </si>
-  <si>
-    <t>Coventry City;Leeds United;Tottenham Hotspur;Liverpool;West Ham United;Aston Villa</t>
-  </si>
-  <si>
-    <t>Paul Konchesky</t>
-  </si>
-  <si>
-    <t>Charlton Athletic;West Ham United;Fulham;Liverpool</t>
-  </si>
-  <si>
-    <t>Robbie Savage</t>
-  </si>
-  <si>
-    <t>Leicester City;Birmingham City;Blackburn Rovers;Derby County</t>
-  </si>
-  <si>
-    <t>Shane Long</t>
-  </si>
-  <si>
-    <t>Reading;West Bromwich Albion;Hull City;Southampton</t>
-  </si>
-  <si>
-    <t>David Seaman</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester City</t>
-  </si>
-  <si>
-    <t>Nick Barmby</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Middlesbrough;Everton;Liverpool;Leeds United</t>
-  </si>
-  <si>
-    <t>Jamie Vardy</t>
-  </si>
-  <si>
-    <t>Leicester City</t>
-  </si>
-  <si>
-    <t>Darren Fletcher</t>
-  </si>
-  <si>
-    <t>Manchester United;West Bromwich Albion;Stoke City</t>
-  </si>
-  <si>
-    <t>Tim Sherwood</t>
-  </si>
-  <si>
-    <t>Norwich City;Blackburn Rovers;Tottenham Hotspur;Portsmouth;Coventry City</t>
-  </si>
-  <si>
-    <t>Joe Hart</t>
-  </si>
-  <si>
-    <t>Manchester City;Birmingham City;West Ham United;Burnley</t>
-  </si>
-  <si>
-    <t>Steed Malbranque</t>
-  </si>
-  <si>
-    <t>Fulham;Tottenham Hotspur;Sunderland</t>
-  </si>
-  <si>
-    <t>Kenny Cunningham</t>
-  </si>
-  <si>
-    <t>Wimbledon;Birmingham City;Sunderland</t>
-  </si>
-  <si>
-    <t>James Tarkowski</t>
-  </si>
-  <si>
-    <t>Burnley;Everton</t>
-  </si>
-  <si>
-    <t>Son Heung-Min</t>
-  </si>
-  <si>
-    <t>Virgil van Dijk</t>
-  </si>
-  <si>
-    <t>Southampton;Liverpool</t>
-  </si>
-  <si>
-    <t>Hermann Hreidarsson</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Wimbledon;Ipswich Town;Charlton Athletic;Portsmouth</t>
-  </si>
-  <si>
-    <t>James Beattie</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Southampton;Everton;Stoke City</t>
-  </si>
-  <si>
-    <t>Jason Dodd</t>
-  </si>
-  <si>
-    <t>Southampton</t>
-  </si>
-  <si>
-    <t>Denis Irwin</t>
-  </si>
-  <si>
-    <t>Andy Robertson</t>
-  </si>
-  <si>
-    <t>Hull City;Liverpool</t>
-  </si>
-  <si>
-    <t>Willian</t>
-  </si>
-  <si>
-    <t>Chelsea;Arsenal;Fulham</t>
-  </si>
-  <si>
-    <t>Graeme Le Saux</t>
-  </si>
-  <si>
-    <t>Chelsea;Blackburn Rovers;Southampton</t>
-  </si>
-  <si>
-    <t>Michael Owen</t>
-  </si>
-  <si>
-    <t>Liverpool;Newcastle United;Manchester United;Stoke City</t>
-  </si>
-  <si>
-    <t>Kevin Campbell</t>
-  </si>
-  <si>
-    <t>Arsenal;Nottingham Forest;Everton</t>
-  </si>
-  <si>
-    <t>Gaël Clichy</t>
-  </si>
-  <si>
-    <t>Gary Kelly</t>
-  </si>
-  <si>
-    <t>Leeds United</t>
-  </si>
-  <si>
-    <t>Kevin Kilbane</t>
-  </si>
-  <si>
-    <t>Coventry City;Everton;Sunderland;Wigan Athletic;Hull City</t>
-  </si>
-  <si>
-    <t>Gary McAllister</t>
-  </si>
-  <si>
-    <t>Coventry City;Liverpool</t>
-  </si>
-  <si>
-    <t>Matthew Taylor</t>
-  </si>
-  <si>
-    <t>Portsmouth;Bolton Wanderers;West Ham United;Burnley</t>
-  </si>
-  <si>
-    <t>Antonio Valencia</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Manchester United</t>
-  </si>
-  <si>
-    <t>Mohamed Salah</t>
-  </si>
-  <si>
-    <t>Chelsea;Liverpool</t>
-  </si>
-  <si>
-    <t>James McArthur</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Martin Keown</t>
-  </si>
-  <si>
-    <t>Everton;Arsenal;Aston Villa</t>
-  </si>
-  <si>
-    <t>Gabriel Agbonlahor</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Robert Huth</t>
-  </si>
-  <si>
-    <t>Chelsea;Middlesbrough;Stoke City;Leicester City</t>
-  </si>
-  <si>
-    <t>William Gallas</t>
-  </si>
-  <si>
-    <t>Chelsea;Arsenal;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>John Arne Riise</t>
-  </si>
-  <si>
-    <t>Liverpool;Fulham</t>
-  </si>
-  <si>
-    <t>Harry Kane</t>
-  </si>
-  <si>
-    <t>Darren Anderton</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Birmingham City;Portsmouth</t>
-  </si>
-  <si>
-    <t>Paul Telfer</t>
-  </si>
-  <si>
-    <t>Coventry City;Southampton</t>
-  </si>
-  <si>
-    <t>Gylfi Sigurdsson</t>
-  </si>
-  <si>
-    <t>Swansea City;Tottenham Hotspur;Everton</t>
-  </si>
-  <si>
-    <t>Sami Hyypiä</t>
-  </si>
-  <si>
-    <t>Peter Atherton</t>
-  </si>
-  <si>
-    <t>Coventry City;Sheffield Wednesday;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Alex Iwobi</t>
-  </si>
-  <si>
-    <t>Arsenal;Everton;Fulham</t>
-  </si>
-  <si>
-    <t>Ben Davies</t>
-  </si>
-  <si>
-    <t>Swansea City;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Ryan Shawcross</t>
-  </si>
-  <si>
-    <t>Manchester United;Stoke City</t>
-  </si>
-  <si>
-    <t>Dennis Bergkamp</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Wayne Bridge</t>
-  </si>
-  <si>
-    <t>Southampton;Chelsea;Fulham;Manchester City;Sunderland</t>
-  </si>
-  <si>
-    <t>Shaun Wright-Phillips</t>
-  </si>
-  <si>
-    <t>Manchester City;Chelsea;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Edwin van der Sar</t>
-  </si>
-  <si>
-    <t>Fulham;Manchester United</t>
-  </si>
-  <si>
-    <t>Ian Walker</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Leicester City;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Dion Dublin</t>
-  </si>
-  <si>
-    <t>Manchester United;Coventry City;Aston Villa;Leicester City</t>
-  </si>
-  <si>
-    <t>Aaron Cresswell</t>
-  </si>
-  <si>
-    <t>James Morrison</t>
-  </si>
-  <si>
-    <t>Middlesbrough;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Marc Albrighton</t>
-  </si>
-  <si>
-    <t>Aston Villa;Leicester City</t>
-  </si>
-  <si>
-    <t>Christian Eriksen</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Brentford;Manchester United</t>
-  </si>
-  <si>
-    <t>Peter Schmeichel</t>
-  </si>
-  <si>
-    <t>Manchester United;Aston Villa;Manchester City</t>
-  </si>
-  <si>
-    <t>David Silva</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Joel Ward</t>
-  </si>
-  <si>
-    <t>Portsmouth;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Wes Brown</t>
-  </si>
-  <si>
-    <t>Declan Rice</t>
-  </si>
-  <si>
-    <t>Arsenal;West Ham United</t>
-  </si>
-  <si>
-    <t>Patrick Vieira</t>
-  </si>
-  <si>
-    <t>Steven Davis</t>
-  </si>
-  <si>
-    <t>Aston Villa;Southampton</t>
-  </si>
-  <si>
-    <t>Paul Ince</t>
-  </si>
-  <si>
-    <t>Manchester United;Liverpool;Middlesbrough;Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Jordan Ayew</t>
-  </si>
-  <si>
-    <t>Aston Villa;Swansea City;Crystal Palace;Leicester City</t>
-  </si>
-  <si>
-    <t>Lee Dixon</t>
-  </si>
-  <si>
-    <t>Adam Lallana</t>
-  </si>
-  <si>
-    <t>Alan Wright</t>
-  </si>
-  <si>
-    <t>Wilfried Zaha</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Jack Cork</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Craig Dawson</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion;Watford;West Ham United;Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Phil Bardsley</t>
-  </si>
-  <si>
-    <t>Manchester United;Sunderland;Stoke City;Burnley</t>
-  </si>
-  <si>
-    <t>Simon Davies</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Nolberto Solano</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Pablo Zabaleta</t>
-  </si>
-  <si>
-    <t>West Ham United;Manchester City</t>
-  </si>
-  <si>
-    <t>Garry Flitcroft</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Gavin McCann</t>
-  </si>
-  <si>
-    <t>Everton;Sunderland;Aston Villa;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Ross Barkley</t>
-  </si>
-  <si>
-    <t>Aston Villa;Chelsea</t>
-  </si>
-  <si>
-    <t>Shola Ameobi</t>
-  </si>
-  <si>
-    <t>Wayne Routledge</t>
-  </si>
-  <si>
-    <t>Swansea City</t>
-  </si>
-  <si>
-    <t>Pepe Reina</t>
-  </si>
-  <si>
-    <t>Liverpool;Aston Villa</t>
-  </si>
-  <si>
-    <t>Marcus Rashford</t>
-  </si>
-  <si>
-    <t>Bernardo Silva</t>
-  </si>
-  <si>
-    <t>Mark Hughes</t>
-  </si>
-  <si>
-    <t>Manchester United;Chelsea;Southampton;Everton;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Luís Boa Morte</t>
-  </si>
-  <si>
-    <t>Arsenal;Southampton;Fulham;West Ham United</t>
-  </si>
-  <si>
-    <t>Lewis Dunk</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Jamie Redknapp</t>
-  </si>
-  <si>
-    <t>Moussa Sissoko</t>
-  </si>
-  <si>
-    <t>Newcastle United;Tottenham Hotspur;Watford</t>
-  </si>
-  <si>
-    <t>Graham Stuart</t>
-  </si>
-  <si>
-    <t>Everton;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Craig Bellamy</t>
-  </si>
-  <si>
-    <t>Coventry City;Newcastle United;Blackburn Rovers;Liverpool;West Ham United;Manchester City;Cardiff City</t>
-  </si>
-  <si>
-    <t>Titus Bramble</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Cheikhou Kouyaté</t>
-  </si>
-  <si>
-    <t>West Ham United;Crystal Palace;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Andros Townsend</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Queens Park Rangers;Newcastle United;Crystal Palace;Everton;Luton Town</t>
-  </si>
-  <si>
-    <t>Jeff Kenna</t>
-  </si>
-  <si>
-    <t>Derby County</t>
-  </si>
-  <si>
-    <t>Claus Lundekvam</t>
-  </si>
-  <si>
-    <t>Luke Shaw</t>
-  </si>
-  <si>
-    <t>Manchester United;Southampton</t>
-  </si>
-  <si>
-    <t>Andy Impey</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Louis Saha</t>
-  </si>
-  <si>
-    <t>Newcastle United;Fulham;Manchester United;Everton;Tottenham Hotspur;Sunderland</t>
-  </si>
-  <si>
-    <t>James Tomkins</t>
-  </si>
-  <si>
-    <t>West Ham United;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Frank Sinclair</t>
-  </si>
-  <si>
-    <t>Chelsea;Leicester City</t>
-  </si>
-  <si>
-    <t>Matt Upson</t>
-  </si>
-  <si>
-    <t>Arsenal;Birmingham City;West Ham United;Stoke City;Leicester City</t>
-  </si>
-  <si>
-    <t>Steve Staunton</t>
-  </si>
-  <si>
-    <t>Coventry City;Aston Villa</t>
-  </si>
-  <si>
-    <t>Kevin De Bruyne</t>
-  </si>
-  <si>
-    <t>Chelsea;Manchester City</t>
-  </si>
-  <si>
-    <t>Jimmy Floyd Hasselbaink</t>
-  </si>
-  <si>
-    <t>Leeds United;Chelsea;Middlesbrough;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Matthew Etherington</t>
-  </si>
-  <si>
-    <t>Stoke City</t>
-  </si>
-  <si>
-    <t>Carlton Cole</t>
-  </si>
-  <si>
-    <t>Joleon Lescott</t>
-  </si>
-  <si>
-    <t>Everton;Manchester City;West Bromwich Albion;Aston Villa;Sunderland</t>
-  </si>
-  <si>
-    <t>Tim Flowers</t>
-  </si>
-  <si>
-    <t>Southampton;Blackburn Rovers;Leicester City</t>
-  </si>
-  <si>
-    <t>Harry Maguire</t>
-  </si>
-  <si>
-    <t>Ashley Westwood</t>
-  </si>
-  <si>
-    <t>Aston Villa;Burnley</t>
-  </si>
-  <si>
-    <t>Brian Deane</t>
-  </si>
-  <si>
-    <t>Michael Dawson</t>
-  </si>
-  <si>
-    <t>Hull City;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Alan Smith</t>
-  </si>
-  <si>
-    <t>Leeds United;Manchester United;Newcastle United</t>
-  </si>
-  <si>
-    <t>Mikel Arteta</t>
-  </si>
-  <si>
-    <t>Everton;Arsenal</t>
-  </si>
-  <si>
-    <t>Zat Knight</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Riyad Mahrez</t>
-  </si>
-  <si>
-    <t>Leicester City;Manchester City</t>
-  </si>
-  <si>
-    <t>Mario Melchiot</t>
-  </si>
-  <si>
-    <t>Chelsea;Birmingham City;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Kasper Schmeichel</t>
-  </si>
-  <si>
-    <t>Lee Carsley</t>
-  </si>
-  <si>
-    <t>Derby County;Blackburn Rovers;Coventry City;Everton;Birmingham City</t>
-  </si>
-  <si>
-    <t>Sebastian Larsson</t>
-  </si>
-  <si>
-    <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
-  </si>
-  <si>
-    <t>Charles N'Zogbia</t>
-  </si>
-  <si>
-    <t>Paul Merson</t>
-  </si>
-  <si>
-    <t>Arsenal;Middlesbrough;Aston Villa;Portsmouth</t>
-  </si>
-  <si>
-    <t>Robin van Persie</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester United</t>
-  </si>
-  <si>
-    <t>Jeffrey Schlupp</t>
-  </si>
-  <si>
-    <t>Norwich City;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Andy O'Brien</t>
-  </si>
-  <si>
-    <t>Christian Benteke</t>
-  </si>
-  <si>
-    <t>Aston Villa;Liverpool;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Robert Lee</t>
-  </si>
-  <si>
-    <t>Michael Keane</t>
-  </si>
-  <si>
-    <t>Everton;Burnley</t>
-  </si>
-  <si>
-    <t>Jermaine Jenas</t>
-  </si>
-  <si>
-    <t>Newcastle United;Tottenham Hotspur;Aston Villa;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Lucas Neill</t>
-  </si>
-  <si>
-    <t>Juan Mata</t>
-  </si>
-  <si>
-    <t>Chelsea;Manchester United</t>
-  </si>
-  <si>
-    <t>Dennis Wise</t>
-  </si>
-  <si>
-    <t>Jonjo Shelvey</t>
-  </si>
-  <si>
-    <t>Liverpool;Swansea City;Newcastle United;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>James Collins</t>
-  </si>
-  <si>
-    <t>Ipswich Town;West Ham United</t>
-  </si>
-  <si>
-    <t>Romelu Lukaku</t>
-  </si>
-  <si>
-    <t>Chelsea;West Bromwich Albion;Everton;Manchester United</t>
-  </si>
-  <si>
-    <t>Patrice Evra</t>
-  </si>
-  <si>
-    <t>Abdoulaye Doucouré</t>
-  </si>
-  <si>
-    <t>Watford;Everton</t>
-  </si>
-  <si>
-    <t>Warren Barton</t>
-  </si>
-  <si>
-    <t>Wimbledon;Newcastle United;Derby County</t>
-  </si>
-  <si>
-    <t>Ben Mee</t>
-  </si>
-  <si>
-    <t>Sheffield United;Burnley</t>
-  </si>
-  <si>
-    <t>Glenn Whelan</t>
-  </si>
-  <si>
-    <t>Ederson</t>
-  </si>
-  <si>
-    <t>Nathan Redmond</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Southampton</t>
-  </si>
-  <si>
-    <t>Dominic Matteo</t>
-  </si>
-  <si>
-    <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
-  </si>
-  <si>
-    <t>Nathaniel Clyne</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Liverpool</t>
-  </si>
-  <si>
-    <t>Darren Bent</t>
-  </si>
-  <si>
-    <t>Ipswich Town;Charlton Athletic;Tottenham Hotspur;Sunderland;Aston Villa;Fulham</t>
-  </si>
-  <si>
-    <t>Sergio Agüero</t>
-  </si>
-  <si>
-    <t>Henning Berg</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Manchester United</t>
-  </si>
-  <si>
-    <t>Steve McManaman</t>
-  </si>
-  <si>
-    <t>Mikaël Silvestre</t>
-  </si>
-  <si>
-    <t>Harry Kewell</t>
-  </si>
-  <si>
-    <t>Chris Powell</t>
-  </si>
-  <si>
-    <t>Leicester City;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Eric Dier</t>
-  </si>
-  <si>
-    <t>Branislav Ivanovic</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion;Chelsea</t>
-  </si>
-  <si>
-    <t>Jason Wilcox</t>
-  </si>
-  <si>
-    <t>Leicester City;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Kanu</t>
-  </si>
-  <si>
-    <t>Portsmouth</t>
-  </si>
-  <si>
-    <t>James McCarthy</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Everton;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Chris Wood</t>
-  </si>
-  <si>
-    <t>Lee Cattermole</t>
-  </si>
-  <si>
-    <t>Richarlison</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Everton</t>
-  </si>
-  <si>
-    <t>Matthew Le Tissier</t>
-  </si>
-  <si>
-    <t>Adama Traoré</t>
-  </si>
-  <si>
-    <t>West Ham United;Fulham</t>
-  </si>
-  <si>
-    <t>Joey Barton</t>
-  </si>
-  <si>
-    <t>Chris Brunt</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Duncan Ferguson</t>
-  </si>
-  <si>
-    <t>Michail Antonio</t>
-  </si>
-  <si>
-    <t>Dominic Calvert-Lewin</t>
-  </si>
-  <si>
-    <t>Leeds United;Everton</t>
-  </si>
-  <si>
-    <t>Dietmar Hamann</t>
-  </si>
-  <si>
-    <t>Ledley King</t>
-  </si>
-  <si>
-    <t>Bacary Sagna</t>
-  </si>
-  <si>
-    <t>Colin Cooper</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Robert Green</t>
-  </si>
-  <si>
-    <t>David Batty</t>
-  </si>
-  <si>
-    <t>Leeds United;Blackburn Rovers;Newcastle United</t>
-  </si>
-  <si>
-    <t>David Beckham</t>
-  </si>
-  <si>
-    <t>Tony Hibbert</t>
-  </si>
-  <si>
-    <t>Adam Johnson</t>
-  </si>
-  <si>
-    <t>Middlesbrough;Manchester City;Sunderland</t>
-  </si>
-  <si>
-    <t>Vincent Kompany</t>
-  </si>
-  <si>
-    <t>Kieran Richardson</t>
-  </si>
-  <si>
-    <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
-  </si>
-  <si>
-    <t>Darius Vassell</t>
-  </si>
-  <si>
-    <t>Callum Wilson</t>
-  </si>
-  <si>
-    <t>Des Walker</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Fernandinho</t>
-  </si>
-  <si>
-    <t>Jason Euell</t>
-  </si>
-  <si>
-    <t>Wimbledon;Charlton Athletic;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Sadio Mané</t>
-  </si>
-  <si>
-    <t>Kevin Phillips</t>
-  </si>
-  <si>
-    <t>Sunderland;Southampton;Aston Villa;West Bromwich Albion;Birmingham City;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Steve Stone</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Aston Villa;Leicester City;Portsmouth</t>
-  </si>
-  <si>
-    <t>Ryan Bertrand</t>
-  </si>
-  <si>
-    <t>Aaron Ramsey</t>
-  </si>
-  <si>
-    <t>Cardiff City;Arsenal</t>
-  </si>
-  <si>
-    <t>Gary Pallister</t>
-  </si>
-  <si>
-    <t>Carlton Palmer</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Leeds United;Coventry City;Southampton</t>
-  </si>
-  <si>
-    <t>Craig Gardner</t>
-  </si>
-  <si>
-    <t>Aston Villa;Birmingham City;Sunderland;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Marouane Fellaini</t>
-  </si>
-  <si>
-    <t>Trent Alexander-Arnold</t>
-  </si>
-  <si>
-    <t>Morten Pedersen</t>
-  </si>
-  <si>
-    <t>Thierry Henry</t>
-  </si>
-  <si>
-    <t>Jay Rodriguez</t>
-  </si>
-  <si>
-    <t>Burnley;Southampton;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Liam Ridgewell</t>
-  </si>
-  <si>
-    <t>Aston Villa;Birmingham City;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>David Wetherall</t>
-  </si>
-  <si>
-    <t>Roberto Firmino</t>
-  </si>
-  <si>
-    <t>Asmir Begovic</t>
-  </si>
-  <si>
-    <t>Olivier Giroud</t>
-  </si>
-  <si>
-    <t>Laurent Koscielny</t>
-  </si>
-  <si>
-    <t>John Stones</t>
-  </si>
-  <si>
-    <t>Everton;Manchester City</t>
-  </si>
-  <si>
-    <t>Chris Sutton</t>
-  </si>
-  <si>
-    <t>Norwich City;Blackburn Rovers;Chelsea;Birmingham City;Aston Villa</t>
-  </si>
-  <si>
-    <t>Tony Adams</t>
-  </si>
-  <si>
-    <t>Alisson Becker</t>
-  </si>
-  <si>
-    <t>Didier Drogba</t>
-  </si>
-  <si>
-    <t>Pierre-Emile Højbjerg</t>
-  </si>
-  <si>
-    <t>Southampton;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Adam Smith</t>
-  </si>
-  <si>
-    <t>Bournemouth</t>
-  </si>
-  <si>
-    <t>Granit Xhaka</t>
-  </si>
-  <si>
-    <t>Sunderland;Arsenal</t>
-  </si>
-  <si>
-    <t>Richard Shaw</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Coventry City</t>
-  </si>
-  <si>
-    <t>Jonathan Greening</t>
-  </si>
-  <si>
-    <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
-  </si>
-  <si>
-    <t>Idrissa Gueye</t>
-  </si>
-  <si>
-    <t>Bobby Zamora</t>
-  </si>
-  <si>
-    <t>Yakubu</t>
-  </si>
-  <si>
-    <t>Coventry City</t>
-  </si>
-  <si>
-    <t>Lee Hendrie</t>
-  </si>
-  <si>
-    <t>Nemanja Matic</t>
-  </si>
-  <si>
-    <t>Matt Oakley</t>
-  </si>
-  <si>
-    <t>Ricardo Gardner</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>David Dunn</t>
-  </si>
-  <si>
-    <t>Niall Quinn</t>
-  </si>
-  <si>
-    <t>Coventry City;Arsenal;Manchester City;Sunderland</t>
-  </si>
-  <si>
-    <t>Nathan Aké</t>
-  </si>
-  <si>
-    <t>Manchester City;Bournemouth</t>
-  </si>
-  <si>
-    <t>Lucas Digne</t>
-  </si>
-  <si>
-    <t>Aston Villa;Everton</t>
-  </si>
-  <si>
-    <t>John Obi Mikel</t>
-  </si>
-  <si>
-    <t>Stoke City;Chelsea</t>
-  </si>
-  <si>
-    <t>Andy Carroll</t>
-  </si>
-  <si>
-    <t>Newcastle United;Liverpool;West Ham United</t>
-  </si>
-  <si>
-    <t>Muzzy Izzet</t>
-  </si>
-  <si>
-    <t>Ian Taylor</t>
-  </si>
-  <si>
-    <t>Derby County;Aston Villa</t>
-  </si>
-  <si>
-    <t>Kurt Zouma</t>
-  </si>
-  <si>
-    <t>Chelsea;Stoke City;Everton;West Ham United</t>
-  </si>
-  <si>
-    <t>Lucas Leiva</t>
-  </si>
-  <si>
-    <t>Neil Sullivan</t>
-  </si>
-  <si>
-    <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
-  </si>
-  <si>
-    <t>Brett Emerton</t>
-  </si>
-  <si>
-    <t>Eden Hazard</t>
-  </si>
-  <si>
-    <t>Bernd Leno</t>
-  </si>
-  <si>
-    <t>Fulham;Arsenal</t>
-  </si>
-  <si>
-    <t>Dwight McNeil</t>
-  </si>
-  <si>
-    <t>Simon Mignolet</t>
   </si>
   <si>
     <t>Stephen Ireland</t>
@@ -7713,7 +7716,7 @@
         <v>559</v>
       </c>
       <c r="C321" t="s">
-        <v>44</v>
+        <v>560</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -7721,10 +7724,10 @@
         <v>2928</v>
       </c>
       <c r="B322" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C322" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -7732,10 +7735,10 @@
         <v>598</v>
       </c>
       <c r="B323" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C323" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -7743,10 +7746,10 @@
         <v>1565</v>
       </c>
       <c r="B324" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C324" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -7754,10 +7757,10 @@
         <v>10079</v>
       </c>
       <c r="B325" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C325" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -7765,10 +7768,10 @@
         <v>245</v>
       </c>
       <c r="B326" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C326" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -7776,10 +7779,10 @@
         <v>1335</v>
       </c>
       <c r="B327" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C327" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -7787,7 +7790,7 @@
         <v>4123</v>
       </c>
       <c r="B328" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C328" t="s">
         <v>145</v>
@@ -7798,7 +7801,7 @@
         <v>523</v>
       </c>
       <c r="B329" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C329" t="s">
         <v>202</v>
@@ -7809,10 +7812,10 @@
         <v>3448</v>
       </c>
       <c r="B330" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C330" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -7820,7 +7823,7 @@
         <v>2289</v>
       </c>
       <c r="B331" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C331" t="s">
         <v>216</v>
@@ -7831,10 +7834,10 @@
         <v>2991</v>
       </c>
       <c r="B332" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C332" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -7842,7 +7845,7 @@
         <v>3404</v>
       </c>
       <c r="B333" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C333" t="s">
         <v>20</v>
@@ -7853,7 +7856,7 @@
         <v>1497</v>
       </c>
       <c r="B334" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C334" t="s">
         <v>282</v>
@@ -7864,7 +7867,7 @@
         <v>4403</v>
       </c>
       <c r="B335" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C335" t="s">
         <v>315</v>
@@ -7875,7 +7878,7 @@
         <v>22542</v>
       </c>
       <c r="B336" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C336" t="s">
         <v>325</v>
@@ -7886,10 +7889,10 @@
         <v>2845</v>
       </c>
       <c r="B337" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C337" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -7897,7 +7900,7 @@
         <v>3807</v>
       </c>
       <c r="B338" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C338" t="s">
         <v>378</v>
@@ -7908,7 +7911,7 @@
         <v>19680</v>
       </c>
       <c r="B339" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C339" t="s">
         <v>177</v>
@@ -7919,10 +7922,10 @@
         <v>8245</v>
       </c>
       <c r="B340" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C340" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -7930,7 +7933,7 @@
         <v>79</v>
       </c>
       <c r="B341" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C341" t="s">
         <v>308</v>
@@ -7941,7 +7944,7 @@
         <v>1505</v>
       </c>
       <c r="B342" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C342" t="s">
         <v>534</v>
@@ -7952,10 +7955,10 @@
         <v>1909</v>
       </c>
       <c r="B343" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C343" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -7963,10 +7966,10 @@
         <v>3982</v>
       </c>
       <c r="B344" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C344" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -7974,7 +7977,7 @@
         <v>4286</v>
       </c>
       <c r="B345" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C345" t="s">
         <v>202</v>
@@ -7985,10 +7988,10 @@
         <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C346" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -7996,7 +7999,7 @@
         <v>5865</v>
       </c>
       <c r="B347" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C347" t="s">
         <v>271</v>
@@ -8007,7 +8010,7 @@
         <v>3394</v>
       </c>
       <c r="B348" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C348" t="s">
         <v>302</v>
@@ -8018,10 +8021,10 @@
         <v>329</v>
       </c>
       <c r="B349" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C349" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -8029,10 +8032,10 @@
         <v>1045</v>
       </c>
       <c r="B350" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C350" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -8040,10 +8043,10 @@
         <v>755</v>
       </c>
       <c r="B351" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C351" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -8051,7 +8054,7 @@
         <v>2522</v>
       </c>
       <c r="B352" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C352" t="s">
         <v>8</v>
@@ -8062,7 +8065,7 @@
         <v>2072</v>
       </c>
       <c r="B353" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C353" t="s">
         <v>444</v>
@@ -8073,7 +8076,7 @@
         <v>1558</v>
       </c>
       <c r="B354" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C354" t="s">
         <v>129</v>
@@ -8084,7 +8087,7 @@
         <v>1217</v>
       </c>
       <c r="B355" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C355" t="s">
         <v>8</v>
@@ -8095,10 +8098,10 @@
         <v>20486</v>
       </c>
       <c r="B356" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C356" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -8106,7 +8109,7 @@
         <v>1253</v>
       </c>
       <c r="B357" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C357" t="s">
         <v>479</v>
@@ -8117,10 +8120,10 @@
         <v>4252</v>
       </c>
       <c r="B358" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C358" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -8128,10 +8131,10 @@
         <v>293</v>
       </c>
       <c r="B359" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C359" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -8139,10 +8142,10 @@
         <v>2980</v>
       </c>
       <c r="B360" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C360" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -8150,7 +8153,7 @@
         <v>2024</v>
       </c>
       <c r="B361" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C361" t="s">
         <v>308</v>
@@ -8161,10 +8164,10 @@
         <v>2047</v>
       </c>
       <c r="B362" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C362" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -8172,7 +8175,7 @@
         <v>8868</v>
       </c>
       <c r="B363" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C363" t="s">
         <v>79</v>
@@ -8183,7 +8186,7 @@
         <v>2012</v>
       </c>
       <c r="B364" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C364" t="s">
         <v>232</v>
@@ -8194,7 +8197,7 @@
         <v>4666</v>
       </c>
       <c r="B365" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C365" t="s">
         <v>145</v>
@@ -8205,10 +8208,10 @@
         <v>448</v>
       </c>
       <c r="B366" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C366" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -8216,10 +8219,10 @@
         <v>1495</v>
       </c>
       <c r="B367" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C367" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -8227,10 +8230,10 @@
         <v>14716</v>
       </c>
       <c r="B368" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C368" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -8238,7 +8241,7 @@
         <v>4487</v>
       </c>
       <c r="B369" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C369" t="s">
         <v>369</v>
@@ -8249,10 +8252,10 @@
         <v>128</v>
       </c>
       <c r="B370" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C370" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -8260,10 +8263,10 @@
         <v>8707</v>
       </c>
       <c r="B371" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C371" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -8271,7 +8274,7 @@
         <v>4148</v>
       </c>
       <c r="B372" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C372" t="s">
         <v>277</v>
@@ -8282,7 +8285,7 @@
         <v>14164</v>
       </c>
       <c r="B373" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C373" t="s">
         <v>79</v>
@@ -8293,10 +8296,10 @@
         <v>1096</v>
       </c>
       <c r="B374" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C374" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -8304,7 +8307,7 @@
         <v>1151</v>
       </c>
       <c r="B375" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C375" t="s">
         <v>167</v>
@@ -8315,10 +8318,10 @@
         <v>3247</v>
       </c>
       <c r="B376" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C376" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -8326,10 +8329,10 @@
         <v>1205</v>
       </c>
       <c r="B377" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C377" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -8337,10 +8340,10 @@
         <v>603</v>
       </c>
       <c r="B378" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C378" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -8348,7 +8351,7 @@
         <v>11071</v>
       </c>
       <c r="B379" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C379" t="s">
         <v>302</v>
@@ -8359,7 +8362,7 @@
         <v>51423</v>
       </c>
       <c r="B380" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C380" t="s">
         <v>232</v>
@@ -8370,7 +8373,7 @@
         <v>2239</v>
       </c>
       <c r="B381" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C381" t="s">
         <v>129</v>
@@ -8381,10 +8384,10 @@
         <v>13492</v>
       </c>
       <c r="B382" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C382" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -8392,7 +8395,7 @@
         <v>13274</v>
       </c>
       <c r="B383" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C383" t="s">
         <v>232</v>
@@ -8403,7 +8406,7 @@
         <v>2705</v>
       </c>
       <c r="B384" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C384" t="s">
         <v>129</v>
@@ -8414,10 +8417,10 @@
         <v>1740</v>
       </c>
       <c r="B385" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C385" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -8425,7 +8428,7 @@
         <v>4821</v>
       </c>
       <c r="B386" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C386" t="s">
         <v>340</v>
@@ -8436,7 +8439,7 @@
         <v>23396</v>
       </c>
       <c r="B387" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C387" t="s">
         <v>8</v>
@@ -8447,7 +8450,7 @@
         <v>401</v>
       </c>
       <c r="B388" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C388" t="s">
         <v>181</v>
@@ -8458,10 +8461,10 @@
         <v>10487</v>
       </c>
       <c r="B389" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C389" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -8469,7 +8472,7 @@
         <v>25183</v>
       </c>
       <c r="B390" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C390" t="s">
         <v>79</v>
@@ -8480,7 +8483,7 @@
         <v>174</v>
       </c>
       <c r="B391" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C391" t="s">
         <v>129</v>
@@ -8491,7 +8494,7 @@
         <v>4245</v>
       </c>
       <c r="B392" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C392" t="s">
         <v>232</v>
@@ -8502,10 +8505,10 @@
         <v>388</v>
       </c>
       <c r="B393" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C393" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -8513,7 +8516,7 @@
         <v>49481</v>
       </c>
       <c r="B394" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C394" t="s">
         <v>256</v>
@@ -8524,7 +8527,7 @@
         <v>3905</v>
       </c>
       <c r="B395" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C395" t="s">
         <v>304</v>
@@ -8535,10 +8538,10 @@
         <v>3169</v>
       </c>
       <c r="B396" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C396" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -8546,7 +8549,7 @@
         <v>8456</v>
       </c>
       <c r="B397" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C397" t="s">
         <v>145</v>
@@ -8557,10 +8560,10 @@
         <v>1080</v>
       </c>
       <c r="B398" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C398" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -8568,10 +8571,10 @@
         <v>3029</v>
       </c>
       <c r="B399" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C399" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -8579,10 +8582,10 @@
         <v>2669</v>
       </c>
       <c r="B400" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C400" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -8590,7 +8593,7 @@
         <v>5101</v>
       </c>
       <c r="B401" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C401" t="s">
         <v>277</v>
@@ -8601,10 +8604,10 @@
         <v>272</v>
       </c>
       <c r="B402" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C402" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -8612,10 +8615,10 @@
         <v>3983</v>
       </c>
       <c r="B403" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C403" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -8623,10 +8626,10 @@
         <v>3546</v>
       </c>
       <c r="B404" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C404" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -8634,7 +8637,7 @@
         <v>20479</v>
       </c>
       <c r="B405" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C405" t="s">
         <v>181</v>
@@ -8645,7 +8648,7 @@
         <v>2385</v>
       </c>
       <c r="B406" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C406" t="s">
         <v>378</v>
@@ -8656,10 +8659,10 @@
         <v>193</v>
       </c>
       <c r="B407" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C407" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -8667,7 +8670,7 @@
         <v>14805</v>
       </c>
       <c r="B408" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C408" t="s">
         <v>277</v>
@@ -8678,10 +8681,10 @@
         <v>179</v>
       </c>
       <c r="B409" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C409" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -8689,7 +8692,7 @@
         <v>3613</v>
       </c>
       <c r="B410" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C410" t="s">
         <v>262</v>
@@ -8700,10 +8703,10 @@
         <v>929</v>
       </c>
       <c r="B411" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C411" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -8711,10 +8714,10 @@
         <v>3154</v>
       </c>
       <c r="B412" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C412" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -8722,10 +8725,10 @@
         <v>2393</v>
       </c>
       <c r="B413" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C413" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -8733,7 +8736,7 @@
         <v>3121</v>
       </c>
       <c r="B414" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C414" t="s">
         <v>302</v>
@@ -8744,7 +8747,7 @@
         <v>75</v>
       </c>
       <c r="B415" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C415" t="s">
         <v>308</v>
@@ -8755,10 +8758,10 @@
         <v>7114</v>
       </c>
       <c r="B416" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C416" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -8766,10 +8769,10 @@
         <v>167</v>
       </c>
       <c r="B417" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C417" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -8777,10 +8780,10 @@
         <v>768</v>
       </c>
       <c r="B418" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C418" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -8788,10 +8791,10 @@
         <v>1382</v>
       </c>
       <c r="B419" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C419" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -8799,10 +8802,10 @@
         <v>954</v>
       </c>
       <c r="B420" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C420" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -8810,10 +8813,10 @@
         <v>112</v>
       </c>
       <c r="B421" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C421" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -8821,7 +8824,7 @@
         <v>8658</v>
       </c>
       <c r="B422" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C422" t="s">
         <v>232</v>
@@ -8832,7 +8835,7 @@
         <v>3562</v>
       </c>
       <c r="B423" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C423" t="s">
         <v>361</v>
@@ -8843,10 +8846,10 @@
         <v>3524</v>
       </c>
       <c r="B424" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C424" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -8854,10 +8857,10 @@
         <v>757</v>
       </c>
       <c r="B425" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C425" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -8865,7 +8868,7 @@
         <v>2550</v>
       </c>
       <c r="B426" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C426" t="s">
         <v>534</v>
@@ -8876,7 +8879,7 @@
         <v>3388</v>
       </c>
       <c r="B427" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C427" t="s">
         <v>153</v>
@@ -8887,10 +8890,10 @@
         <v>3362</v>
       </c>
       <c r="B428" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C428" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -8898,7 +8901,7 @@
         <v>29</v>
       </c>
       <c r="B429" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C429" t="s">
         <v>282</v>
@@ -8909,10 +8912,10 @@
         <v>3157</v>
       </c>
       <c r="B430" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C430" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -8920,7 +8923,7 @@
         <v>4100</v>
       </c>
       <c r="B431" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C431" t="s">
         <v>56</v>
@@ -8931,10 +8934,10 @@
         <v>2279</v>
       </c>
       <c r="B432" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C432" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -8942,10 +8945,10 @@
         <v>3420</v>
       </c>
       <c r="B433" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C433" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -8953,10 +8956,10 @@
         <v>1017</v>
       </c>
       <c r="B434" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C434" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -8964,10 +8967,10 @@
         <v>9662</v>
       </c>
       <c r="B435" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C435" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -8975,10 +8978,10 @@
         <v>509</v>
       </c>
       <c r="B436" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C436" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -8986,7 +8989,7 @@
         <v>3680</v>
       </c>
       <c r="B437" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C437" t="s">
         <v>304</v>
@@ -8997,7 +9000,7 @@
         <v>1866</v>
       </c>
       <c r="B438" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C438" t="s">
         <v>167</v>
@@ -9008,7 +9011,7 @@
         <v>8589</v>
       </c>
       <c r="B439" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C439" t="s">
         <v>294</v>
@@ -9019,7 +9022,7 @@
         <v>2530</v>
       </c>
       <c r="B440" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C440" t="s">
         <v>534</v>
@@ -9030,7 +9033,7 @@
         <v>1455</v>
       </c>
       <c r="B441" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C441" t="s">
         <v>202</v>
@@ -9041,7 +9044,7 @@
         <v>5220</v>
       </c>
       <c r="B442" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C442" t="s">
         <v>304</v>
@@ -9052,7 +9055,7 @@
         <v>2935</v>
       </c>
       <c r="B443" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -9063,7 +9066,7 @@
         <v>20607</v>
       </c>
       <c r="B444" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C444" t="s">
         <v>304</v>
@@ -9074,7 +9077,7 @@
         <v>4260</v>
       </c>
       <c r="B445" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C445" t="s">
         <v>510</v>
@@ -9085,10 +9088,10 @@
         <v>1426</v>
       </c>
       <c r="B446" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C446" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -9096,7 +9099,7 @@
         <v>11272</v>
       </c>
       <c r="B447" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C447" t="s">
         <v>8</v>
@@ -9107,10 +9110,10 @@
         <v>1282</v>
       </c>
       <c r="B448" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C448" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -9118,7 +9121,7 @@
         <v>172</v>
       </c>
       <c r="B449" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C449" t="s">
         <v>129</v>
@@ -9129,7 +9132,7 @@
         <v>3135</v>
       </c>
       <c r="B450" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C450" t="s">
         <v>20</v>
@@ -9140,7 +9143,7 @@
         <v>5066</v>
       </c>
       <c r="B451" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C451" t="s">
         <v>232</v>
@@ -9151,10 +9154,10 @@
         <v>495</v>
       </c>
       <c r="B452" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C452" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -9162,10 +9165,10 @@
         <v>43</v>
       </c>
       <c r="B453" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C453" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -9176,7 +9179,7 @@
         <v>126</v>
       </c>
       <c r="C454" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -9184,7 +9187,7 @@
         <v>4081</v>
       </c>
       <c r="B455" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C455" t="s">
         <v>378</v>
@@ -9195,7 +9198,7 @@
         <v>8246</v>
       </c>
       <c r="B456" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C456" t="s">
         <v>296</v>
@@ -9206,7 +9209,7 @@
         <v>32</v>
       </c>
       <c r="B457" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C457" t="s">
         <v>232</v>
@@ -9217,7 +9220,7 @@
         <v>12520</v>
       </c>
       <c r="B458" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C458" t="s">
         <v>277</v>
@@ -9228,10 +9231,10 @@
         <v>3015</v>
       </c>
       <c r="B459" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C459" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -9239,10 +9242,10 @@
         <v>4000</v>
       </c>
       <c r="B460" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C460" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -9250,7 +9253,7 @@
         <v>2905</v>
       </c>
       <c r="B461" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C461" t="s">
         <v>334</v>
@@ -9261,10 +9264,10 @@
         <v>394</v>
       </c>
       <c r="B462" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C462" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -9272,10 +9275,10 @@
         <v>3799</v>
       </c>
       <c r="B463" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C463" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -9283,10 +9286,10 @@
         <v>809</v>
       </c>
       <c r="B464" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C464" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -9294,7 +9297,7 @@
         <v>3820</v>
       </c>
       <c r="B465" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C465" t="s">
         <v>432</v>
@@ -9305,10 +9308,10 @@
         <v>3926</v>
       </c>
       <c r="B466" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C466" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -9316,7 +9319,7 @@
         <v>785</v>
       </c>
       <c r="B467" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C467" t="s">
         <v>79</v>
@@ -9327,10 +9330,10 @@
         <v>4084</v>
       </c>
       <c r="B468" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C468" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -9338,7 +9341,7 @@
         <v>1030</v>
       </c>
       <c r="B469" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C469" t="s">
         <v>361</v>
@@ -9349,7 +9352,7 @@
         <v>2925</v>
       </c>
       <c r="B470" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C470" t="s">
         <v>232</v>
@@ -9360,10 +9363,10 @@
         <v>363</v>
       </c>
       <c r="B471" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C471" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -9371,7 +9374,7 @@
         <v>4437</v>
       </c>
       <c r="B472" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C472" t="s">
         <v>456</v>
@@ -9382,10 +9385,10 @@
         <v>1898</v>
       </c>
       <c r="B473" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C473" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -9393,10 +9396,10 @@
         <v>395</v>
       </c>
       <c r="B474" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C474" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -9404,10 +9407,10 @@
         <v>3507</v>
       </c>
       <c r="B475" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C475" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -9415,7 +9418,7 @@
         <v>2080</v>
       </c>
       <c r="B476" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C476" t="s">
         <v>534</v>
@@ -9426,10 +9429,10 @@
         <v>5514</v>
       </c>
       <c r="B477" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C477" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -9437,10 +9440,10 @@
         <v>3281</v>
       </c>
       <c r="B478" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C478" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -9448,10 +9451,10 @@
         <v>2120</v>
       </c>
       <c r="B479" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C479" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -9459,10 +9462,10 @@
         <v>3734</v>
       </c>
       <c r="B480" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C480" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -9470,10 +9473,10 @@
         <v>1193</v>
       </c>
       <c r="B481" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C481" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -9481,10 +9484,10 @@
         <v>1082</v>
       </c>
       <c r="B482" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C482" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -9492,10 +9495,10 @@
         <v>269</v>
       </c>
       <c r="B483" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C483" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -9503,7 +9506,7 @@
         <v>4916</v>
       </c>
       <c r="B484" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C484" t="s">
         <v>517</v>
@@ -9514,10 +9517,10 @@
         <v>7946</v>
       </c>
       <c r="B485" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C485" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -9525,7 +9528,7 @@
         <v>24334</v>
       </c>
       <c r="B486" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C486" t="s">
         <v>294</v>
@@ -9536,10 +9539,10 @@
         <v>4615</v>
       </c>
       <c r="B487" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C487" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -9547,7 +9550,7 @@
         <v>2007</v>
       </c>
       <c r="B488" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C488" t="s">
         <v>325</v>
@@ -9558,7 +9561,7 @@
         <v>1196</v>
       </c>
       <c r="B489" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C489" t="s">
         <v>181</v>
@@ -9569,10 +9572,10 @@
         <v>5672</v>
       </c>
       <c r="B490" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C490" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -9580,7 +9583,7 @@
         <v>4413</v>
       </c>
       <c r="B491" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C491" t="s">
         <v>315</v>
@@ -9591,7 +9594,7 @@
         <v>50245</v>
       </c>
       <c r="B492" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C492" t="s">
         <v>145</v>
@@ -9602,10 +9605,10 @@
         <v>4136</v>
       </c>
       <c r="B493" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C493" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -9613,10 +9616,10 @@
         <v>87</v>
       </c>
       <c r="B494" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C494" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -9624,7 +9627,7 @@
         <v>522</v>
       </c>
       <c r="B495" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C495" t="s">
         <v>202</v>
@@ -9635,7 +9638,7 @@
         <v>1835</v>
       </c>
       <c r="B496" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C496" t="s">
         <v>256</v>
@@ -9646,10 +9649,10 @@
         <v>4183</v>
       </c>
       <c r="B497" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C497" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -9657,10 +9660,10 @@
         <v>3508</v>
       </c>
       <c r="B498" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C498" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -9668,7 +9671,7 @@
         <v>63633</v>
       </c>
       <c r="B499" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C499" t="s">
         <v>20</v>
@@ -9679,10 +9682,10 @@
         <v>2634</v>
       </c>
       <c r="B500" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C500" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -9690,10 +9693,10 @@
         <v>2867</v>
       </c>
       <c r="B501" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C501" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -9701,7 +9704,7 @@
         <v>886</v>
       </c>
       <c r="B502" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C502" t="s">
         <v>216</v>
@@ -9712,10 +9715,10 @@
         <v>248</v>
       </c>
       <c r="B503" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C503" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -9723,10 +9726,10 @@
         <v>967</v>
       </c>
       <c r="B504" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C504" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -9734,10 +9737,10 @@
         <v>3244</v>
       </c>
       <c r="B505" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C505" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -9745,10 +9748,10 @@
         <v>13554</v>
       </c>
       <c r="B506" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C506" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -9756,10 +9759,10 @@
         <v>60</v>
       </c>
       <c r="B507" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C507" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -9767,7 +9770,7 @@
         <v>5682</v>
       </c>
       <c r="B508" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C508" t="s">
         <v>56</v>
@@ -9778,10 +9781,10 @@
         <v>9</v>
       </c>
       <c r="B509" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C509" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -9789,10 +9792,10 @@
         <v>1163</v>
       </c>
       <c r="B510" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C510" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -9800,10 +9803,10 @@
         <v>38</v>
       </c>
       <c r="B511" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C511" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -9811,10 +9814,10 @@
         <v>3719</v>
       </c>
       <c r="B512" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C512" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -9822,10 +9825,10 @@
         <v>1083</v>
       </c>
       <c r="B513" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C513" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -9833,10 +9836,10 @@
         <v>2796</v>
       </c>
       <c r="B514" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C514" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -9844,10 +9847,10 @@
         <v>1848</v>
       </c>
       <c r="B515" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C515" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -9855,10 +9858,10 @@
         <v>558</v>
       </c>
       <c r="B516" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C516" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -9866,7 +9869,7 @@
         <v>16286</v>
       </c>
       <c r="B517" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C517" t="s">
         <v>277</v>
@@ -9877,7 +9880,7 @@
         <v>2323</v>
       </c>
       <c r="B518" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C518" t="s">
         <v>304</v>
@@ -9888,7 +9891,7 @@
         <v>13703</v>
       </c>
       <c r="B519" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C519" t="s">
         <v>304</v>
@@ -9899,10 +9902,10 @@
         <v>2066</v>
       </c>
       <c r="B520" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C520" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -9910,7 +9913,7 @@
         <v>3821</v>
       </c>
       <c r="B521" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C521" t="s">
         <v>361</v>
@@ -9921,7 +9924,7 @@
         <v>26151</v>
       </c>
       <c r="B522" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C522" t="s">
         <v>302</v>
@@ -9932,7 +9935,7 @@
         <v>6451</v>
       </c>
       <c r="B523" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C523" t="s">
         <v>296</v>
@@ -9943,10 +9946,10 @@
         <v>918</v>
       </c>
       <c r="B524" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C524" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -9954,10 +9957,10 @@
         <v>3013</v>
       </c>
       <c r="B525" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C525" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -9965,7 +9968,7 @@
         <v>9167</v>
       </c>
       <c r="B526" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C526" t="s">
         <v>145</v>
@@ -9976,10 +9979,10 @@
         <v>1756</v>
       </c>
       <c r="B527" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C527" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -9987,10 +9990,10 @@
         <v>714</v>
       </c>
       <c r="B528" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C528" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -9998,7 +10001,7 @@
         <v>4525</v>
       </c>
       <c r="B529" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C529" t="s">
         <v>317</v>
@@ -10009,7 +10012,7 @@
         <v>2435</v>
       </c>
       <c r="B530" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C530" t="s">
         <v>296</v>
@@ -10020,7 +10023,7 @@
         <v>24626</v>
       </c>
       <c r="B531" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C531" t="s">
         <v>232</v>
@@ -10031,10 +10034,10 @@
         <v>256</v>
       </c>
       <c r="B532" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C532" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -10042,7 +10045,7 @@
         <v>8171</v>
       </c>
       <c r="B533" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C533" t="s">
         <v>325</v>
@@ -10053,7 +10056,7 @@
         <v>122</v>
       </c>
       <c r="B534" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C534" t="s">
         <v>529</v>
@@ -10064,7 +10067,7 @@
         <v>2837</v>
       </c>
       <c r="B535" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C535" t="s">
         <v>282</v>
@@ -10075,10 +10078,10 @@
         <v>19758</v>
       </c>
       <c r="B536" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C536" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -10086,10 +10089,10 @@
         <v>1095</v>
       </c>
       <c r="B537" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C537" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -10097,10 +10100,10 @@
         <v>1451</v>
       </c>
       <c r="B538" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C538" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -10108,10 +10111,10 @@
         <v>3713</v>
       </c>
       <c r="B539" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C539" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -10119,10 +10122,10 @@
         <v>775</v>
       </c>
       <c r="B540" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C540" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -10130,10 +10133,10 @@
         <v>1754</v>
       </c>
       <c r="B541" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C541" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -10141,10 +10144,10 @@
         <v>4229</v>
       </c>
       <c r="B542" t="s">
+        <v>888</v>
+      </c>
+      <c r="C542" t="s">
         <v>887</v>
-      </c>
-      <c r="C542" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -10152,10 +10155,10 @@
         <v>3850</v>
       </c>
       <c r="B543" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C543" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -10163,10 +10166,10 @@
         <v>1359</v>
       </c>
       <c r="B544" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C544" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -10174,7 +10177,7 @@
         <v>14897</v>
       </c>
       <c r="B545" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C545" t="s">
         <v>216</v>
@@ -10185,10 +10188,10 @@
         <v>452</v>
       </c>
       <c r="B546" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C546" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -10196,10 +10199,10 @@
         <v>2728</v>
       </c>
       <c r="B547" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C547" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -10207,10 +10210,10 @@
         <v>3390</v>
       </c>
       <c r="B548" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C548" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -10218,7 +10221,7 @@
         <v>10766</v>
       </c>
       <c r="B549" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C549" t="s">
         <v>519</v>
@@ -10229,10 +10232,10 @@
         <v>2695</v>
       </c>
       <c r="B550" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C550" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -10240,10 +10243,10 @@
         <v>4656</v>
       </c>
       <c r="B551" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C551" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -10251,7 +10254,7 @@
         <v>66104</v>
       </c>
       <c r="B552" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C552" t="s">
         <v>256</v>
@@ -10262,7 +10265,7 @@
         <v>4472</v>
       </c>
       <c r="B553" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C553" t="s">
         <v>256</v>
@@ -10273,10 +10276,10 @@
         <v>1355</v>
       </c>
       <c r="B554" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C554" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -10284,10 +10287,10 @@
         <v>2569</v>
       </c>
       <c r="B555" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C555" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -10295,7 +10298,7 @@
         <v>54312</v>
       </c>
       <c r="B556" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C556" t="s">
         <v>304</v>
@@ -10306,7 +10309,7 @@
         <v>50234</v>
       </c>
       <c r="B557" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C557" t="s">
         <v>256</v>
@@ -10317,7 +10320,7 @@
         <v>15259</v>
       </c>
       <c r="B558" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C558" t="s">
         <v>345</v>
@@ -10328,7 +10331,7 @@
         <v>13522</v>
       </c>
       <c r="B559" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C559" t="s">
         <v>79</v>
@@ -10339,10 +10342,10 @@
         <v>973</v>
       </c>
       <c r="B560" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C560" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -10350,7 +10353,7 @@
         <v>37776</v>
       </c>
       <c r="B561" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C561" t="s">
         <v>294</v>
@@ -10361,10 +10364,10 @@
         <v>953</v>
       </c>
       <c r="B562" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C562" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -10372,10 +10375,10 @@
         <v>530</v>
       </c>
       <c r="B563" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C563" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -10383,7 +10386,7 @@
         <v>8900</v>
       </c>
       <c r="B564" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C564" t="s">
         <v>232</v>
@@ -10394,7 +10397,7 @@
         <v>3063</v>
       </c>
       <c r="B565" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C565" t="s">
         <v>232</v>
@@ -10405,10 +10408,10 @@
         <v>723</v>
       </c>
       <c r="B566" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C566" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -10416,10 +10419,10 @@
         <v>194</v>
       </c>
       <c r="B567" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C567" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -10427,10 +10430,10 @@
         <v>423</v>
       </c>
       <c r="B568" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C568" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -10438,7 +10441,7 @@
         <v>4714</v>
       </c>
       <c r="B569" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C569" t="s">
         <v>256</v>
@@ -10449,10 +10452,10 @@
         <v>599</v>
       </c>
       <c r="B570" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C570" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -10460,7 +10463,7 @@
         <v>3934</v>
       </c>
       <c r="B571" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C571" t="s">
         <v>378</v>
@@ -10471,7 +10474,7 @@
         <v>1831</v>
       </c>
       <c r="B572" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C572" t="s">
         <v>444</v>
@@ -10482,7 +10485,7 @@
         <v>2009</v>
       </c>
       <c r="B573" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C573" t="s">
         <v>145</v>
@@ -10493,7 +10496,7 @@
         <v>19589</v>
       </c>
       <c r="B574" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C574" t="s">
         <v>202</v>
@@ -10504,10 +10507,10 @@
         <v>4823</v>
       </c>
       <c r="B575" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C575" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -10515,7 +10518,7 @@
         <v>4474</v>
       </c>
       <c r="B576" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C576" t="s">
         <v>256</v>
@@ -10526,10 +10529,10 @@
         <v>3160</v>
       </c>
       <c r="B577" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C577" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -10537,10 +10540,10 @@
         <v>903</v>
       </c>
       <c r="B578" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C578" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -10548,7 +10551,7 @@
         <v>5859</v>
       </c>
       <c r="B579" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C579" t="s">
         <v>294</v>
@@ -10559,10 +10562,10 @@
         <v>4337</v>
       </c>
       <c r="B580" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C580" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -10570,7 +10573,7 @@
         <v>3547</v>
       </c>
       <c r="B581" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C581" t="s">
         <v>519</v>
@@ -10581,7 +10584,7 @@
         <v>3471</v>
       </c>
       <c r="B582" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C582" t="s">
         <v>534</v>
@@ -10592,10 +10595,10 @@
         <v>1037</v>
       </c>
       <c r="B583" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C583" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -10603,10 +10606,10 @@
         <v>1177</v>
       </c>
       <c r="B584" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C584" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -10614,10 +10617,10 @@
         <v>807</v>
       </c>
       <c r="B585" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C585" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -10625,7 +10628,7 @@
         <v>33135</v>
       </c>
       <c r="B586" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C586" t="s">
         <v>460</v>
@@ -10636,10 +10639,10 @@
         <v>938</v>
       </c>
       <c r="B587" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C587" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -10647,10 +10650,10 @@
         <v>8052</v>
       </c>
       <c r="B588" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C588" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -10658,10 +10661,10 @@
         <v>4620</v>
       </c>
       <c r="B589" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C589" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -10669,10 +10672,10 @@
         <v>4843</v>
       </c>
       <c r="B590" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C590" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -10680,10 +10683,10 @@
         <v>8045</v>
       </c>
       <c r="B591" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C591" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -10691,10 +10694,10 @@
         <v>3046</v>
       </c>
       <c r="B592" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C592" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -10702,7 +10705,7 @@
         <v>1242</v>
       </c>
       <c r="B593" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C593" t="s">
         <v>216</v>
@@ -10713,10 +10716,10 @@
         <v>2056</v>
       </c>
       <c r="B594" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C594" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -10724,7 +10727,7 @@
         <v>328</v>
       </c>
       <c r="B595" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C595" t="s">
         <v>8</v>
@@ -10735,7 +10738,7 @@
         <v>16431</v>
       </c>
       <c r="B596" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C596" t="s">
         <v>277</v>
@@ -10746,7 +10749,7 @@
         <v>3513</v>
       </c>
       <c r="B597" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C597" t="s">
         <v>145</v>
@@ -10757,10 +10760,10 @@
         <v>7975</v>
       </c>
       <c r="B598" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C598" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -10768,7 +10771,7 @@
         <v>337</v>
       </c>
       <c r="B599" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C599" t="s">
         <v>8</v>
@@ -10779,7 +10782,7 @@
         <v>1533</v>
       </c>
       <c r="B600" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C600" t="s">
         <v>167</v>
@@ -10790,7 +10793,7 @@
         <v>342</v>
       </c>
       <c r="B601" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C601" t="s">
         <v>8</v>
@@ -10801,7 +10804,7 @@
         <v>2940</v>
       </c>
       <c r="B602" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C602" t="s">
         <v>8</v>
@@ -10812,7 +10815,7 @@
         <v>1210</v>
       </c>
       <c r="B603" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C603" t="s">
         <v>8</v>
@@ -10823,10 +10826,10 @@
         <v>19620</v>
       </c>
       <c r="B604" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C604" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -10834,7 +10837,7 @@
         <v>2117</v>
       </c>
       <c r="B605" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C605" t="s">
         <v>8</v>
@@ -10845,10 +10848,10 @@
         <v>319</v>
       </c>
       <c r="B606" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C606" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -10856,7 +10859,7 @@
         <v>3447</v>
       </c>
       <c r="B607" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C607" t="s">
         <v>8</v>
@@ -10867,7 +10870,7 @@
         <v>5110</v>
       </c>
       <c r="B608" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C608" t="s">
         <v>107</v>
@@ -10878,7 +10881,7 @@
         <v>2654</v>
       </c>
       <c r="B609" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C609" t="s">
         <v>167</v>
@@ -10889,7 +10892,7 @@
         <v>2653</v>
       </c>
       <c r="B610" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C610" t="s">
         <v>167</v>
@@ -10900,7 +10903,7 @@
         <v>3543</v>
       </c>
       <c r="B611" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C611" t="s">
         <v>256</v>
@@ -10911,7 +10914,7 @@
         <v>65970</v>
       </c>
       <c r="B612" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C612" t="s">
         <v>277</v>
@@ -10922,7 +10925,7 @@
         <v>4911</v>
       </c>
       <c r="B613" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C613" t="s">
         <v>167</v>
@@ -10933,10 +10936,10 @@
         <v>1072</v>
       </c>
       <c r="B614" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C614" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -10944,7 +10947,7 @@
         <v>11044</v>
       </c>
       <c r="B615" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C615" t="s">
         <v>277</v>
@@ -10955,7 +10958,7 @@
         <v>4138</v>
       </c>
       <c r="B616" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C616" t="s">
         <v>20</v>
@@ -10966,7 +10969,7 @@
         <v>3664</v>
       </c>
       <c r="B617" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C617" t="s">
         <v>8</v>
@@ -10977,7 +10980,7 @@
         <v>3446</v>
       </c>
       <c r="B618" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C618" t="s">
         <v>8</v>
@@ -10988,7 +10991,7 @@
         <v>5051</v>
       </c>
       <c r="B619" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C619" t="s">
         <v>277</v>
@@ -10999,10 +11002,10 @@
         <v>16723</v>
       </c>
       <c r="B620" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C620" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -11010,7 +11013,7 @@
         <v>1580</v>
       </c>
       <c r="B621" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C621" t="s">
         <v>8</v>
@@ -11021,10 +11024,10 @@
         <v>2818</v>
       </c>
       <c r="B622" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C622" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -11032,7 +11035,7 @@
         <v>5575</v>
       </c>
       <c r="B623" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C623" t="s">
         <v>277</v>

--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="15040"/>
+    <workbookView windowHeight="16380"/>
   </bookViews>
   <sheets>
     <sheet name="premier_league_players_merged_f" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="1003">
   <si>
     <t>player_id</t>
   </si>
@@ -3033,6 +3033,9 @@
   </si>
   <si>
     <t>Benjamin Mendy</t>
+  </si>
+  <si>
+    <t>Matty Cash</t>
   </si>
 </sst>
 </file>
@@ -3045,7 +3048,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3518,16 +3528,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3536,122 +3543,126 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4185,7 +4196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C623"/>
+  <dimension ref="A1:C624"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -11041,6 +11052,17 @@
         <v>277</v>
       </c>
     </row>
+    <row r="624" spans="1:3">
+      <c r="A624" s="1">
+        <v>13344</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C624" t="s">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16380"/>
+    <workbookView windowWidth="2124" windowHeight="25980"/>
   </bookViews>
   <sheets>
-    <sheet name="premier_league_players_merged_f" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="744">
   <si>
     <t>player_id</t>
   </si>
@@ -1946,10 +1946,7 @@
     <t>Aaron Wan-Bissaka</t>
   </si>
   <si>
-    <t>Mark Pembridge</t>
-  </si>
-  <si>
-    <t>Coventry City;Sheffield Wednesday;Everton;Fulham</t>
+    <t>West Ham United;Manchester United</t>
   </si>
   <si>
     <t>Gianfranco Zola</t>
@@ -1961,18 +1958,6 @@
     <t>Tottenham Hotspur;Manchester United;Fulham</t>
   </si>
   <si>
-    <t>Patrik Berger</t>
-  </si>
-  <si>
-    <t>Liverpool;Portsmouth;Aston Villa</t>
-  </si>
-  <si>
-    <t>Dean Holdsworth</t>
-  </si>
-  <si>
-    <t>Wimbledon;Bolton Wanderers</t>
-  </si>
-  <si>
     <t>Raúl Jiménez</t>
   </si>
   <si>
@@ -2000,18 +1985,9 @@
     <t>Queens Park Rangers;Newcastle United</t>
   </si>
   <si>
-    <t>Erik Pieters</t>
-  </si>
-  <si>
     <t>Bruno Fernandes</t>
   </si>
   <si>
-    <t>Scot Gemmill</t>
-  </si>
-  <si>
-    <t>Ayoze Pérez</t>
-  </si>
-  <si>
     <t>Tomás Soucek</t>
   </si>
   <si>
@@ -2021,919 +1997,166 @@
     <t>Emiliano Martínez</t>
   </si>
   <si>
-    <t>Ruel Fox</t>
-  </si>
-  <si>
-    <t>Norwich City;Newcastle United;Tottenham Hotspur</t>
-  </si>
-  <si>
     <t>Bukayo Saka</t>
   </si>
   <si>
-    <t>Kieran Trippier</t>
-  </si>
-  <si>
-    <t>Tim Krul</t>
-  </si>
-  <si>
-    <t>Luton Town</t>
-  </si>
-  <si>
-    <t>James Maddison</t>
-  </si>
-  <si>
-    <t>Shaka Hislop</t>
-  </si>
-  <si>
-    <t>Newcastle United;West Ham United;Portsmouth</t>
-  </si>
-  <si>
-    <t>Paul Scharner</t>
+    <t>Ilkay Gündogan</t>
+  </si>
+  <si>
+    <t>Wilfred Ndidi</t>
+  </si>
+  <si>
+    <t>Phil Foden</t>
+  </si>
+  <si>
+    <t>Clint Dempsey</t>
+  </si>
+  <si>
+    <t>Colin Hendry</t>
+  </si>
+  <si>
+    <t>Ollie Watkins</t>
+  </si>
+  <si>
+    <t>Steven Pienaar</t>
+  </si>
+  <si>
+    <t>Ian Wright</t>
+  </si>
+  <si>
+    <t>Fernando Torres</t>
+  </si>
+  <si>
+    <t>Liverpool;Chelsea</t>
+  </si>
+  <si>
+    <t>Jacob Murphy</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday;Newcastle United</t>
+  </si>
+  <si>
+    <t>Fabricio Coloccini</t>
+  </si>
+  <si>
+    <t>Eidur Gudjohnsen</t>
+  </si>
+  <si>
+    <t>Paul Jones</t>
+  </si>
+  <si>
+    <t>Fabian Schär</t>
+  </si>
+  <si>
+    <t>Nemanja Vidic</t>
+  </si>
+  <si>
+    <t>Joelinton</t>
+  </si>
+  <si>
+    <t>Jack Grealish</t>
+  </si>
+  <si>
+    <t>Neville Southall</t>
+  </si>
+  <si>
+    <t>Dirk Kuijt</t>
+  </si>
+  <si>
+    <t>Kevin Pressman</t>
+  </si>
+  <si>
+    <t>Coventry City;Sheffield Wednesday</t>
+  </si>
+  <si>
+    <t>Ashley Barnes</t>
+  </si>
+  <si>
+    <t>Mark Bosnich</t>
+  </si>
+  <si>
+    <t>Steve Potts</t>
+  </si>
+  <si>
+    <t>Robbie Mustoe</t>
+  </si>
+  <si>
+    <t>Gareth McAuley</t>
+  </si>
+  <si>
+    <t>Angelo Ogbonna</t>
+  </si>
+  <si>
+    <t>Watford;West Ham United</t>
+  </si>
+  <si>
+    <t>Carlos Tevez</t>
+  </si>
+  <si>
+    <t>West Ham United;Manchester United;Manchester City</t>
+  </si>
+  <si>
+    <t>Jonas Olsson</t>
   </si>
   <si>
     <t>Wigan Athletic;West Bromwich Albion</t>
   </si>
   <si>
-    <t>Emmerson Boyce</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Ilkay Gündogan</t>
-  </si>
-  <si>
-    <t>Don Hutchison</t>
-  </si>
-  <si>
-    <t>Liverpool;West Ham United;Coventry City;Everton;Sunderland</t>
-  </si>
-  <si>
-    <t>Victor Moses</t>
-  </si>
-  <si>
-    <t>Samir Nasri</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester City;West Ham United</t>
-  </si>
-  <si>
-    <t>Wilfred Ndidi</t>
-  </si>
-  <si>
-    <t>Jason Roberts</t>
-  </si>
-  <si>
-    <t>Tony Cottee</t>
-  </si>
-  <si>
-    <t>West Ham United;Everton;Leicester City</t>
-  </si>
-  <si>
-    <t>Phil Foden</t>
-  </si>
-  <si>
-    <t>Andy Hinchcliffe</t>
-  </si>
-  <si>
-    <t>Everton;Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Chris Smalling</t>
-  </si>
-  <si>
-    <t>Danny Mills</t>
-  </si>
-  <si>
-    <t>Charlton Athletic;Leeds United;Middlesbrough;Manchester City;Derby County</t>
-  </si>
-  <si>
-    <t>Daniel Sturridge</t>
-  </si>
-  <si>
-    <t>Manchester City;Chelsea;Bolton Wanderers;Liverpool;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Anton Ferdinand</t>
-  </si>
-  <si>
-    <t>West Ham United;Sunderland;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Clint Dempsey</t>
-  </si>
-  <si>
-    <t>Colin Hendry</t>
-  </si>
-  <si>
-    <t>Georginio Wijnaldum</t>
-  </si>
-  <si>
-    <t>Newcastle United;Liverpool</t>
-  </si>
-  <si>
-    <t>Chris Armstrong</t>
-  </si>
-  <si>
-    <t>Wimbledon;Crystal Palace;Tottenham Hotspur;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>John Moncur</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Nottingham Forest;Swindon Town;West Ham United</t>
-  </si>
-  <si>
-    <t>Marcus Bent</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Blackburn Rovers;Ipswich Town;Leicester City;Everton;Charlton Athletic;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Dan Petrescu</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Chelsea;Bradford City;Southampton</t>
-  </si>
-  <si>
-    <t>Andy Townsend</t>
-  </si>
-  <si>
-    <t>Chelsea;Aston Villa;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Ollie Watkins</t>
-  </si>
-  <si>
-    <t>Ciaran Clark</t>
-  </si>
-  <si>
-    <t>Maynor Figueroa</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Hull City</t>
-  </si>
-  <si>
-    <t>Jim Magilton</t>
-  </si>
-  <si>
-    <t>Southampton;Sheffield Wednesday;Ipswich Town</t>
-  </si>
-  <si>
-    <t>Gary O'Neil</t>
-  </si>
-  <si>
-    <t>Steven Pienaar</t>
-  </si>
-  <si>
-    <t>Patrick van Aanholt</t>
-  </si>
-  <si>
-    <t>Chelsea;Wigan Athletic;Sunderland;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Ian Wright</t>
-  </si>
-  <si>
-    <t>Danny Simpson</t>
-  </si>
-  <si>
-    <t>Manchester United;Blackburn Rovers;Newcastle United;Queens Park Rangers;Leicester City</t>
-  </si>
-  <si>
-    <t>David Luiz</t>
-  </si>
-  <si>
-    <t>Stephen Warnock</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>Fernando Torres</t>
-  </si>
-  <si>
-    <t>Liverpool;Chelsea</t>
-  </si>
-  <si>
-    <t>Alan Stubbs</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers;Everton;Sunderland</t>
-  </si>
-  <si>
-    <t>Jacob Murphy</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Newcastle United</t>
-  </si>
-  <si>
-    <t>Chris Bart-Williams</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Sheffield Wednesday;Charlton Athletic;Ipswich Town</t>
-  </si>
-  <si>
-    <t>Fabricio Coloccini</t>
-  </si>
-  <si>
-    <t>Eidur Gudjohnsen</t>
-  </si>
-  <si>
-    <t>Will Hughes</t>
-  </si>
-  <si>
-    <t>Cameron Jerome</t>
-  </si>
-  <si>
-    <t>Paul Jones</t>
-  </si>
-  <si>
-    <t>Fabian Schär</t>
-  </si>
-  <si>
-    <t>Nemanja Vidic</t>
-  </si>
-  <si>
-    <t>Joelinton</t>
-  </si>
-  <si>
-    <t>Jack Grealish</t>
-  </si>
-  <si>
-    <t>Danny Higginbotham</t>
-  </si>
-  <si>
-    <t>Manchester United;Derby County;Southampton;Sunderland;Stoke City</t>
-  </si>
-  <si>
-    <t>Anthony Martial</t>
-  </si>
-  <si>
-    <t>Ben Thatcher</t>
-  </si>
-  <si>
-    <t>Ipswich Town</t>
-  </si>
-  <si>
-    <t>Neville Southall</t>
-  </si>
-  <si>
-    <t>Dirk Kuijt</t>
-  </si>
-  <si>
-    <t>Victor Lindelöf</t>
-  </si>
-  <si>
-    <t>Kevin Pressman</t>
-  </si>
-  <si>
-    <t>Coventry City;Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Kevin Richardson</t>
-  </si>
-  <si>
-    <t>Aston Villa;Coventry City;Southampton</t>
-  </si>
-  <si>
-    <t>Birmingham City</t>
-  </si>
-  <si>
-    <t>Charlie Adam</t>
-  </si>
-  <si>
-    <t>Ashley Barnes</t>
-  </si>
-  <si>
-    <t>Mark Bosnich</t>
-  </si>
-  <si>
-    <t>Mateo Kovacic</t>
-  </si>
-  <si>
-    <t>Nigel Reo-Coker</t>
-  </si>
-  <si>
-    <t>West Ham United;Aston Villa;Bolton Wanderers;Norwich City</t>
-  </si>
-  <si>
-    <t>Matthew Jarvis</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers;West Ham United;Norwich City</t>
-  </si>
-  <si>
-    <t>Victor Anichebe</t>
-  </si>
-  <si>
-    <t>Mark Crossley</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Middlesbrough;Fulham</t>
-  </si>
-  <si>
-    <t>Fabian Delph</t>
-  </si>
-  <si>
-    <t>Aston Villa;Manchester City;Everton</t>
-  </si>
-  <si>
-    <t>Marcus Gayle</t>
-  </si>
-  <si>
-    <t>Wimbledon;Watford</t>
-  </si>
-  <si>
-    <t>Phil Jones</t>
-  </si>
-  <si>
-    <t>Joshua King</t>
-  </si>
-  <si>
-    <t>Manchester United;AFC Bournemouth;Everton;Watford</t>
-  </si>
-  <si>
-    <t>Steve Potts</t>
-  </si>
-  <si>
-    <t>Jason Puncheon</t>
-  </si>
-  <si>
-    <t>Paul Williams</t>
-  </si>
-  <si>
-    <t>Micah Richards</t>
-  </si>
-  <si>
-    <t>Robbie Mustoe</t>
-  </si>
-  <si>
-    <t>Gareth McAuley</t>
-  </si>
-  <si>
-    <t>Matt Holland</t>
-  </si>
-  <si>
-    <t>Ipswich Town;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Stuart Pearce</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Newcastle United;West Ham United;Manchester City</t>
-  </si>
-  <si>
-    <t>Danny Rose</t>
-  </si>
-  <si>
-    <t>Sean Davis</t>
-  </si>
-  <si>
-    <t>Angelo Ogbonna</t>
-  </si>
-  <si>
-    <t>Watford;West Ham United</t>
-  </si>
-  <si>
-    <t>Carlos Tevez</t>
-  </si>
-  <si>
-    <t>West Ham United;Manchester United;Manchester City</t>
-  </si>
-  <si>
-    <t>Franck Queudrue</t>
-  </si>
-  <si>
-    <t>Middlesbrough;Fulham;Birmingham City</t>
-  </si>
-  <si>
-    <t>Jonas Olsson</t>
-  </si>
-  <si>
-    <t>Kasey Keller</t>
-  </si>
-  <si>
-    <t>Leicester City;Tottenham Hotspur;Southampton;Fulham</t>
-  </si>
-  <si>
-    <t>Darren Huckerby</t>
-  </si>
-  <si>
-    <t>Newcastle United;Coventry City;Leeds United;Manchester City;Norwich City</t>
-  </si>
-  <si>
-    <t>John Barnes</t>
-  </si>
-  <si>
-    <t>Watford;Liverpool;Newcastle United;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Toby Alderweireld</t>
-  </si>
-  <si>
-    <t>Demarai Gray</t>
-  </si>
-  <si>
     <t>Tyrick Mitchell</t>
   </si>
   <si>
-    <t>Morgan Schneiderlin</t>
-  </si>
-  <si>
-    <t>Southampton;Manchester United;Everton</t>
-  </si>
-  <si>
-    <t>Steve Sidwell</t>
-  </si>
-  <si>
     <t>Matt Elliott</t>
   </si>
   <si>
-    <t>Federico Fernández</t>
-  </si>
-  <si>
-    <t>Swansea City;Newcastle United</t>
-  </si>
-  <si>
-    <t>Joe Allen</t>
-  </si>
-  <si>
-    <t>Yves Bissouma</t>
-  </si>
-  <si>
-    <t>Conor Coady</t>
-  </si>
-  <si>
-    <t>Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Kevin Gallacher</t>
-  </si>
-  <si>
-    <t>Coventry City;Blackburn Rovers;Newcastle United</t>
-  </si>
-  <si>
     <t>Kenneth Monkou</t>
   </si>
   <si>
     <t>Robert Pirès</t>
   </si>
   <si>
-    <t>Ahmed El Mohamady</t>
-  </si>
-  <si>
-    <t>Sunderland;Hull City;Aston Villa</t>
-  </si>
-  <si>
-    <t>Younes Kaboul</t>
-  </si>
-  <si>
-    <t>Alexis Mac Allister</t>
-  </si>
-  <si>
-    <t>Ryan Nelsen</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Tottenham Hotspur;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Martin Olsson</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Norwich City;Swansea City</t>
-  </si>
-  <si>
     <t>Lucas Radebe</t>
   </si>
   <si>
-    <t>Rod Wallace</t>
-  </si>
-  <si>
-    <t>Southampton;Leeds United;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Michael Hughes</t>
-  </si>
-  <si>
-    <t>Manchester City;West Ham United;Wimbledon;Coventry City;Birmingham City;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Jake Livermore</t>
-  </si>
-  <si>
-    <t>Kelechi Iheanacho</t>
-  </si>
-  <si>
-    <t>Manchester City;Leicester City</t>
-  </si>
-  <si>
-    <t>Dean Saunders</t>
-  </si>
-  <si>
-    <t>Liverpool;Aston Villa;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Jorginho</t>
-  </si>
-  <si>
-    <t>Steve Bould</t>
-  </si>
-  <si>
-    <t>Arsenal;Sunderland</t>
-  </si>
-  <si>
-    <t>Christian Dailly</t>
-  </si>
-  <si>
-    <t>Derby County;Blackburn Rovers;West Ham United</t>
-  </si>
-  <si>
-    <t>Earl Barrett</t>
-  </si>
-  <si>
-    <t>Aston Villa;Everton;Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Heurelho Gomes</t>
-  </si>
-  <si>
-    <t>David Ginola</t>
-  </si>
-  <si>
-    <t>Newcastle United;Tottenham Hotspur;Aston Villa;Everton</t>
-  </si>
-  <si>
-    <t>Kenwyne Jones</t>
-  </si>
-  <si>
-    <t>Southampton;Sunderland;Stoke City;Cardiff City</t>
-  </si>
-  <si>
-    <t>Dean Kiely</t>
-  </si>
-  <si>
-    <t>Charlton Athletic;Portsmouth;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Neil Ruddock</t>
-  </si>
-  <si>
-    <t>Southampton;Tottenham Hotspur;Liverpool;West Ham United;Crystal Palace</t>
-  </si>
-  <si>
     <t>Rodri</t>
   </si>
   <si>
     <t>Steven Taylor</t>
   </si>
   <si>
-    <t>Aaron Ramsdale</t>
-  </si>
-  <si>
-    <t>Tomasz Radzinski</t>
-  </si>
-  <si>
-    <t>Everton;Fulham</t>
-  </si>
-  <si>
-    <t>Steven Nzonzi</t>
-  </si>
-  <si>
-    <t>Joachim Andersen</t>
-  </si>
-  <si>
-    <t>Martin Dúbravka</t>
-  </si>
-  <si>
-    <t>Michael Brown</t>
-  </si>
-  <si>
-    <t>Manchester City;Tottenham Hotspur;Fulham;Wigan Athletic;Portsmouth</t>
-  </si>
-  <si>
-    <t>Yossi Benayoun</t>
-  </si>
-  <si>
-    <t>West Ham United;Liverpool;Chelsea;Arsenal;Queens Park Rangers</t>
-  </si>
-  <si>
     <t>Dele Alli</t>
   </si>
   <si>
-    <t>George McCartney</t>
-  </si>
-  <si>
-    <t>Sunderland;West Ham United</t>
-  </si>
-  <si>
-    <t>Steve Howey</t>
-  </si>
-  <si>
-    <t>Newcastle United;Manchester City;Leicester City;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Philippe Coutinho</t>
-  </si>
-  <si>
-    <t>Steven Reid</t>
-  </si>
-  <si>
     <t>Douglas Luiz</t>
   </si>
   <si>
-    <t>David Burrows</t>
-  </si>
-  <si>
-    <t>Liverpool;West Ham United;Everton;Coventry City;Birmingham City</t>
-  </si>
-  <si>
     <t>Solly March</t>
   </si>
   <si>
     <t>Steve Ogrizovic</t>
   </si>
   <si>
-    <t>Alexandre Song</t>
-  </si>
-  <si>
-    <t>Diogo Jota</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers;Liverpool</t>
-  </si>
-  <si>
-    <t>Dejan Stefanovic</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Portsmouth;Fulham</t>
-  </si>
-  <si>
-    <t>Paolo Di Canio</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;West Ham United;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Jack Colback</t>
-  </si>
-  <si>
-    <t>Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Colin Calderwood</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Swindon Town;Aston Villa;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Jody Craddock</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Matt Doherty</t>
-  </si>
-  <si>
-    <t>Steven Fletcher</t>
-  </si>
-  <si>
-    <t>Burnley;Wolverhampton Wanderers;Sunderland</t>
-  </si>
-  <si>
-    <t>Chris Kirkland</t>
-  </si>
-  <si>
-    <t>Coventry City;Liverpool;West Bromwich Albion;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Sean Longstaff</t>
-  </si>
-  <si>
-    <t>Clive Wilson</t>
-  </si>
-  <si>
-    <t>Chelsea;Queens Park Rangers;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Nedum Onuoha</t>
-  </si>
-  <si>
-    <t>Manchester City;Sunderland;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Dan Gosling</t>
-  </si>
-  <si>
-    <t>Everton;Newcastle United;AFC Bournemouth</t>
-  </si>
-  <si>
     <t>Lewis Cook</t>
   </si>
   <si>
-    <t>Andrew Johnson</t>
-  </si>
-  <si>
-    <t>Birmingham City;Crystal Palace;Everton;Fulham</t>
-  </si>
-  <si>
-    <t>Ki Sung-Yueng</t>
-  </si>
-  <si>
-    <t>Swansea City;Sunderland;Newcastle United</t>
-  </si>
-  <si>
     <t>Gabriel Martinelli</t>
   </si>
   <si>
     <t>Nacho Monreal</t>
   </si>
   <si>
-    <t>Gustavo Poyet</t>
-  </si>
-  <si>
-    <t>Chelsea;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Wayne Hennessey</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers;Crystal Palace;Burnley;Nottingham Forest</t>
-  </si>
-  <si>
     <t>Miguel Almirón</t>
   </si>
   <si>
     <t>Gabriel Magalhães</t>
   </si>
   <si>
-    <t>Morgan Gibbs-White</t>
-  </si>
-  <si>
-    <t>Maximilian Kilman</t>
-  </si>
-  <si>
-    <t>Oyvind Leonhardsen</t>
-  </si>
-  <si>
-    <t>Wimbledon;Liverpool;Tottenham Hotspur;Aston Villa</t>
-  </si>
-  <si>
-    <t>Jefferson Lerma</t>
-  </si>
-  <si>
-    <t>Ian Nolan</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Bradford City</t>
-  </si>
-  <si>
-    <t>Neil Maddison</t>
-  </si>
-  <si>
-    <t>Southampton;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Tyrone Mings</t>
-  </si>
-  <si>
     <t>Stiliyan Petrov</t>
   </si>
   <si>
-    <t>Lee Clark</t>
-  </si>
-  <si>
-    <t>Newcastle United;Sunderland;Fulham</t>
-  </si>
-  <si>
-    <t>Peter Beardsley</t>
-  </si>
-  <si>
-    <t>Everton;Newcastle United;Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>Gunnar Halle</t>
-  </si>
-  <si>
-    <t>Oldham Athletic;Leeds United;Bradford City</t>
-  </si>
-  <si>
-    <t>Mesut Özil</t>
-  </si>
-  <si>
-    <t>Vinnie Jones</t>
-  </si>
-  <si>
-    <t>Wimbledon;Chelsea</t>
-  </si>
-  <si>
-    <t>Matt Ritchie</t>
-  </si>
-  <si>
-    <t>Lauren</t>
-  </si>
-  <si>
-    <t>David Bentley</t>
-  </si>
-  <si>
     <t>Jan Bednarek</t>
   </si>
   <si>
-    <t>Marko Arnautovic</t>
-  </si>
-  <si>
-    <t>Stoke City;West Ham United</t>
-  </si>
-  <si>
-    <t>Héctor Bellerín</t>
-  </si>
-  <si>
-    <t>Craig Cathcart</t>
-  </si>
-  <si>
-    <t>Blackpool;Watford</t>
-  </si>
-  <si>
-    <t>Mark Draper</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Leicester City;Aston Villa;Southampton</t>
-  </si>
-  <si>
     <t>Luka Milivojevic</t>
-  </si>
-  <si>
-    <t>Jesse Lingard</t>
-  </si>
-  <si>
-    <t>Manchester United;West Ham United;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Jack Wilshere</t>
-  </si>
-  <si>
-    <t>Marc Wilson</t>
-  </si>
-  <si>
-    <t>Craig Short</t>
-  </si>
-  <si>
-    <t>Everton;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Darryl Powell</t>
-  </si>
-  <si>
-    <t>Derby County;Birmingham City</t>
-  </si>
-  <si>
-    <t>Alan Kimble</t>
-  </si>
-  <si>
-    <t>Jack Harrison</t>
-  </si>
-  <si>
-    <t>Alf Inge Haaland</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Leeds United;Manchester City</t>
-  </si>
-  <si>
-    <t>Ryan Fraser</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth;Newcastle United</t>
-  </si>
-  <si>
-    <t>Calum Chambers</t>
-  </si>
-  <si>
-    <t>Cardiff City</t>
-  </si>
-  <si>
-    <t>Étienne Capoue</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Watford</t>
-  </si>
-  <si>
-    <t>Steve Cook</t>
-  </si>
-  <si>
-    <t>Kieran Gibbs</t>
-  </si>
-  <si>
-    <t>Arsenal;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Maik Taylor</t>
-  </si>
-  <si>
-    <t>Boudewijn Zenden</t>
-  </si>
-  <si>
-    <t>Chelsea;Middlesbrough;Liverpool;Sunderland</t>
   </si>
   <si>
     <t>Lee Sharpe</t>
@@ -3048,10 +2271,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3402,12 +2632,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3510,34 +2755,29 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3546,123 +2786,126 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3715,221 +2958,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3939,7 +2968,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3949,39 +2978,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4013,7 +3042,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4048,7 +3076,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4060,131 +3087,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -4196,17 +3252,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C624"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:C464"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="19.5480769230769" customWidth="1"/>
+    <col min="3" max="3" width="29.9711538461538" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -8299,81 +7359,81 @@
         <v>638</v>
       </c>
       <c r="C373" t="s">
-        <v>79</v>
+        <v>639</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374">
-        <v>1096</v>
+        <v>1151</v>
       </c>
       <c r="B374" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C374" t="s">
-        <v>640</v>
+        <v>167</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375">
-        <v>1151</v>
+        <v>3247</v>
       </c>
       <c r="B375" t="s">
         <v>641</v>
       </c>
       <c r="C375" t="s">
-        <v>167</v>
+        <v>642</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376">
-        <v>3247</v>
+        <v>11071</v>
       </c>
       <c r="B376" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C376" t="s">
-        <v>643</v>
+        <v>302</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377">
-        <v>1205</v>
+        <v>51423</v>
       </c>
       <c r="B377" t="s">
         <v>644</v>
       </c>
       <c r="C377" t="s">
-        <v>645</v>
+        <v>232</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378">
-        <v>603</v>
+        <v>2239</v>
       </c>
       <c r="B378" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C378" t="s">
-        <v>647</v>
+        <v>129</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379">
-        <v>11071</v>
+        <v>13492</v>
       </c>
       <c r="B379" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C379" t="s">
-        <v>302</v>
+        <v>647</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380">
-        <v>51423</v>
+        <v>13274</v>
       </c>
       <c r="B380" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C380" t="s">
         <v>232</v>
@@ -8381,10 +7441,10 @@
     </row>
     <row r="381" spans="1:3">
       <c r="A381">
-        <v>2239</v>
+        <v>2705</v>
       </c>
       <c r="B381" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C381" t="s">
         <v>129</v>
@@ -8392,681 +7452,681 @@
     </row>
     <row r="382" spans="1:3">
       <c r="A382">
-        <v>13492</v>
+        <v>1740</v>
       </c>
       <c r="B382" t="s">
+        <v>650</v>
+      </c>
+      <c r="C382" t="s">
         <v>651</v>
-      </c>
-      <c r="C382" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383">
-        <v>13274</v>
+        <v>23396</v>
       </c>
       <c r="B383" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C383" t="s">
-        <v>232</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384">
-        <v>2705</v>
+        <v>25183</v>
       </c>
       <c r="B384" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C384" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385">
-        <v>1740</v>
+        <v>174</v>
       </c>
       <c r="B385" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C385" t="s">
-        <v>656</v>
+        <v>129</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
-        <v>4821</v>
+        <v>4245</v>
       </c>
       <c r="B386" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C386" t="s">
-        <v>340</v>
+        <v>232</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387">
-        <v>23396</v>
+        <v>49481</v>
       </c>
       <c r="B387" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C387" t="s">
-        <v>8</v>
+        <v>256</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388">
-        <v>401</v>
+        <v>5101</v>
       </c>
       <c r="B388" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C388" t="s">
-        <v>181</v>
+        <v>277</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389">
-        <v>10487</v>
+        <v>20479</v>
       </c>
       <c r="B389" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C389" t="s">
-        <v>631</v>
+        <v>181</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390">
-        <v>25183</v>
+        <v>14805</v>
       </c>
       <c r="B390" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C390" t="s">
-        <v>79</v>
+        <v>277</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391">
-        <v>174</v>
+        <v>3121</v>
       </c>
       <c r="B391" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C391" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392">
-        <v>4245</v>
+        <v>75</v>
       </c>
       <c r="B392" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C392" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393">
-        <v>388</v>
+        <v>8658</v>
       </c>
       <c r="B393" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C393" t="s">
-        <v>665</v>
+        <v>232</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394">
-        <v>49481</v>
+        <v>3388</v>
       </c>
       <c r="B394" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C394" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395">
-        <v>3905</v>
+        <v>29</v>
       </c>
       <c r="B395" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C395" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396">
-        <v>3169</v>
+        <v>3420</v>
       </c>
       <c r="B396" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C396" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397">
-        <v>8456</v>
+        <v>9662</v>
       </c>
       <c r="B397" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C397" t="s">
-        <v>145</v>
+        <v>668</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398">
-        <v>1080</v>
+        <v>3680</v>
       </c>
       <c r="B398" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C398" t="s">
-        <v>672</v>
+        <v>304</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399">
-        <v>3029</v>
+        <v>1866</v>
       </c>
       <c r="B399" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C399" t="s">
-        <v>674</v>
+        <v>167</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400">
-        <v>2669</v>
+        <v>1455</v>
       </c>
       <c r="B400" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C400" t="s">
-        <v>676</v>
+        <v>202</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401">
-        <v>5101</v>
+        <v>5220</v>
       </c>
       <c r="B401" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C401" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402">
-        <v>272</v>
+        <v>2935</v>
       </c>
       <c r="B402" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C402" t="s">
-        <v>679</v>
+        <v>8</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403">
-        <v>3983</v>
+        <v>20607</v>
       </c>
       <c r="B403" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C403" t="s">
-        <v>669</v>
+        <v>304</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404">
-        <v>3546</v>
+        <v>4260</v>
       </c>
       <c r="B404" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C404" t="s">
-        <v>682</v>
+        <v>510</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405">
-        <v>20479</v>
+        <v>172</v>
       </c>
       <c r="B405" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C405" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406">
-        <v>2385</v>
+        <v>3135</v>
       </c>
       <c r="B406" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="C406" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407">
-        <v>193</v>
+        <v>495</v>
       </c>
       <c r="B407" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C407" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408">
-        <v>14805</v>
+        <v>8246</v>
       </c>
       <c r="B408" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="C408" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="B409" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C409" t="s">
-        <v>689</v>
+        <v>232</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410">
-        <v>3613</v>
+        <v>785</v>
       </c>
       <c r="B410" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C410" t="s">
-        <v>262</v>
+        <v>79</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411">
-        <v>929</v>
+        <v>363</v>
       </c>
       <c r="B411" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="C411" t="s">
-        <v>692</v>
+        <v>566</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412">
-        <v>3154</v>
+        <v>4437</v>
       </c>
       <c r="B412" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="C412" t="s">
-        <v>694</v>
+        <v>456</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413">
-        <v>2393</v>
+        <v>5514</v>
       </c>
       <c r="B413" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C413" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414">
-        <v>3121</v>
+        <v>3281</v>
       </c>
       <c r="B414" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C414" t="s">
-        <v>302</v>
+        <v>688</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415">
-        <v>75</v>
+        <v>3734</v>
       </c>
       <c r="B415" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="C415" t="s">
-        <v>308</v>
+        <v>690</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416">
-        <v>7114</v>
+        <v>24334</v>
       </c>
       <c r="B416" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="C416" t="s">
-        <v>700</v>
+        <v>294</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417">
-        <v>167</v>
+        <v>1196</v>
       </c>
       <c r="B417" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="C417" t="s">
-        <v>702</v>
+        <v>181</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418">
-        <v>768</v>
+        <v>522</v>
       </c>
       <c r="B418" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="C418" t="s">
-        <v>704</v>
+        <v>202</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419">
-        <v>1382</v>
+        <v>1835</v>
       </c>
       <c r="B419" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="C419" t="s">
-        <v>706</v>
+        <v>256</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420">
-        <v>954</v>
+        <v>886</v>
       </c>
       <c r="B420" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="C420" t="s">
-        <v>708</v>
+        <v>216</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421">
-        <v>112</v>
+        <v>16286</v>
       </c>
       <c r="B421" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="C421" t="s">
-        <v>710</v>
+        <v>277</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422">
-        <v>8658</v>
+        <v>2323</v>
       </c>
       <c r="B422" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="C422" t="s">
-        <v>232</v>
+        <v>304</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423">
-        <v>3562</v>
+        <v>9167</v>
       </c>
       <c r="B423" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="C423" t="s">
-        <v>361</v>
+        <v>145</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424">
-        <v>3524</v>
+        <v>24626</v>
       </c>
       <c r="B424" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="C424" t="s">
-        <v>714</v>
+        <v>232</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425">
-        <v>757</v>
+        <v>8171</v>
       </c>
       <c r="B425" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="C425" t="s">
-        <v>716</v>
+        <v>325</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426">
-        <v>2550</v>
+        <v>122</v>
       </c>
       <c r="B426" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="C426" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427">
-        <v>3388</v>
+        <v>10766</v>
       </c>
       <c r="B427" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="C427" t="s">
-        <v>153</v>
+        <v>519</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428">
-        <v>3362</v>
+        <v>66104</v>
       </c>
       <c r="B428" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="C428" t="s">
-        <v>720</v>
+        <v>256</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429">
-        <v>29</v>
+        <v>4472</v>
       </c>
       <c r="B429" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="C429" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430">
-        <v>3157</v>
+        <v>54312</v>
       </c>
       <c r="B430" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="C430" t="s">
-        <v>723</v>
+        <v>304</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431">
-        <v>4100</v>
+        <v>50234</v>
       </c>
       <c r="B431" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="C431" t="s">
-        <v>56</v>
+        <v>256</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432">
-        <v>2279</v>
+        <v>3063</v>
       </c>
       <c r="B432" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="C432" t="s">
-        <v>726</v>
+        <v>232</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433">
-        <v>3420</v>
+        <v>19589</v>
       </c>
       <c r="B433" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="C433" t="s">
-        <v>728</v>
+        <v>202</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434">
-        <v>1017</v>
+        <v>5859</v>
       </c>
       <c r="B434" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="C434" t="s">
-        <v>730</v>
+        <v>294</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435">
-        <v>9662</v>
+        <v>328</v>
       </c>
       <c r="B435" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="C435" t="s">
-        <v>732</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436">
-        <v>509</v>
+        <v>16431</v>
       </c>
       <c r="B436" t="s">
-        <v>733</v>
+        <v>711</v>
       </c>
       <c r="C436" t="s">
-        <v>734</v>
+        <v>277</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437">
-        <v>3680</v>
+        <v>3513</v>
       </c>
       <c r="B437" t="s">
-        <v>735</v>
+        <v>712</v>
       </c>
       <c r="C437" t="s">
-        <v>304</v>
+        <v>145</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438">
-        <v>1866</v>
+        <v>7975</v>
       </c>
       <c r="B438" t="s">
-        <v>736</v>
+        <v>713</v>
       </c>
       <c r="C438" t="s">
-        <v>167</v>
+        <v>714</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439">
-        <v>8589</v>
+        <v>337</v>
       </c>
       <c r="B439" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="C439" t="s">
-        <v>294</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440">
-        <v>2530</v>
+        <v>1533</v>
       </c>
       <c r="B440" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="C440" t="s">
-        <v>534</v>
+        <v>167</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441">
-        <v>1455</v>
+        <v>342</v>
       </c>
       <c r="B441" t="s">
-        <v>739</v>
+        <v>717</v>
       </c>
       <c r="C441" t="s">
-        <v>202</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442">
-        <v>5220</v>
+        <v>2940</v>
       </c>
       <c r="B442" t="s">
-        <v>740</v>
+        <v>718</v>
       </c>
       <c r="C442" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443">
-        <v>2935</v>
+        <v>1210</v>
       </c>
       <c r="B443" t="s">
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -9074,43 +8134,43 @@
     </row>
     <row r="444" spans="1:3">
       <c r="A444">
-        <v>20607</v>
+        <v>19620</v>
       </c>
       <c r="B444" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="C444" t="s">
-        <v>304</v>
+        <v>721</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445">
-        <v>4260</v>
+        <v>2117</v>
       </c>
       <c r="B445" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="C445" t="s">
-        <v>510</v>
+        <v>8</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446">
-        <v>1426</v>
+        <v>319</v>
       </c>
       <c r="B446" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="C446" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447">
-        <v>11272</v>
+        <v>3447</v>
       </c>
       <c r="B447" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
       <c r="C447" t="s">
         <v>8</v>
@@ -9118,1948 +8178,188 @@
     </row>
     <row r="448" spans="1:3">
       <c r="A448">
-        <v>1282</v>
+        <v>5110</v>
       </c>
       <c r="B448" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="C448" t="s">
-        <v>748</v>
+        <v>107</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449">
-        <v>172</v>
+        <v>2654</v>
       </c>
       <c r="B449" t="s">
-        <v>749</v>
+        <v>727</v>
       </c>
       <c r="C449" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450">
-        <v>3135</v>
+        <v>2653</v>
       </c>
       <c r="B450" t="s">
-        <v>750</v>
+        <v>728</v>
       </c>
       <c r="C450" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451">
-        <v>5066</v>
+        <v>3543</v>
       </c>
       <c r="B451" t="s">
-        <v>751</v>
+        <v>729</v>
       </c>
       <c r="C451" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452">
-        <v>495</v>
+        <v>65970</v>
       </c>
       <c r="B452" t="s">
-        <v>752</v>
+        <v>730</v>
       </c>
       <c r="C452" t="s">
-        <v>753</v>
+        <v>277</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453">
-        <v>43</v>
+        <v>4911</v>
       </c>
       <c r="B453" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="C453" t="s">
-        <v>755</v>
+        <v>167</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454">
-        <v>1780</v>
+        <v>1072</v>
       </c>
       <c r="B454" t="s">
-        <v>126</v>
+        <v>732</v>
       </c>
       <c r="C454" t="s">
-        <v>756</v>
+        <v>566</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455">
-        <v>4081</v>
+        <v>11044</v>
       </c>
       <c r="B455" t="s">
-        <v>757</v>
+        <v>733</v>
       </c>
       <c r="C455" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456">
-        <v>8246</v>
+        <v>4138</v>
       </c>
       <c r="B456" t="s">
-        <v>758</v>
+        <v>734</v>
       </c>
       <c r="C456" t="s">
-        <v>296</v>
+        <v>20</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457">
-        <v>32</v>
+        <v>3664</v>
       </c>
       <c r="B457" t="s">
-        <v>759</v>
+        <v>735</v>
       </c>
       <c r="C457" t="s">
-        <v>232</v>
+        <v>8</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458">
-        <v>12520</v>
+        <v>3446</v>
       </c>
       <c r="B458" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="C458" t="s">
-        <v>277</v>
+        <v>8</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459">
-        <v>3015</v>
+        <v>5051</v>
       </c>
       <c r="B459" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="C459" t="s">
-        <v>762</v>
+        <v>277</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460">
-        <v>4000</v>
+        <v>16723</v>
       </c>
       <c r="B460" t="s">
-        <v>763</v>
+        <v>738</v>
       </c>
       <c r="C460" t="s">
-        <v>764</v>
+        <v>739</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461">
-        <v>2905</v>
+        <v>1580</v>
       </c>
       <c r="B461" t="s">
-        <v>765</v>
+        <v>740</v>
       </c>
       <c r="C461" t="s">
-        <v>334</v>
+        <v>8</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462">
-        <v>394</v>
+        <v>2818</v>
       </c>
       <c r="B462" t="s">
-        <v>766</v>
+        <v>741</v>
       </c>
       <c r="C462" t="s">
-        <v>767</v>
+        <v>724</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463">
-        <v>3799</v>
+        <v>5575</v>
       </c>
       <c r="B463" t="s">
-        <v>768</v>
+        <v>742</v>
       </c>
       <c r="C463" t="s">
-        <v>769</v>
+        <v>277</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464">
-        <v>809</v>
+        <v>13344</v>
       </c>
       <c r="B464" t="s">
-        <v>770</v>
+        <v>743</v>
       </c>
       <c r="C464" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3">
-      <c r="A465">
-        <v>3820</v>
-      </c>
-      <c r="B465" t="s">
-        <v>772</v>
-      </c>
-      <c r="C465" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3">
-      <c r="A466">
-        <v>3926</v>
-      </c>
-      <c r="B466" t="s">
-        <v>773</v>
-      </c>
-      <c r="C466" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3">
-      <c r="A467">
-        <v>785</v>
-      </c>
-      <c r="B467" t="s">
-        <v>775</v>
-      </c>
-      <c r="C467" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3">
-      <c r="A468">
-        <v>4084</v>
-      </c>
-      <c r="B468" t="s">
-        <v>776</v>
-      </c>
-      <c r="C468" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3">
-      <c r="A469">
-        <v>1030</v>
-      </c>
-      <c r="B469" t="s">
-        <v>777</v>
-      </c>
-      <c r="C469" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3">
-      <c r="A470">
-        <v>2925</v>
-      </c>
-      <c r="B470" t="s">
-        <v>778</v>
-      </c>
-      <c r="C470" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3">
-      <c r="A471">
-        <v>363</v>
-      </c>
-      <c r="B471" t="s">
-        <v>779</v>
-      </c>
-      <c r="C471" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3">
-      <c r="A472">
-        <v>4437</v>
-      </c>
-      <c r="B472" t="s">
-        <v>780</v>
-      </c>
-      <c r="C472" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3">
-      <c r="A473">
-        <v>1898</v>
-      </c>
-      <c r="B473" t="s">
-        <v>781</v>
-      </c>
-      <c r="C473" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3">
-      <c r="A474">
-        <v>395</v>
-      </c>
-      <c r="B474" t="s">
-        <v>783</v>
-      </c>
-      <c r="C474" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3">
-      <c r="A475">
-        <v>3507</v>
-      </c>
-      <c r="B475" t="s">
-        <v>785</v>
-      </c>
-      <c r="C475" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3">
-      <c r="A476">
-        <v>2080</v>
-      </c>
-      <c r="B476" t="s">
-        <v>786</v>
-      </c>
-      <c r="C476" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3">
-      <c r="A477">
-        <v>5514</v>
-      </c>
-      <c r="B477" t="s">
-        <v>787</v>
-      </c>
-      <c r="C477" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3">
-      <c r="A478">
-        <v>3281</v>
-      </c>
-      <c r="B478" t="s">
-        <v>789</v>
-      </c>
-      <c r="C478" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3">
-      <c r="A479">
-        <v>2120</v>
-      </c>
-      <c r="B479" t="s">
-        <v>791</v>
-      </c>
-      <c r="C479" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3">
-      <c r="A480">
-        <v>3734</v>
-      </c>
-      <c r="B480" t="s">
-        <v>793</v>
-      </c>
-      <c r="C480" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3">
-      <c r="A481">
-        <v>1193</v>
-      </c>
-      <c r="B481" t="s">
-        <v>794</v>
-      </c>
-      <c r="C481" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3">
-      <c r="A482">
-        <v>1082</v>
-      </c>
-      <c r="B482" t="s">
-        <v>796</v>
-      </c>
-      <c r="C482" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3">
-      <c r="A483">
-        <v>269</v>
-      </c>
-      <c r="B483" t="s">
-        <v>798</v>
-      </c>
-      <c r="C483" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3">
-      <c r="A484">
-        <v>4916</v>
-      </c>
-      <c r="B484" t="s">
-        <v>800</v>
-      </c>
-      <c r="C484" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3">
-      <c r="A485">
-        <v>7946</v>
-      </c>
-      <c r="B485" t="s">
-        <v>801</v>
-      </c>
-      <c r="C485" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3">
-      <c r="A486">
-        <v>24334</v>
-      </c>
-      <c r="B486" t="s">
-        <v>802</v>
-      </c>
-      <c r="C486" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3">
-      <c r="A487">
-        <v>4615</v>
-      </c>
-      <c r="B487" t="s">
-        <v>803</v>
-      </c>
-      <c r="C487" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3">
-      <c r="A488">
-        <v>2007</v>
-      </c>
-      <c r="B488" t="s">
-        <v>805</v>
-      </c>
-      <c r="C488" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3">
-      <c r="A489">
-        <v>1196</v>
-      </c>
-      <c r="B489" t="s">
-        <v>806</v>
-      </c>
-      <c r="C489" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3">
-      <c r="A490">
-        <v>5672</v>
-      </c>
-      <c r="B490" t="s">
-        <v>807</v>
-      </c>
-      <c r="C490" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3">
-      <c r="A491">
-        <v>4413</v>
-      </c>
-      <c r="B491" t="s">
-        <v>809</v>
-      </c>
-      <c r="C491" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3">
-      <c r="A492">
-        <v>50245</v>
-      </c>
-      <c r="B492" t="s">
-        <v>810</v>
-      </c>
-      <c r="C492" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3">
-      <c r="A493">
-        <v>4136</v>
-      </c>
-      <c r="B493" t="s">
-        <v>811</v>
-      </c>
-      <c r="C493" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3">
-      <c r="A494">
-        <v>87</v>
-      </c>
-      <c r="B494" t="s">
-        <v>813</v>
-      </c>
-      <c r="C494" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3">
-      <c r="A495">
-        <v>522</v>
-      </c>
-      <c r="B495" t="s">
-        <v>815</v>
-      </c>
-      <c r="C495" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3">
-      <c r="A496">
-        <v>1835</v>
-      </c>
-      <c r="B496" t="s">
-        <v>816</v>
-      </c>
-      <c r="C496" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3">
-      <c r="A497">
-        <v>4183</v>
-      </c>
-      <c r="B497" t="s">
-        <v>817</v>
-      </c>
-      <c r="C497" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3">
-      <c r="A498">
-        <v>3508</v>
-      </c>
-      <c r="B498" t="s">
-        <v>819</v>
-      </c>
-      <c r="C498" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3">
-      <c r="A499">
-        <v>63633</v>
-      </c>
-      <c r="B499" t="s">
-        <v>820</v>
-      </c>
-      <c r="C499" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3">
-      <c r="A500">
-        <v>2634</v>
-      </c>
-      <c r="B500" t="s">
-        <v>821</v>
-      </c>
-      <c r="C500" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3">
-      <c r="A501">
-        <v>2867</v>
-      </c>
-      <c r="B501" t="s">
-        <v>823</v>
-      </c>
-      <c r="C501" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3">
-      <c r="A502">
-        <v>886</v>
-      </c>
-      <c r="B502" t="s">
-        <v>825</v>
-      </c>
-      <c r="C502" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3">
-      <c r="A503">
-        <v>248</v>
-      </c>
-      <c r="B503" t="s">
-        <v>826</v>
-      </c>
-      <c r="C503" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3">
-      <c r="A504">
-        <v>967</v>
-      </c>
-      <c r="B504" t="s">
-        <v>828</v>
-      </c>
-      <c r="C504" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3">
-      <c r="A505">
-        <v>3244</v>
-      </c>
-      <c r="B505" t="s">
-        <v>830</v>
-      </c>
-      <c r="C505" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3">
-      <c r="A506">
-        <v>13554</v>
-      </c>
-      <c r="B506" t="s">
-        <v>831</v>
-      </c>
-      <c r="C506" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3">
-      <c r="A507">
-        <v>60</v>
-      </c>
-      <c r="B507" t="s">
-        <v>833</v>
-      </c>
-      <c r="C507" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3">
-      <c r="A508">
-        <v>5682</v>
-      </c>
-      <c r="B508" t="s">
-        <v>835</v>
-      </c>
-      <c r="C508" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3">
-      <c r="A509">
-        <v>9</v>
-      </c>
-      <c r="B509" t="s">
-        <v>836</v>
-      </c>
-      <c r="C509" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3">
-      <c r="A510">
-        <v>1163</v>
-      </c>
-      <c r="B510" t="s">
-        <v>838</v>
-      </c>
-      <c r="C510" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3">
-      <c r="A511">
-        <v>38</v>
-      </c>
-      <c r="B511" t="s">
-        <v>840</v>
-      </c>
-      <c r="C511" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3">
-      <c r="A512">
-        <v>3719</v>
-      </c>
-      <c r="B512" t="s">
-        <v>842</v>
-      </c>
-      <c r="C512" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3">
-      <c r="A513">
-        <v>1083</v>
-      </c>
-      <c r="B513" t="s">
-        <v>843</v>
-      </c>
-      <c r="C513" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3">
-      <c r="A514">
-        <v>2796</v>
-      </c>
-      <c r="B514" t="s">
-        <v>845</v>
-      </c>
-      <c r="C514" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3">
-      <c r="A515">
-        <v>1848</v>
-      </c>
-      <c r="B515" t="s">
-        <v>847</v>
-      </c>
-      <c r="C515" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3">
-      <c r="A516">
-        <v>558</v>
-      </c>
-      <c r="B516" t="s">
-        <v>849</v>
-      </c>
-      <c r="C516" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3">
-      <c r="A517">
-        <v>16286</v>
-      </c>
-      <c r="B517" t="s">
-        <v>851</v>
-      </c>
-      <c r="C517" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3">
-      <c r="A518">
-        <v>2323</v>
-      </c>
-      <c r="B518" t="s">
-        <v>852</v>
-      </c>
-      <c r="C518" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3">
-      <c r="A519">
-        <v>13703</v>
-      </c>
-      <c r="B519" t="s">
-        <v>853</v>
-      </c>
-      <c r="C519" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3">
-      <c r="A520">
-        <v>2066</v>
-      </c>
-      <c r="B520" t="s">
-        <v>854</v>
-      </c>
-      <c r="C520" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3">
-      <c r="A521">
-        <v>3821</v>
-      </c>
-      <c r="B521" t="s">
-        <v>856</v>
-      </c>
-      <c r="C521" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3">
-      <c r="A522">
-        <v>26151</v>
-      </c>
-      <c r="B522" t="s">
-        <v>857</v>
-      </c>
-      <c r="C522" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3">
-      <c r="A523">
-        <v>6451</v>
-      </c>
-      <c r="B523" t="s">
-        <v>858</v>
-      </c>
-      <c r="C523" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3">
-      <c r="A524">
-        <v>918</v>
-      </c>
-      <c r="B524" t="s">
-        <v>859</v>
-      </c>
-      <c r="C524" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3">
-      <c r="A525">
-        <v>3013</v>
-      </c>
-      <c r="B525" t="s">
-        <v>861</v>
-      </c>
-      <c r="C525" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3">
-      <c r="A526">
-        <v>9167</v>
-      </c>
-      <c r="B526" t="s">
-        <v>863</v>
-      </c>
-      <c r="C526" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3">
-      <c r="A527">
-        <v>1756</v>
-      </c>
-      <c r="B527" t="s">
-        <v>864</v>
-      </c>
-      <c r="C527" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3">
-      <c r="A528">
-        <v>714</v>
-      </c>
-      <c r="B528" t="s">
-        <v>866</v>
-      </c>
-      <c r="C528" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3">
-      <c r="A529">
-        <v>4525</v>
-      </c>
-      <c r="B529" t="s">
-        <v>868</v>
-      </c>
-      <c r="C529" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3">
-      <c r="A530">
-        <v>2435</v>
-      </c>
-      <c r="B530" t="s">
-        <v>869</v>
-      </c>
-      <c r="C530" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3">
-      <c r="A531">
-        <v>24626</v>
-      </c>
-      <c r="B531" t="s">
-        <v>870</v>
-      </c>
-      <c r="C531" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3">
-      <c r="A532">
-        <v>256</v>
-      </c>
-      <c r="B532" t="s">
-        <v>871</v>
-      </c>
-      <c r="C532" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3">
-      <c r="A533">
-        <v>8171</v>
-      </c>
-      <c r="B533" t="s">
-        <v>873</v>
-      </c>
-      <c r="C533" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3">
-      <c r="A534">
-        <v>122</v>
-      </c>
-      <c r="B534" t="s">
-        <v>874</v>
-      </c>
-      <c r="C534" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3">
-      <c r="A535">
-        <v>2837</v>
-      </c>
-      <c r="B535" t="s">
-        <v>875</v>
-      </c>
-      <c r="C535" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3">
-      <c r="A536">
-        <v>19758</v>
-      </c>
-      <c r="B536" t="s">
-        <v>876</v>
-      </c>
-      <c r="C536" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3">
-      <c r="A537">
-        <v>1095</v>
-      </c>
-      <c r="B537" t="s">
-        <v>878</v>
-      </c>
-      <c r="C537" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3">
-      <c r="A538">
-        <v>1451</v>
-      </c>
-      <c r="B538" t="s">
-        <v>880</v>
-      </c>
-      <c r="C538" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3">
-      <c r="A539">
-        <v>3713</v>
-      </c>
-      <c r="B539" t="s">
-        <v>882</v>
-      </c>
-      <c r="C539" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3">
-      <c r="A540">
-        <v>775</v>
-      </c>
-      <c r="B540" t="s">
-        <v>884</v>
-      </c>
-      <c r="C540" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3">
-      <c r="A541">
-        <v>1754</v>
-      </c>
-      <c r="B541" t="s">
-        <v>886</v>
-      </c>
-      <c r="C541" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3">
-      <c r="A542">
-        <v>4229</v>
-      </c>
-      <c r="B542" t="s">
-        <v>888</v>
-      </c>
-      <c r="C542" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3">
-      <c r="A543">
-        <v>3850</v>
-      </c>
-      <c r="B543" t="s">
-        <v>889</v>
-      </c>
-      <c r="C543" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3">
-      <c r="A544">
-        <v>1359</v>
-      </c>
-      <c r="B544" t="s">
-        <v>891</v>
-      </c>
-      <c r="C544" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3">
-      <c r="A545">
-        <v>14897</v>
-      </c>
-      <c r="B545" t="s">
-        <v>893</v>
-      </c>
-      <c r="C545" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3">
-      <c r="A546">
-        <v>452</v>
-      </c>
-      <c r="B546" t="s">
-        <v>894</v>
-      </c>
-      <c r="C546" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3">
-      <c r="A547">
-        <v>2728</v>
-      </c>
-      <c r="B547" t="s">
-        <v>896</v>
-      </c>
-      <c r="C547" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3">
-      <c r="A548">
-        <v>3390</v>
-      </c>
-      <c r="B548" t="s">
-        <v>898</v>
-      </c>
-      <c r="C548" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3">
-      <c r="A549">
-        <v>10766</v>
-      </c>
-      <c r="B549" t="s">
-        <v>900</v>
-      </c>
-      <c r="C549" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3">
-      <c r="A550">
-        <v>2695</v>
-      </c>
-      <c r="B550" t="s">
-        <v>901</v>
-      </c>
-      <c r="C550" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3">
-      <c r="A551">
-        <v>4656</v>
-      </c>
-      <c r="B551" t="s">
-        <v>903</v>
-      </c>
-      <c r="C551" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3">
-      <c r="A552">
-        <v>66104</v>
-      </c>
-      <c r="B552" t="s">
-        <v>905</v>
-      </c>
-      <c r="C552" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3">
-      <c r="A553">
-        <v>4472</v>
-      </c>
-      <c r="B553" t="s">
-        <v>906</v>
-      </c>
-      <c r="C553" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3">
-      <c r="A554">
-        <v>1355</v>
-      </c>
-      <c r="B554" t="s">
-        <v>907</v>
-      </c>
-      <c r="C554" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3">
-      <c r="A555">
-        <v>2569</v>
-      </c>
-      <c r="B555" t="s">
-        <v>909</v>
-      </c>
-      <c r="C555" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3">
-      <c r="A556">
-        <v>54312</v>
-      </c>
-      <c r="B556" t="s">
-        <v>911</v>
-      </c>
-      <c r="C556" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3">
-      <c r="A557">
-        <v>50234</v>
-      </c>
-      <c r="B557" t="s">
-        <v>912</v>
-      </c>
-      <c r="C557" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3">
-      <c r="A558">
-        <v>15259</v>
-      </c>
-      <c r="B558" t="s">
-        <v>913</v>
-      </c>
-      <c r="C558" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3">
-      <c r="A559">
-        <v>13522</v>
-      </c>
-      <c r="B559" t="s">
-        <v>914</v>
-      </c>
-      <c r="C559" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3">
-      <c r="A560">
-        <v>973</v>
-      </c>
-      <c r="B560" t="s">
-        <v>915</v>
-      </c>
-      <c r="C560" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3">
-      <c r="A561">
-        <v>37776</v>
-      </c>
-      <c r="B561" t="s">
-        <v>917</v>
-      </c>
-      <c r="C561" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3">
-      <c r="A562">
-        <v>953</v>
-      </c>
-      <c r="B562" t="s">
-        <v>918</v>
-      </c>
-      <c r="C562" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3">
-      <c r="A563">
-        <v>530</v>
-      </c>
-      <c r="B563" t="s">
-        <v>920</v>
-      </c>
-      <c r="C563" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3">
-      <c r="A564">
-        <v>8900</v>
-      </c>
-      <c r="B564" t="s">
-        <v>922</v>
-      </c>
-      <c r="C564" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3">
-      <c r="A565">
-        <v>3063</v>
-      </c>
-      <c r="B565" t="s">
-        <v>923</v>
-      </c>
-      <c r="C565" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3">
-      <c r="A566">
-        <v>723</v>
-      </c>
-      <c r="B566" t="s">
-        <v>924</v>
-      </c>
-      <c r="C566" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3">
-      <c r="A567">
-        <v>194</v>
-      </c>
-      <c r="B567" t="s">
-        <v>926</v>
-      </c>
-      <c r="C567" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3">
-      <c r="A568">
-        <v>423</v>
-      </c>
-      <c r="B568" t="s">
-        <v>928</v>
-      </c>
-      <c r="C568" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3">
-      <c r="A569">
-        <v>4714</v>
-      </c>
-      <c r="B569" t="s">
-        <v>930</v>
-      </c>
-      <c r="C569" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3">
-      <c r="A570">
-        <v>599</v>
-      </c>
-      <c r="B570" t="s">
-        <v>931</v>
-      </c>
-      <c r="C570" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3">
-      <c r="A571">
-        <v>3934</v>
-      </c>
-      <c r="B571" t="s">
-        <v>933</v>
-      </c>
-      <c r="C571" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3">
-      <c r="A572">
-        <v>1831</v>
-      </c>
-      <c r="B572" t="s">
-        <v>934</v>
-      </c>
-      <c r="C572" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3">
-      <c r="A573">
-        <v>2009</v>
-      </c>
-      <c r="B573" t="s">
-        <v>935</v>
-      </c>
-      <c r="C573" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3">
-      <c r="A574">
-        <v>19589</v>
-      </c>
-      <c r="B574" t="s">
-        <v>936</v>
-      </c>
-      <c r="C574" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3">
-      <c r="A575">
-        <v>4823</v>
-      </c>
-      <c r="B575" t="s">
-        <v>937</v>
-      </c>
-      <c r="C575" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3">
-      <c r="A576">
-        <v>4474</v>
-      </c>
-      <c r="B576" t="s">
-        <v>939</v>
-      </c>
-      <c r="C576" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3">
-      <c r="A577">
-        <v>3160</v>
-      </c>
-      <c r="B577" t="s">
-        <v>940</v>
-      </c>
-      <c r="C577" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3">
-      <c r="A578">
-        <v>903</v>
-      </c>
-      <c r="B578" t="s">
-        <v>942</v>
-      </c>
-      <c r="C578" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3">
-      <c r="A579">
-        <v>5859</v>
-      </c>
-      <c r="B579" t="s">
-        <v>944</v>
-      </c>
-      <c r="C579" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3">
-      <c r="A580">
-        <v>4337</v>
-      </c>
-      <c r="B580" t="s">
-        <v>945</v>
-      </c>
-      <c r="C580" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3">
-      <c r="A581">
-        <v>3547</v>
-      </c>
-      <c r="B581" t="s">
-        <v>947</v>
-      </c>
-      <c r="C581" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3">
-      <c r="A582">
-        <v>3471</v>
-      </c>
-      <c r="B582" t="s">
-        <v>948</v>
-      </c>
-      <c r="C582" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3">
-      <c r="A583">
-        <v>1037</v>
-      </c>
-      <c r="B583" t="s">
-        <v>949</v>
-      </c>
-      <c r="C583" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3">
-      <c r="A584">
-        <v>1177</v>
-      </c>
-      <c r="B584" t="s">
-        <v>951</v>
-      </c>
-      <c r="C584" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3">
-      <c r="A585">
-        <v>807</v>
-      </c>
-      <c r="B585" t="s">
-        <v>953</v>
-      </c>
-      <c r="C585" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3">
-      <c r="A586">
-        <v>33135</v>
-      </c>
-      <c r="B586" t="s">
-        <v>954</v>
-      </c>
-      <c r="C586" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3">
-      <c r="A587">
-        <v>938</v>
-      </c>
-      <c r="B587" t="s">
-        <v>955</v>
-      </c>
-      <c r="C587" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3">
-      <c r="A588">
-        <v>8052</v>
-      </c>
-      <c r="B588" t="s">
-        <v>957</v>
-      </c>
-      <c r="C588" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3">
-      <c r="A589">
-        <v>4620</v>
-      </c>
-      <c r="B589" t="s">
-        <v>959</v>
-      </c>
-      <c r="C589" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3">
-      <c r="A590">
-        <v>4843</v>
-      </c>
-      <c r="B590" t="s">
-        <v>961</v>
-      </c>
-      <c r="C590" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3">
-      <c r="A591">
-        <v>8045</v>
-      </c>
-      <c r="B591" t="s">
-        <v>963</v>
-      </c>
-      <c r="C591" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3">
-      <c r="A592">
-        <v>3046</v>
-      </c>
-      <c r="B592" t="s">
-        <v>964</v>
-      </c>
-      <c r="C592" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3">
-      <c r="A593">
-        <v>1242</v>
-      </c>
-      <c r="B593" t="s">
-        <v>966</v>
-      </c>
-      <c r="C593" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3">
-      <c r="A594">
-        <v>2056</v>
-      </c>
-      <c r="B594" t="s">
-        <v>967</v>
-      </c>
-      <c r="C594" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3">
-      <c r="A595">
-        <v>328</v>
-      </c>
-      <c r="B595" t="s">
-        <v>969</v>
-      </c>
-      <c r="C595" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3">
-      <c r="A596">
-        <v>16431</v>
-      </c>
-      <c r="B596" t="s">
-        <v>970</v>
-      </c>
-      <c r="C596" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3">
-      <c r="A597">
-        <v>3513</v>
-      </c>
-      <c r="B597" t="s">
-        <v>971</v>
-      </c>
-      <c r="C597" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3">
-      <c r="A598">
-        <v>7975</v>
-      </c>
-      <c r="B598" t="s">
-        <v>972</v>
-      </c>
-      <c r="C598" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3">
-      <c r="A599">
-        <v>337</v>
-      </c>
-      <c r="B599" t="s">
-        <v>974</v>
-      </c>
-      <c r="C599" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3">
-      <c r="A600">
-        <v>1533</v>
-      </c>
-      <c r="B600" t="s">
-        <v>975</v>
-      </c>
-      <c r="C600" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3">
-      <c r="A601">
-        <v>342</v>
-      </c>
-      <c r="B601" t="s">
-        <v>976</v>
-      </c>
-      <c r="C601" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3">
-      <c r="A602">
-        <v>2940</v>
-      </c>
-      <c r="B602" t="s">
-        <v>977</v>
-      </c>
-      <c r="C602" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3">
-      <c r="A603">
-        <v>1210</v>
-      </c>
-      <c r="B603" t="s">
-        <v>978</v>
-      </c>
-      <c r="C603" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3">
-      <c r="A604">
-        <v>19620</v>
-      </c>
-      <c r="B604" t="s">
-        <v>979</v>
-      </c>
-      <c r="C604" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3">
-      <c r="A605">
-        <v>2117</v>
-      </c>
-      <c r="B605" t="s">
-        <v>981</v>
-      </c>
-      <c r="C605" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3">
-      <c r="A606">
-        <v>319</v>
-      </c>
-      <c r="B606" t="s">
-        <v>982</v>
-      </c>
-      <c r="C606" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3">
-      <c r="A607">
-        <v>3447</v>
-      </c>
-      <c r="B607" t="s">
-        <v>984</v>
-      </c>
-      <c r="C607" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3">
-      <c r="A608">
-        <v>5110</v>
-      </c>
-      <c r="B608" t="s">
-        <v>985</v>
-      </c>
-      <c r="C608" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3">
-      <c r="A609">
-        <v>2654</v>
-      </c>
-      <c r="B609" t="s">
-        <v>986</v>
-      </c>
-      <c r="C609" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3">
-      <c r="A610">
-        <v>2653</v>
-      </c>
-      <c r="B610" t="s">
-        <v>987</v>
-      </c>
-      <c r="C610" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3">
-      <c r="A611">
-        <v>3543</v>
-      </c>
-      <c r="B611" t="s">
-        <v>988</v>
-      </c>
-      <c r="C611" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3">
-      <c r="A612">
-        <v>65970</v>
-      </c>
-      <c r="B612" t="s">
-        <v>989</v>
-      </c>
-      <c r="C612" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3">
-      <c r="A613">
-        <v>4911</v>
-      </c>
-      <c r="B613" t="s">
-        <v>990</v>
-      </c>
-      <c r="C613" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3">
-      <c r="A614">
-        <v>1072</v>
-      </c>
-      <c r="B614" t="s">
-        <v>991</v>
-      </c>
-      <c r="C614" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3">
-      <c r="A615">
-        <v>11044</v>
-      </c>
-      <c r="B615" t="s">
-        <v>992</v>
-      </c>
-      <c r="C615" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3">
-      <c r="A616">
-        <v>4138</v>
-      </c>
-      <c r="B616" t="s">
-        <v>993</v>
-      </c>
-      <c r="C616" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3">
-      <c r="A617">
-        <v>3664</v>
-      </c>
-      <c r="B617" t="s">
-        <v>994</v>
-      </c>
-      <c r="C617" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3">
-      <c r="A618">
-        <v>3446</v>
-      </c>
-      <c r="B618" t="s">
-        <v>995</v>
-      </c>
-      <c r="C618" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3">
-      <c r="A619">
-        <v>5051</v>
-      </c>
-      <c r="B619" t="s">
-        <v>996</v>
-      </c>
-      <c r="C619" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3">
-      <c r="A620">
-        <v>16723</v>
-      </c>
-      <c r="B620" t="s">
-        <v>997</v>
-      </c>
-      <c r="C620" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3">
-      <c r="A621">
-        <v>1580</v>
-      </c>
-      <c r="B621" t="s">
-        <v>999</v>
-      </c>
-      <c r="C621" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3">
-      <c r="A622">
-        <v>2818</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C622" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3">
-      <c r="A623">
-        <v>5575</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C623" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3">
-      <c r="A624" s="1">
-        <v>13344</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C624" t="s">
         <v>232</v>
       </c>
     </row>

--- a/backend/data/premier_league_players_history_clubs.xlsx
+++ b/backend/data/premier_league_players_history_clubs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="748">
   <si>
     <t>player_id</t>
   </si>
@@ -125,7 +125,7 @@
     <t>John Terry</t>
   </si>
   <si>
-    <t>Chelsea;Aston Villa</t>
+    <t>Chelsea</t>
   </si>
   <si>
     <t>Wayne Rooney</t>
@@ -530,9 +530,6 @@
     <t>César Azpilicueta</t>
   </si>
   <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
     <t>Robbie Keane</t>
   </si>
   <si>
@@ -1163,640 +1160,652 @@
     <t>Zat Knight</t>
   </si>
   <si>
+    <t>Fulham;Aston Villa;Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Riyad Mahrez</t>
+  </si>
+  <si>
+    <t>Leicester City;Manchester City</t>
+  </si>
+  <si>
+    <t>Mario Melchiot</t>
+  </si>
+  <si>
+    <t>Chelsea;Birmingham City;Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Kasper Schmeichel</t>
+  </si>
+  <si>
+    <t>Lee Carsley</t>
+  </si>
+  <si>
+    <t>Derby County;Blackburn Rovers;Coventry City;Everton;Birmingham City</t>
+  </si>
+  <si>
+    <t>Sebastian Larsson</t>
+  </si>
+  <si>
+    <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
+  </si>
+  <si>
+    <t>Charles N'Zogbia</t>
+  </si>
+  <si>
+    <t>Paul Merson</t>
+  </si>
+  <si>
+    <t>Arsenal;Middlesbrough;Aston Villa;Portsmouth</t>
+  </si>
+  <si>
+    <t>Robin van Persie</t>
+  </si>
+  <si>
+    <t>Arsenal;Manchester United</t>
+  </si>
+  <si>
+    <t>Jeffrey Schlupp</t>
+  </si>
+  <si>
+    <t>Norwich City;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Andy O'Brien</t>
+  </si>
+  <si>
+    <t>Christian Benteke</t>
+  </si>
+  <si>
+    <t>Aston Villa;Liverpool;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Robert Lee</t>
+  </si>
+  <si>
+    <t>Michael Keane</t>
+  </si>
+  <si>
+    <t>Everton;Burnley</t>
+  </si>
+  <si>
+    <t>Jermaine Jenas</t>
+  </si>
+  <si>
+    <t>Newcastle United;Tottenham Hotspur;Aston Villa;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Lucas Neill</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;West Ham United</t>
+  </si>
+  <si>
+    <t>Juan Mata</t>
+  </si>
+  <si>
+    <t>Chelsea;Manchester United</t>
+  </si>
+  <si>
+    <t>Dennis Wise</t>
+  </si>
+  <si>
+    <t>Jonjo Shelvey</t>
+  </si>
+  <si>
+    <t>Liverpool;Swansea City;Newcastle United;Nottingham Forest</t>
+  </si>
+  <si>
+    <t>James Collins</t>
+  </si>
+  <si>
+    <t>Aston Villa;West Ham United</t>
+  </si>
+  <si>
+    <t>Romelu Lukaku</t>
+  </si>
+  <si>
+    <t>Chelsea;West Bromwich Albion;Everton;Manchester United</t>
+  </si>
+  <si>
+    <t>Patrice Evra</t>
+  </si>
+  <si>
+    <t>Abdoulaye Doucouré</t>
+  </si>
+  <si>
+    <t>Watford;Everton</t>
+  </si>
+  <si>
+    <t>Warren Barton</t>
+  </si>
+  <si>
+    <t>Wimbledon;Newcastle United;Derby County</t>
+  </si>
+  <si>
+    <t>Ben Mee</t>
+  </si>
+  <si>
+    <t>Brentford;Burnley</t>
+  </si>
+  <si>
+    <t>Glenn Whelan</t>
+  </si>
+  <si>
+    <t>Ederson</t>
+  </si>
+  <si>
+    <t>Nathan Redmond</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Southampton</t>
+  </si>
+  <si>
+    <t>Dominic Matteo</t>
+  </si>
+  <si>
+    <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
+  </si>
+  <si>
+    <t>Nathaniel Clyne</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Liverpool;Southampton;Bournemouth</t>
+  </si>
+  <si>
+    <t>Darren Bent</t>
+  </si>
+  <si>
+    <t>Ipswich Town;Charlton Athletic;Tottenham Hotspur;Sunderland;Aston Villa;Fulham</t>
+  </si>
+  <si>
+    <t>Sergio Agüero</t>
+  </si>
+  <si>
+    <t>Henning Berg</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Manchester United</t>
+  </si>
+  <si>
+    <t>Steve McManaman</t>
+  </si>
+  <si>
+    <t>Mikaël Silvestre</t>
+  </si>
+  <si>
+    <t>Harry Kewell</t>
+  </si>
+  <si>
+    <t>Chris Powell</t>
+  </si>
+  <si>
+    <t>Leicester City;Charlton Athletic</t>
+  </si>
+  <si>
+    <t>Eric Dier</t>
+  </si>
+  <si>
+    <t>Branislav Ivanovic</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion;Chelsea</t>
+  </si>
+  <si>
+    <t>Jason Wilcox</t>
+  </si>
+  <si>
+    <t>Leicester City;Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Kanu</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>James McCarthy</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Everton;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Chris Wood</t>
+  </si>
+  <si>
+    <t>Lee Cattermole</t>
+  </si>
+  <si>
+    <t>Richarlison</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;Everton</t>
+  </si>
+  <si>
+    <t>Matthew Le Tissier</t>
+  </si>
+  <si>
+    <t>Adama Traoré</t>
+  </si>
+  <si>
+    <t>Aston Villa;Middlesbrough;Wolverhampton Wanderers;Fulham;West Ham United</t>
+  </si>
+  <si>
+    <t>Joey Barton</t>
+  </si>
+  <si>
+    <t>Chris Brunt</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Duncan Ferguson</t>
+  </si>
+  <si>
+    <t>Michail Antonio</t>
+  </si>
+  <si>
+    <t>Dominic Calvert-Lewin</t>
+  </si>
+  <si>
+    <t>Leeds United;Everton</t>
+  </si>
+  <si>
+    <t>Dietmar Hamann</t>
+  </si>
+  <si>
+    <t>Ledley King</t>
+  </si>
+  <si>
+    <t>Bacary Sagna</t>
+  </si>
+  <si>
+    <t>Colin Cooper</t>
+  </si>
+  <si>
+    <t>Nottingham Forest;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Robert Green</t>
+  </si>
+  <si>
+    <t>Norwich City;West Ham United;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>David Batty</t>
+  </si>
+  <si>
+    <t>Leeds United;Blackburn Rovers;Newcastle United</t>
+  </si>
+  <si>
+    <t>David Beckham</t>
+  </si>
+  <si>
+    <t>Tony Hibbert</t>
+  </si>
+  <si>
+    <t>Adam Johnson</t>
+  </si>
+  <si>
+    <t>Middlesbrough;Manchester City;Sunderland</t>
+  </si>
+  <si>
+    <t>Vincent Kompany</t>
+  </si>
+  <si>
+    <t>Kieran Richardson</t>
+  </si>
+  <si>
+    <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
+  </si>
+  <si>
+    <t>Darius Vassell</t>
+  </si>
+  <si>
+    <t>Callum Wilson</t>
+  </si>
+  <si>
+    <t>Des Walker</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday</t>
+  </si>
+  <si>
+    <t>Fernandinho</t>
+  </si>
+  <si>
+    <t>Jason Euell</t>
+  </si>
+  <si>
+    <t>Wimbledon;Charlton Athletic;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Sadio Mané</t>
+  </si>
+  <si>
+    <t>Kevin Phillips</t>
+  </si>
+  <si>
+    <t>Sunderland;Southampton;Aston Villa;West Bromwich Albion;Birmingham City;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Steve Stone</t>
+  </si>
+  <si>
+    <t>Nottingham Forest;Aston Villa;Leicester City;Portsmouth</t>
+  </si>
+  <si>
+    <t>Ryan Bertrand</t>
+  </si>
+  <si>
+    <t>Aaron Ramsey</t>
+  </si>
+  <si>
+    <t>Cardiff City;Arsenal</t>
+  </si>
+  <si>
+    <t>Gary Pallister</t>
+  </si>
+  <si>
+    <t>Carlton Palmer</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday;Leeds United;Coventry City;Southampton</t>
+  </si>
+  <si>
+    <t>Craig Gardner</t>
+  </si>
+  <si>
+    <t>Aston Villa;Birmingham City;Sunderland;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Marouane Fellaini</t>
+  </si>
+  <si>
+    <t>Trent Alexander-Arnold</t>
+  </si>
+  <si>
+    <t>Morten Pedersen</t>
+  </si>
+  <si>
+    <t>Thierry Henry</t>
+  </si>
+  <si>
+    <t>Jay Rodriguez</t>
+  </si>
+  <si>
+    <t>Burnley;Southampton;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Liam Ridgewell</t>
+  </si>
+  <si>
+    <t>Aston Villa;Birmingham City;West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>David Wetherall</t>
+  </si>
+  <si>
+    <t>Roberto Firmino</t>
+  </si>
+  <si>
+    <t>Asmir Begovic</t>
+  </si>
+  <si>
+    <t>Olivier Giroud</t>
+  </si>
+  <si>
+    <t>Laurent Koscielny</t>
+  </si>
+  <si>
+    <t>John Stones</t>
+  </si>
+  <si>
+    <t>Everton;Manchester City</t>
+  </si>
+  <si>
+    <t>Chris Sutton</t>
+  </si>
+  <si>
+    <t>Norwich City;Blackburn Rovers;Chelsea;Birmingham City;Aston Villa</t>
+  </si>
+  <si>
+    <t>Tony Adams</t>
+  </si>
+  <si>
+    <t>Alisson Becker</t>
+  </si>
+  <si>
+    <t>Didier Drogba</t>
+  </si>
+  <si>
+    <t>Pierre-Emile Højbjerg</t>
+  </si>
+  <si>
+    <t>Southampton;Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Adam Smith</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Granit Xhaka</t>
+  </si>
+  <si>
+    <t>Sunderland;Arsenal</t>
+  </si>
+  <si>
+    <t>Richard Shaw</t>
+  </si>
+  <si>
+    <t>Crystal Palace;Coventry City</t>
+  </si>
+  <si>
+    <t>Jonathan Greening</t>
+  </si>
+  <si>
+    <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
+  </si>
+  <si>
+    <t>Idrissa Gueye</t>
+  </si>
+  <si>
+    <t>Bobby Zamora</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur;West Ham United;Fulham;Queens Park Rangers</t>
+  </si>
+  <si>
+    <t>Yakubu</t>
+  </si>
+  <si>
+    <t>Coventry City</t>
+  </si>
+  <si>
+    <t>Lee Hendrie</t>
+  </si>
+  <si>
+    <t>Nemanja Matic</t>
+  </si>
+  <si>
+    <t>Matt Oakley</t>
+  </si>
+  <si>
+    <t>Ricardo Gardner</t>
+  </si>
+  <si>
+    <t>Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>David Dunn</t>
+  </si>
+  <si>
+    <t>Niall Quinn</t>
+  </si>
+  <si>
+    <t>Coventry City;Arsenal;Manchester City;Sunderland</t>
+  </si>
+  <si>
+    <t>Nathan Aké</t>
+  </si>
+  <si>
+    <t>Manchester City;Bournemouth</t>
+  </si>
+  <si>
+    <t>Lucas Digne</t>
+  </si>
+  <si>
+    <t>Aston Villa;Everton</t>
+  </si>
+  <si>
+    <t>John Obi Mikel</t>
+  </si>
+  <si>
+    <t>Stoke City;Chelsea</t>
+  </si>
+  <si>
+    <t>Andy Carroll</t>
+  </si>
+  <si>
+    <t>Newcastle United;Liverpool;West Ham United</t>
+  </si>
+  <si>
+    <t>Muzzy Izzet</t>
+  </si>
+  <si>
+    <t>Ian Taylor</t>
+  </si>
+  <si>
+    <t>Derby County;Aston Villa</t>
+  </si>
+  <si>
+    <t>Kurt Zouma</t>
+  </si>
+  <si>
+    <t>Chelsea;Stoke City;Everton;West Ham United</t>
+  </si>
+  <si>
+    <t>Lucas Leiva</t>
+  </si>
+  <si>
+    <t>Neil Sullivan</t>
+  </si>
+  <si>
+    <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
+  </si>
+  <si>
+    <t>Brett Emerton</t>
+  </si>
+  <si>
+    <t>Eden Hazard</t>
+  </si>
+  <si>
+    <t>Bernd Leno</t>
+  </si>
+  <si>
+    <t>Fulham;Arsenal</t>
+  </si>
+  <si>
+    <t>Dwight McNeil</t>
+  </si>
+  <si>
+    <t>Simon Mignolet</t>
+  </si>
+  <si>
+    <t>Sunderland;Liverpool</t>
+  </si>
+  <si>
+    <t>Stephen Ireland</t>
+  </si>
+  <si>
+    <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
+  </si>
+  <si>
+    <t>Robbie Earle</t>
+  </si>
+  <si>
+    <t>Wimbledon</t>
+  </si>
+  <si>
+    <t>Jonathan Woodgate</t>
+  </si>
+  <si>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Nick Pope</t>
+  </si>
+  <si>
+    <t>Newcastle United;Burnley</t>
+  </si>
+  <si>
+    <t>Noel Whelan</t>
+  </si>
+  <si>
+    <t>Leeds United;Coventry City;Middlesbrough</t>
+  </si>
+  <si>
+    <t>Stéphane Henchoz</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers;Liverpool;Wigan Athletic</t>
+  </si>
+  <si>
+    <t>Mousa Dembélé</t>
+  </si>
+  <si>
+    <t>Francis Benali</t>
+  </si>
+  <si>
+    <t>Tom Cleverley</t>
+  </si>
+  <si>
+    <t>Wigan Athletic;Manchester United;Aston Villa;Everton;Watford</t>
+  </si>
+  <si>
+    <t>El Hadji Diouf</t>
+  </si>
+  <si>
+    <t>Tom Huddlestone</t>
+  </si>
+  <si>
+    <t>Hull City</t>
+  </si>
+  <si>
+    <t>Martin Skrtel</t>
+  </si>
+  <si>
+    <t>Freddie Ljungberg</t>
+  </si>
+  <si>
+    <t>Ashley Williams</t>
+  </si>
+  <si>
+    <t>Pascal Groß</t>
+  </si>
+  <si>
+    <t>Emmanuel Adebayor</t>
+  </si>
+  <si>
+    <t>Arsenal;Manchester City;Tottenham Hotspur;Crystal Palace</t>
+  </si>
+  <si>
+    <t>Scott Dann</t>
+  </si>
+  <si>
     <t>Reading</t>
   </si>
   <si>
-    <t>Riyad Mahrez</t>
-  </si>
-  <si>
-    <t>Leicester City;Manchester City</t>
-  </si>
-  <si>
-    <t>Mario Melchiot</t>
-  </si>
-  <si>
-    <t>Chelsea;Birmingham City;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Kasper Schmeichel</t>
-  </si>
-  <si>
-    <t>Lee Carsley</t>
-  </si>
-  <si>
-    <t>Derby County;Blackburn Rovers;Coventry City;Everton;Birmingham City</t>
-  </si>
-  <si>
-    <t>Sebastian Larsson</t>
-  </si>
-  <si>
-    <t>Arsenal;Birmingham City;Sunderland;Hull City</t>
-  </si>
-  <si>
-    <t>Charles N'Zogbia</t>
-  </si>
-  <si>
-    <t>Paul Merson</t>
-  </si>
-  <si>
-    <t>Arsenal;Middlesbrough;Aston Villa;Portsmouth</t>
-  </si>
-  <si>
-    <t>Robin van Persie</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester United</t>
-  </si>
-  <si>
-    <t>Jeffrey Schlupp</t>
-  </si>
-  <si>
-    <t>Norwich City;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Andy O'Brien</t>
-  </si>
-  <si>
-    <t>Christian Benteke</t>
-  </si>
-  <si>
-    <t>Aston Villa;Liverpool;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Robert Lee</t>
-  </si>
-  <si>
-    <t>Michael Keane</t>
-  </si>
-  <si>
-    <t>Everton;Burnley</t>
-  </si>
-  <si>
-    <t>Jermaine Jenas</t>
-  </si>
-  <si>
-    <t>Newcastle United;Tottenham Hotspur;Aston Villa;Queens Park Rangers</t>
-  </si>
-  <si>
-    <t>Lucas Neill</t>
-  </si>
-  <si>
-    <t>Juan Mata</t>
-  </si>
-  <si>
-    <t>Chelsea;Manchester United</t>
-  </si>
-  <si>
-    <t>Dennis Wise</t>
-  </si>
-  <si>
-    <t>Jonjo Shelvey</t>
-  </si>
-  <si>
-    <t>Liverpool;Swansea City;Newcastle United;Nottingham Forest</t>
-  </si>
-  <si>
-    <t>James Collins</t>
-  </si>
-  <si>
-    <t>Ipswich Town;West Ham United</t>
-  </si>
-  <si>
-    <t>Romelu Lukaku</t>
-  </si>
-  <si>
-    <t>Chelsea;West Bromwich Albion;Everton;Manchester United</t>
-  </si>
-  <si>
-    <t>Patrice Evra</t>
-  </si>
-  <si>
-    <t>Abdoulaye Doucouré</t>
-  </si>
-  <si>
-    <t>Watford;Everton</t>
-  </si>
-  <si>
-    <t>Warren Barton</t>
-  </si>
-  <si>
-    <t>Wimbledon;Newcastle United;Derby County</t>
-  </si>
-  <si>
-    <t>Ben Mee</t>
-  </si>
-  <si>
-    <t>Sheffield United;Burnley</t>
-  </si>
-  <si>
-    <t>Glenn Whelan</t>
-  </si>
-  <si>
-    <t>Ederson</t>
-  </si>
-  <si>
-    <t>Nathan Redmond</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Southampton</t>
-  </si>
-  <si>
-    <t>Dominic Matteo</t>
-  </si>
-  <si>
-    <t>Liverpool;Leeds United;Blackburn Rovers;Stoke City</t>
-  </si>
-  <si>
-    <t>Nathaniel Clyne</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Liverpool</t>
-  </si>
-  <si>
-    <t>Darren Bent</t>
-  </si>
-  <si>
-    <t>Ipswich Town;Charlton Athletic;Tottenham Hotspur;Sunderland;Aston Villa;Fulham</t>
-  </si>
-  <si>
-    <t>Sergio Agüero</t>
-  </si>
-  <si>
-    <t>Henning Berg</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Manchester United</t>
-  </si>
-  <si>
-    <t>Steve McManaman</t>
-  </si>
-  <si>
-    <t>Mikaël Silvestre</t>
-  </si>
-  <si>
-    <t>Harry Kewell</t>
-  </si>
-  <si>
-    <t>Chris Powell</t>
-  </si>
-  <si>
-    <t>Leicester City;Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Eric Dier</t>
-  </si>
-  <si>
-    <t>Branislav Ivanovic</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion;Chelsea</t>
-  </si>
-  <si>
-    <t>Jason Wilcox</t>
-  </si>
-  <si>
-    <t>Leicester City;Blackburn Rovers</t>
-  </si>
-  <si>
-    <t>Kanu</t>
-  </si>
-  <si>
-    <t>Portsmouth</t>
-  </si>
-  <si>
-    <t>James McCarthy</t>
-  </si>
-  <si>
-    <t>Wigan Athletic;Everton;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Chris Wood</t>
-  </si>
-  <si>
-    <t>Lee Cattermole</t>
-  </si>
-  <si>
-    <t>Richarlison</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur;Everton</t>
-  </si>
-  <si>
-    <t>Matthew Le Tissier</t>
-  </si>
-  <si>
-    <t>Adama Traoré</t>
-  </si>
-  <si>
-    <t>West Ham United;Fulham</t>
-  </si>
-  <si>
-    <t>Joey Barton</t>
-  </si>
-  <si>
-    <t>Chris Brunt</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Duncan Ferguson</t>
-  </si>
-  <si>
-    <t>Michail Antonio</t>
-  </si>
-  <si>
-    <t>Dominic Calvert-Lewin</t>
-  </si>
-  <si>
-    <t>Leeds United;Everton</t>
-  </si>
-  <si>
-    <t>Dietmar Hamann</t>
-  </si>
-  <si>
-    <t>Ledley King</t>
-  </si>
-  <si>
-    <t>Bacary Sagna</t>
-  </si>
-  <si>
-    <t>Colin Cooper</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Robert Green</t>
-  </si>
-  <si>
-    <t>David Batty</t>
-  </si>
-  <si>
-    <t>Leeds United;Blackburn Rovers;Newcastle United</t>
-  </si>
-  <si>
-    <t>David Beckham</t>
-  </si>
-  <si>
-    <t>Tony Hibbert</t>
-  </si>
-  <si>
-    <t>Adam Johnson</t>
-  </si>
-  <si>
-    <t>Middlesbrough;Manchester City;Sunderland</t>
-  </si>
-  <si>
-    <t>Vincent Kompany</t>
-  </si>
-  <si>
-    <t>Kieran Richardson</t>
-  </si>
-  <si>
-    <t>Manchester United;West Bromwich Albion;Sunderland;Fulham;Aston Villa</t>
-  </si>
-  <si>
-    <t>Darius Vassell</t>
-  </si>
-  <si>
-    <t>Callum Wilson</t>
-  </si>
-  <si>
-    <t>Des Walker</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Fernandinho</t>
-  </si>
-  <si>
-    <t>Jason Euell</t>
-  </si>
-  <si>
-    <t>Wimbledon;Charlton Athletic;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Sadio Mané</t>
-  </si>
-  <si>
-    <t>Kevin Phillips</t>
-  </si>
-  <si>
-    <t>Sunderland;Southampton;Aston Villa;West Bromwich Albion;Birmingham City;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Steve Stone</t>
-  </si>
-  <si>
-    <t>Nottingham Forest;Aston Villa;Leicester City;Portsmouth</t>
-  </si>
-  <si>
-    <t>Ryan Bertrand</t>
-  </si>
-  <si>
-    <t>Aaron Ramsey</t>
-  </si>
-  <si>
-    <t>Cardiff City;Arsenal</t>
-  </si>
-  <si>
-    <t>Gary Pallister</t>
-  </si>
-  <si>
-    <t>Carlton Palmer</t>
-  </si>
-  <si>
-    <t>Sheffield Wednesday;Leeds United;Coventry City;Southampton</t>
-  </si>
-  <si>
-    <t>Craig Gardner</t>
-  </si>
-  <si>
-    <t>Aston Villa;Birmingham City;Sunderland;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Marouane Fellaini</t>
-  </si>
-  <si>
-    <t>Trent Alexander-Arnold</t>
-  </si>
-  <si>
-    <t>Morten Pedersen</t>
-  </si>
-  <si>
-    <t>Thierry Henry</t>
-  </si>
-  <si>
-    <t>Jay Rodriguez</t>
-  </si>
-  <si>
-    <t>Burnley;Southampton;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Liam Ridgewell</t>
-  </si>
-  <si>
-    <t>Aston Villa;Birmingham City;West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>David Wetherall</t>
-  </si>
-  <si>
-    <t>Roberto Firmino</t>
-  </si>
-  <si>
-    <t>Asmir Begovic</t>
-  </si>
-  <si>
-    <t>Olivier Giroud</t>
-  </si>
-  <si>
-    <t>Laurent Koscielny</t>
-  </si>
-  <si>
-    <t>John Stones</t>
-  </si>
-  <si>
-    <t>Everton;Manchester City</t>
-  </si>
-  <si>
-    <t>Chris Sutton</t>
-  </si>
-  <si>
-    <t>Norwich City;Blackburn Rovers;Chelsea;Birmingham City;Aston Villa</t>
-  </si>
-  <si>
-    <t>Tony Adams</t>
-  </si>
-  <si>
-    <t>Alisson Becker</t>
-  </si>
-  <si>
-    <t>Didier Drogba</t>
-  </si>
-  <si>
-    <t>Pierre-Emile Højbjerg</t>
-  </si>
-  <si>
-    <t>Southampton;Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>Adam Smith</t>
-  </si>
-  <si>
-    <t>Bournemouth</t>
-  </si>
-  <si>
-    <t>Granit Xhaka</t>
-  </si>
-  <si>
-    <t>Sunderland;Arsenal</t>
-  </si>
-  <si>
-    <t>Richard Shaw</t>
-  </si>
-  <si>
-    <t>Crystal Palace;Coventry City</t>
-  </si>
-  <si>
-    <t>Jonathan Greening</t>
-  </si>
-  <si>
-    <t>Manchester United;Middlesbrough;West Bromwich Albion;Fulham</t>
-  </si>
-  <si>
-    <t>Idrissa Gueye</t>
-  </si>
-  <si>
-    <t>Bobby Zamora</t>
-  </si>
-  <si>
-    <t>Yakubu</t>
-  </si>
-  <si>
-    <t>Coventry City</t>
-  </si>
-  <si>
-    <t>Lee Hendrie</t>
-  </si>
-  <si>
-    <t>Nemanja Matic</t>
-  </si>
-  <si>
-    <t>Matt Oakley</t>
-  </si>
-  <si>
-    <t>Ricardo Gardner</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers</t>
-  </si>
-  <si>
-    <t>David Dunn</t>
-  </si>
-  <si>
-    <t>Niall Quinn</t>
-  </si>
-  <si>
-    <t>Coventry City;Arsenal;Manchester City;Sunderland</t>
-  </si>
-  <si>
-    <t>Nathan Aké</t>
-  </si>
-  <si>
-    <t>Manchester City;Bournemouth</t>
-  </si>
-  <si>
-    <t>Lucas Digne</t>
-  </si>
-  <si>
-    <t>Aston Villa;Everton</t>
-  </si>
-  <si>
-    <t>John Obi Mikel</t>
-  </si>
-  <si>
-    <t>Stoke City;Chelsea</t>
-  </si>
-  <si>
-    <t>Andy Carroll</t>
-  </si>
-  <si>
-    <t>Newcastle United;Liverpool;West Ham United</t>
-  </si>
-  <si>
-    <t>Muzzy Izzet</t>
-  </si>
-  <si>
-    <t>Ian Taylor</t>
-  </si>
-  <si>
-    <t>Derby County;Aston Villa</t>
-  </si>
-  <si>
-    <t>Kurt Zouma</t>
-  </si>
-  <si>
-    <t>Chelsea;Stoke City;Everton;West Ham United</t>
-  </si>
-  <si>
-    <t>Lucas Leiva</t>
-  </si>
-  <si>
-    <t>Neil Sullivan</t>
-  </si>
-  <si>
-    <t>Wimbledon;Tottenham Hotspur;Chelsea;Leeds United</t>
-  </si>
-  <si>
-    <t>Brett Emerton</t>
-  </si>
-  <si>
-    <t>Eden Hazard</t>
-  </si>
-  <si>
-    <t>Bernd Leno</t>
-  </si>
-  <si>
-    <t>Fulham;Arsenal</t>
-  </si>
-  <si>
-    <t>Dwight McNeil</t>
-  </si>
-  <si>
-    <t>Simon Mignolet</t>
-  </si>
-  <si>
-    <t>Sunderland;Liverpool</t>
-  </si>
-  <si>
-    <t>Stephen Ireland</t>
-  </si>
-  <si>
-    <t>Manchester City;Aston Villa;Newcastle United;Stoke City</t>
-  </si>
-  <si>
-    <t>Robbie Earle</t>
-  </si>
-  <si>
-    <t>Wimbledon</t>
-  </si>
-  <si>
-    <t>Jonathan Woodgate</t>
-  </si>
-  <si>
-    <t>Middlesbrough</t>
-  </si>
-  <si>
-    <t>Nick Pope</t>
-  </si>
-  <si>
-    <t>Newcastle United;Burnley</t>
-  </si>
-  <si>
-    <t>Noel Whelan</t>
-  </si>
-  <si>
-    <t>Leeds United;Coventry City;Middlesbrough</t>
-  </si>
-  <si>
-    <t>Stéphane Henchoz</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers;Liverpool;Wigan Athletic</t>
-  </si>
-  <si>
-    <t>Mousa Dembélé</t>
-  </si>
-  <si>
-    <t>Francis Benali</t>
-  </si>
-  <si>
-    <t>Tom Cleverley</t>
-  </si>
-  <si>
-    <t>Watford</t>
-  </si>
-  <si>
-    <t>El Hadji Diouf</t>
-  </si>
-  <si>
-    <t>Tom Huddlestone</t>
-  </si>
-  <si>
-    <t>Hull City</t>
-  </si>
-  <si>
-    <t>Martin Skrtel</t>
-  </si>
-  <si>
-    <t>Freddie Ljungberg</t>
-  </si>
-  <si>
-    <t>Ashley Williams</t>
-  </si>
-  <si>
-    <t>Pascal Groß</t>
-  </si>
-  <si>
-    <t>Emmanuel Adebayor</t>
-  </si>
-  <si>
-    <t>Arsenal;Manchester City;Tottenham Hotspur;Crystal Palace</t>
-  </si>
-  <si>
-    <t>Scott Dann</t>
-  </si>
-  <si>
     <t>Gabriel Jesus</t>
   </si>
   <si>
     <t>Danny Ings</t>
   </si>
   <si>
-    <t>Sheffield United</t>
+    <t>Burnley;Liverpool;Southampton;Aston Villa;West Ham United</t>
   </si>
   <si>
     <t>Stuart Ripley</t>
@@ -1886,7 +1895,7 @@
     <t>Dean Whitehead</t>
   </si>
   <si>
-    <t>Huddersfield Town</t>
+    <t>Sunderland;Stoke City;Huddersfield Town</t>
   </si>
   <si>
     <t>Tugay</t>
@@ -2057,6 +2066,9 @@
     <t>Jack Grealish</t>
   </si>
   <si>
+    <t>Aston Villa;Manchester City;Everton</t>
+  </si>
+  <si>
     <t>Neville Southall</t>
   </si>
   <si>
@@ -2201,9 +2213,6 @@
     <t>Steve Bruce</t>
   </si>
   <si>
-    <t>Birmingham City;Manchester United</t>
-  </si>
-  <si>
     <t>Nani</t>
   </si>
   <si>
@@ -2253,6 +2262,9 @@
   </si>
   <si>
     <t>Tomasz Kuszczak</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion;Manchester United</t>
   </si>
   <si>
     <t>Benjamin Mendy</t>
@@ -4213,7 +4225,7 @@
         <v>166</v>
       </c>
       <c r="C87" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4221,10 +4233,10 @@
         <v>1692</v>
       </c>
       <c r="B88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" t="s">
         <v>168</v>
-      </c>
-      <c r="C88" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4232,10 +4244,10 @@
         <v>1515</v>
       </c>
       <c r="B89" t="s">
+        <v>169</v>
+      </c>
+      <c r="C89" t="s">
         <v>170</v>
-      </c>
-      <c r="C89" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4243,10 +4255,10 @@
         <v>706</v>
       </c>
       <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" t="s">
         <v>172</v>
-      </c>
-      <c r="C90" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4254,10 +4266,10 @@
         <v>3206</v>
       </c>
       <c r="B91" t="s">
+        <v>173</v>
+      </c>
+      <c r="C91" t="s">
         <v>174</v>
-      </c>
-      <c r="C91" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4265,10 +4277,10 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
+        <v>175</v>
+      </c>
+      <c r="C92" t="s">
         <v>176</v>
-      </c>
-      <c r="C92" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4276,10 +4288,10 @@
         <v>569</v>
       </c>
       <c r="B93" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" t="s">
         <v>178</v>
-      </c>
-      <c r="C93" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4287,10 +4299,10 @@
         <v>8979</v>
       </c>
       <c r="B94" t="s">
+        <v>179</v>
+      </c>
+      <c r="C94" t="s">
         <v>180</v>
-      </c>
-      <c r="C94" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4298,10 +4310,10 @@
         <v>1943</v>
       </c>
       <c r="B95" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" t="s">
         <v>182</v>
-      </c>
-      <c r="C95" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4309,10 +4321,10 @@
         <v>78</v>
       </c>
       <c r="B96" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" t="s">
         <v>184</v>
-      </c>
-      <c r="C96" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -4320,10 +4332,10 @@
         <v>3143</v>
       </c>
       <c r="B97" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" t="s">
         <v>186</v>
-      </c>
-      <c r="C97" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4331,10 +4343,10 @@
         <v>2078</v>
       </c>
       <c r="B98" t="s">
+        <v>187</v>
+      </c>
+      <c r="C98" t="s">
         <v>188</v>
-      </c>
-      <c r="C98" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -4342,10 +4354,10 @@
         <v>972</v>
       </c>
       <c r="B99" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" t="s">
         <v>190</v>
-      </c>
-      <c r="C99" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -4353,10 +4365,10 @@
         <v>8143</v>
       </c>
       <c r="B100" t="s">
+        <v>191</v>
+      </c>
+      <c r="C100" t="s">
         <v>192</v>
-      </c>
-      <c r="C100" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4364,7 +4376,7 @@
         <v>4999</v>
       </c>
       <c r="B101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C101" t="s">
         <v>145</v>
@@ -4375,10 +4387,10 @@
         <v>5140</v>
       </c>
       <c r="B102" t="s">
+        <v>194</v>
+      </c>
+      <c r="C102" t="s">
         <v>195</v>
-      </c>
-      <c r="C102" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -4386,10 +4398,10 @@
         <v>1371</v>
       </c>
       <c r="B103" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" t="s">
         <v>197</v>
-      </c>
-      <c r="C103" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -4397,10 +4409,10 @@
         <v>1005</v>
       </c>
       <c r="B104" t="s">
+        <v>198</v>
+      </c>
+      <c r="C104" t="s">
         <v>199</v>
-      </c>
-      <c r="C104" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -4408,10 +4420,10 @@
         <v>528</v>
       </c>
       <c r="B105" t="s">
+        <v>200</v>
+      </c>
+      <c r="C105" t="s">
         <v>201</v>
-      </c>
-      <c r="C105" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -4419,7 +4431,7 @@
         <v>315</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C106" t="s">
         <v>8</v>
@@ -4430,10 +4442,10 @@
         <v>10458</v>
       </c>
       <c r="B107" t="s">
+        <v>203</v>
+      </c>
+      <c r="C107" t="s">
         <v>204</v>
-      </c>
-      <c r="C107" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -4441,10 +4453,10 @@
         <v>4748</v>
       </c>
       <c r="B108" t="s">
+        <v>205</v>
+      </c>
+      <c r="C108" t="s">
         <v>206</v>
-      </c>
-      <c r="C108" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -4452,10 +4464,10 @@
         <v>70</v>
       </c>
       <c r="B109" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109" t="s">
         <v>208</v>
-      </c>
-      <c r="C109" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -4463,10 +4475,10 @@
         <v>1208</v>
       </c>
       <c r="B110" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" t="s">
         <v>210</v>
-      </c>
-      <c r="C110" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -4474,10 +4486,10 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
+        <v>211</v>
+      </c>
+      <c r="C111" t="s">
         <v>212</v>
-      </c>
-      <c r="C111" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -4485,10 +4497,10 @@
         <v>2413</v>
       </c>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -4496,10 +4508,10 @@
         <v>694</v>
       </c>
       <c r="B113" t="s">
+        <v>214</v>
+      </c>
+      <c r="C113" t="s">
         <v>215</v>
-      </c>
-      <c r="C113" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -4507,10 +4519,10 @@
         <v>1757</v>
       </c>
       <c r="B114" t="s">
+        <v>216</v>
+      </c>
+      <c r="C114" t="s">
         <v>217</v>
-      </c>
-      <c r="C114" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -4518,10 +4530,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
+        <v>218</v>
+      </c>
+      <c r="C115" t="s">
         <v>219</v>
-      </c>
-      <c r="C115" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -4529,10 +4541,10 @@
         <v>2542</v>
       </c>
       <c r="B116" t="s">
+        <v>220</v>
+      </c>
+      <c r="C116" t="s">
         <v>221</v>
-      </c>
-      <c r="C116" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -4540,10 +4552,10 @@
         <v>3285</v>
       </c>
       <c r="B117" t="s">
+        <v>222</v>
+      </c>
+      <c r="C117" t="s">
         <v>223</v>
-      </c>
-      <c r="C117" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -4551,10 +4563,10 @@
         <v>5178</v>
       </c>
       <c r="B118" t="s">
+        <v>224</v>
+      </c>
+      <c r="C118" t="s">
         <v>225</v>
-      </c>
-      <c r="C118" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -4562,10 +4574,10 @@
         <v>4224</v>
       </c>
       <c r="B119" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119" t="s">
         <v>227</v>
-      </c>
-      <c r="C119" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -4573,10 +4585,10 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
+        <v>228</v>
+      </c>
+      <c r="C120" t="s">
         <v>229</v>
-      </c>
-      <c r="C120" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -4584,10 +4596,10 @@
         <v>2622</v>
       </c>
       <c r="B121" t="s">
+        <v>230</v>
+      </c>
+      <c r="C121" t="s">
         <v>231</v>
-      </c>
-      <c r="C121" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -4595,10 +4607,10 @@
         <v>2053</v>
       </c>
       <c r="B122" t="s">
+        <v>232</v>
+      </c>
+      <c r="C122" t="s">
         <v>233</v>
-      </c>
-      <c r="C122" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -4606,10 +4618,10 @@
         <v>2054</v>
       </c>
       <c r="B123" t="s">
+        <v>234</v>
+      </c>
+      <c r="C123" t="s">
         <v>235</v>
-      </c>
-      <c r="C123" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -4617,10 +4629,10 @@
         <v>2110</v>
       </c>
       <c r="B124" t="s">
+        <v>236</v>
+      </c>
+      <c r="C124" t="s">
         <v>237</v>
-      </c>
-      <c r="C124" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -4628,7 +4640,7 @@
         <v>3960</v>
       </c>
       <c r="B125" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C125" t="s">
         <v>145</v>
@@ -4639,10 +4651,10 @@
         <v>566</v>
       </c>
       <c r="B126" t="s">
+        <v>239</v>
+      </c>
+      <c r="C126" t="s">
         <v>240</v>
-      </c>
-      <c r="C126" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -4650,10 +4662,10 @@
         <v>1033</v>
       </c>
       <c r="B127" t="s">
+        <v>241</v>
+      </c>
+      <c r="C127" t="s">
         <v>242</v>
-      </c>
-      <c r="C127" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -4661,10 +4673,10 @@
         <v>4421</v>
       </c>
       <c r="B128" t="s">
+        <v>243</v>
+      </c>
+      <c r="C128" t="s">
         <v>244</v>
-      </c>
-      <c r="C128" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -4672,7 +4684,7 @@
         <v>1710</v>
       </c>
       <c r="B129" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C129" t="s">
         <v>20</v>
@@ -4683,10 +4695,10 @@
         <v>125</v>
       </c>
       <c r="B130" t="s">
+        <v>246</v>
+      </c>
+      <c r="C130" t="s">
         <v>247</v>
-      </c>
-      <c r="C130" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -4694,10 +4706,10 @@
         <v>4717</v>
       </c>
       <c r="B131" t="s">
+        <v>248</v>
+      </c>
+      <c r="C131" t="s">
         <v>249</v>
-      </c>
-      <c r="C131" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -4705,10 +4717,10 @@
         <v>4408</v>
       </c>
       <c r="B132" t="s">
+        <v>250</v>
+      </c>
+      <c r="C132" t="s">
         <v>251</v>
-      </c>
-      <c r="C132" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -4716,10 +4728,10 @@
         <v>3158</v>
       </c>
       <c r="B133" t="s">
+        <v>252</v>
+      </c>
+      <c r="C133" t="s">
         <v>253</v>
-      </c>
-      <c r="C133" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -4727,10 +4739,10 @@
         <v>991</v>
       </c>
       <c r="B134" t="s">
+        <v>254</v>
+      </c>
+      <c r="C134" t="s">
         <v>255</v>
-      </c>
-      <c r="C134" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -4738,10 +4750,10 @@
         <v>1458</v>
       </c>
       <c r="B135" t="s">
+        <v>256</v>
+      </c>
+      <c r="C135" t="s">
         <v>257</v>
-      </c>
-      <c r="C135" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -4749,10 +4761,10 @@
         <v>1934</v>
       </c>
       <c r="B136" t="s">
+        <v>258</v>
+      </c>
+      <c r="C136" t="s">
         <v>259</v>
-      </c>
-      <c r="C136" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -4760,10 +4772,10 @@
         <v>2070</v>
       </c>
       <c r="B137" t="s">
+        <v>260</v>
+      </c>
+      <c r="C137" t="s">
         <v>261</v>
-      </c>
-      <c r="C137" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -4771,10 +4783,10 @@
         <v>544</v>
       </c>
       <c r="B138" t="s">
+        <v>262</v>
+      </c>
+      <c r="C138" t="s">
         <v>263</v>
-      </c>
-      <c r="C138" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -4782,10 +4794,10 @@
         <v>338</v>
       </c>
       <c r="B139" t="s">
+        <v>264</v>
+      </c>
+      <c r="C139" t="s">
         <v>265</v>
-      </c>
-      <c r="C139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -4793,7 +4805,7 @@
         <v>8897</v>
       </c>
       <c r="B140" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C140" t="s">
         <v>79</v>
@@ -4804,10 +4816,10 @@
         <v>2529</v>
       </c>
       <c r="B141" t="s">
+        <v>267</v>
+      </c>
+      <c r="C141" t="s">
         <v>268</v>
-      </c>
-      <c r="C141" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -4815,10 +4827,10 @@
         <v>3564</v>
       </c>
       <c r="B142" t="s">
+        <v>269</v>
+      </c>
+      <c r="C142" t="s">
         <v>270</v>
-      </c>
-      <c r="C142" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -4826,10 +4838,10 @@
         <v>4845</v>
       </c>
       <c r="B143" t="s">
+        <v>271</v>
+      </c>
+      <c r="C143" t="s">
         <v>272</v>
-      </c>
-      <c r="C143" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -4837,10 +4849,10 @@
         <v>307</v>
       </c>
       <c r="B144" t="s">
+        <v>273</v>
+      </c>
+      <c r="C144" t="s">
         <v>274</v>
-      </c>
-      <c r="C144" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -4848,10 +4860,10 @@
         <v>4145</v>
       </c>
       <c r="B145" t="s">
+        <v>275</v>
+      </c>
+      <c r="C145" t="s">
         <v>276</v>
-      </c>
-      <c r="C145" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -4859,10 +4871,10 @@
         <v>3929</v>
       </c>
       <c r="B146" t="s">
+        <v>277</v>
+      </c>
+      <c r="C146" t="s">
         <v>278</v>
-      </c>
-      <c r="C146" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -4870,7 +4882,7 @@
         <v>1211</v>
       </c>
       <c r="B147" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C147" t="s">
         <v>52</v>
@@ -4881,10 +4893,10 @@
         <v>15202</v>
       </c>
       <c r="B148" t="s">
+        <v>280</v>
+      </c>
+      <c r="C148" t="s">
         <v>281</v>
-      </c>
-      <c r="C148" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -4892,10 +4904,10 @@
         <v>1132</v>
       </c>
       <c r="B149" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C149" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -4903,10 +4915,10 @@
         <v>2423</v>
       </c>
       <c r="B150" t="s">
+        <v>283</v>
+      </c>
+      <c r="C150" t="s">
         <v>284</v>
-      </c>
-      <c r="C150" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -4914,10 +4926,10 @@
         <v>326</v>
       </c>
       <c r="B151" t="s">
+        <v>285</v>
+      </c>
+      <c r="C151" t="s">
         <v>286</v>
-      </c>
-      <c r="C151" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -4925,10 +4937,10 @@
         <v>5595</v>
       </c>
       <c r="B152" t="s">
+        <v>287</v>
+      </c>
+      <c r="C152" t="s">
         <v>288</v>
-      </c>
-      <c r="C152" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -4936,10 +4948,10 @@
         <v>13</v>
       </c>
       <c r="B153" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C153" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -4947,10 +4959,10 @@
         <v>4618</v>
       </c>
       <c r="B154" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -4958,10 +4970,10 @@
         <v>72</v>
       </c>
       <c r="B155" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C155" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -4969,10 +4981,10 @@
         <v>4539</v>
       </c>
       <c r="B156" t="s">
+        <v>292</v>
+      </c>
+      <c r="C156" t="s">
         <v>293</v>
-      </c>
-      <c r="C156" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -4980,10 +4992,10 @@
         <v>2889</v>
       </c>
       <c r="B157" t="s">
+        <v>294</v>
+      </c>
+      <c r="C157" t="s">
         <v>295</v>
-      </c>
-      <c r="C157" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -4991,10 +5003,10 @@
         <v>4198</v>
       </c>
       <c r="B158" t="s">
+        <v>296</v>
+      </c>
+      <c r="C158" t="s">
         <v>297</v>
-      </c>
-      <c r="C158" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -5002,10 +5014,10 @@
         <v>2517</v>
       </c>
       <c r="B159" t="s">
+        <v>298</v>
+      </c>
+      <c r="C159" t="s">
         <v>299</v>
-      </c>
-      <c r="C159" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -5013,10 +5025,10 @@
         <v>1775</v>
       </c>
       <c r="B160" t="s">
+        <v>300</v>
+      </c>
+      <c r="C160" t="s">
         <v>301</v>
-      </c>
-      <c r="C160" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5024,10 +5036,10 @@
         <v>1597</v>
       </c>
       <c r="B161" t="s">
+        <v>302</v>
+      </c>
+      <c r="C161" t="s">
         <v>303</v>
-      </c>
-      <c r="C161" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5035,10 +5047,10 @@
         <v>3654</v>
       </c>
       <c r="B162" t="s">
+        <v>304</v>
+      </c>
+      <c r="C162" t="s">
         <v>305</v>
-      </c>
-      <c r="C162" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5046,10 +5058,10 @@
         <v>300</v>
       </c>
       <c r="B163" t="s">
+        <v>306</v>
+      </c>
+      <c r="C163" t="s">
         <v>307</v>
-      </c>
-      <c r="C163" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5057,10 +5069,10 @@
         <v>1042</v>
       </c>
       <c r="B164" t="s">
+        <v>308</v>
+      </c>
+      <c r="C164" t="s">
         <v>309</v>
-      </c>
-      <c r="C164" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5068,10 +5080,10 @@
         <v>4115</v>
       </c>
       <c r="B165" t="s">
+        <v>310</v>
+      </c>
+      <c r="C165" t="s">
         <v>311</v>
-      </c>
-      <c r="C165" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5079,10 +5091,10 @@
         <v>1962</v>
       </c>
       <c r="B166" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C166" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5090,10 +5102,10 @@
         <v>2681</v>
       </c>
       <c r="B167" t="s">
+        <v>313</v>
+      </c>
+      <c r="C167" t="s">
         <v>314</v>
-      </c>
-      <c r="C167" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5101,10 +5113,10 @@
         <v>2911</v>
       </c>
       <c r="B168" t="s">
+        <v>315</v>
+      </c>
+      <c r="C168" t="s">
         <v>316</v>
-      </c>
-      <c r="C168" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5112,7 +5124,7 @@
         <v>13565</v>
       </c>
       <c r="B169" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C169" t="s">
         <v>8</v>
@@ -5123,10 +5135,10 @@
         <v>5067</v>
       </c>
       <c r="B170" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C170" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5134,10 +5146,10 @@
         <v>339</v>
       </c>
       <c r="B171" t="s">
+        <v>319</v>
+      </c>
+      <c r="C171" t="s">
         <v>320</v>
-      </c>
-      <c r="C171" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5145,10 +5157,10 @@
         <v>1306</v>
       </c>
       <c r="B172" t="s">
+        <v>321</v>
+      </c>
+      <c r="C172" t="s">
         <v>322</v>
-      </c>
-      <c r="C172" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5156,10 +5168,10 @@
         <v>8163</v>
       </c>
       <c r="B173" t="s">
+        <v>323</v>
+      </c>
+      <c r="C173" t="s">
         <v>324</v>
-      </c>
-      <c r="C173" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5167,7 +5179,7 @@
         <v>262</v>
       </c>
       <c r="B174" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C174" t="s">
         <v>20</v>
@@ -5178,10 +5190,10 @@
         <v>4549</v>
       </c>
       <c r="B175" t="s">
+        <v>326</v>
+      </c>
+      <c r="C175" t="s">
         <v>327</v>
-      </c>
-      <c r="C175" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5189,10 +5201,10 @@
         <v>111</v>
       </c>
       <c r="B176" t="s">
+        <v>328</v>
+      </c>
+      <c r="C176" t="s">
         <v>329</v>
-      </c>
-      <c r="C176" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5200,10 +5212,10 @@
         <v>1869</v>
       </c>
       <c r="B177" t="s">
+        <v>330</v>
+      </c>
+      <c r="C177" t="s">
         <v>331</v>
-      </c>
-      <c r="C177" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5211,10 +5223,10 @@
         <v>1890</v>
       </c>
       <c r="B178" t="s">
+        <v>332</v>
+      </c>
+      <c r="C178" t="s">
         <v>333</v>
-      </c>
-      <c r="C178" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5222,10 +5234,10 @@
         <v>5861</v>
       </c>
       <c r="B179" t="s">
+        <v>334</v>
+      </c>
+      <c r="C179" t="s">
         <v>335</v>
-      </c>
-      <c r="C179" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5233,10 +5245,10 @@
         <v>3724</v>
       </c>
       <c r="B180" t="s">
+        <v>336</v>
+      </c>
+      <c r="C180" t="s">
         <v>337</v>
-      </c>
-      <c r="C180" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5244,10 +5256,10 @@
         <v>524</v>
       </c>
       <c r="B181" t="s">
+        <v>338</v>
+      </c>
+      <c r="C181" t="s">
         <v>339</v>
-      </c>
-      <c r="C181" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5255,10 +5267,10 @@
         <v>1246</v>
       </c>
       <c r="B182" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C182" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5266,10 +5278,10 @@
         <v>4608</v>
       </c>
       <c r="B183" t="s">
+        <v>341</v>
+      </c>
+      <c r="C183" t="s">
         <v>342</v>
-      </c>
-      <c r="C183" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5277,10 +5289,10 @@
         <v>453</v>
       </c>
       <c r="B184" t="s">
+        <v>343</v>
+      </c>
+      <c r="C184" t="s">
         <v>344</v>
-      </c>
-      <c r="C184" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5288,10 +5300,10 @@
         <v>1598</v>
       </c>
       <c r="B185" t="s">
+        <v>345</v>
+      </c>
+      <c r="C185" t="s">
         <v>346</v>
-      </c>
-      <c r="C185" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5299,10 +5311,10 @@
         <v>3517</v>
       </c>
       <c r="B186" t="s">
+        <v>347</v>
+      </c>
+      <c r="C186" t="s">
         <v>348</v>
-      </c>
-      <c r="C186" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5310,10 +5322,10 @@
         <v>103</v>
       </c>
       <c r="B187" t="s">
+        <v>349</v>
+      </c>
+      <c r="C187" t="s">
         <v>350</v>
-      </c>
-      <c r="C187" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5321,10 +5333,10 @@
         <v>1131</v>
       </c>
       <c r="B188" t="s">
+        <v>351</v>
+      </c>
+      <c r="C188" t="s">
         <v>352</v>
-      </c>
-      <c r="C188" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5332,10 +5344,10 @@
         <v>41</v>
       </c>
       <c r="B189" t="s">
+        <v>353</v>
+      </c>
+      <c r="C189" t="s">
         <v>354</v>
-      </c>
-      <c r="C189" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5343,10 +5355,10 @@
         <v>4288</v>
       </c>
       <c r="B190" t="s">
+        <v>355</v>
+      </c>
+      <c r="C190" t="s">
         <v>356</v>
-      </c>
-      <c r="C190" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5354,10 +5366,10 @@
         <v>1413</v>
       </c>
       <c r="B191" t="s">
+        <v>357</v>
+      </c>
+      <c r="C191" t="s">
         <v>358</v>
-      </c>
-      <c r="C191" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5365,10 +5377,10 @@
         <v>1772</v>
       </c>
       <c r="B192" t="s">
+        <v>359</v>
+      </c>
+      <c r="C192" t="s">
         <v>360</v>
-      </c>
-      <c r="C192" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5376,7 +5388,7 @@
         <v>2058</v>
       </c>
       <c r="B193" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C193" t="s">
         <v>79</v>
@@ -5387,10 +5399,10 @@
         <v>2574</v>
       </c>
       <c r="B194" t="s">
+        <v>362</v>
+      </c>
+      <c r="C194" t="s">
         <v>363</v>
-      </c>
-      <c r="C194" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -5398,10 +5410,10 @@
         <v>519</v>
       </c>
       <c r="B195" t="s">
+        <v>364</v>
+      </c>
+      <c r="C195" t="s">
         <v>365</v>
-      </c>
-      <c r="C195" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -5409,7 +5421,7 @@
         <v>9566</v>
       </c>
       <c r="B196" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C196" t="s">
         <v>8</v>
@@ -5420,10 +5432,10 @@
         <v>4489</v>
       </c>
       <c r="B197" t="s">
+        <v>367</v>
+      </c>
+      <c r="C197" t="s">
         <v>368</v>
-      </c>
-      <c r="C197" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -5431,10 +5443,10 @@
         <v>488</v>
       </c>
       <c r="B198" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C198" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -5442,10 +5454,10 @@
         <v>2805</v>
       </c>
       <c r="B199" t="s">
+        <v>370</v>
+      </c>
+      <c r="C199" t="s">
         <v>371</v>
-      </c>
-      <c r="C199" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -5453,10 +5465,10 @@
         <v>1412</v>
       </c>
       <c r="B200" t="s">
+        <v>372</v>
+      </c>
+      <c r="C200" t="s">
         <v>373</v>
-      </c>
-      <c r="C200" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -5464,10 +5476,10 @@
         <v>2704</v>
       </c>
       <c r="B201" t="s">
+        <v>374</v>
+      </c>
+      <c r="C201" t="s">
         <v>375</v>
-      </c>
-      <c r="C201" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -5475,10 +5487,10 @@
         <v>2075</v>
       </c>
       <c r="B202" t="s">
+        <v>376</v>
+      </c>
+      <c r="C202" t="s">
         <v>377</v>
-      </c>
-      <c r="C202" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -5486,10 +5498,10 @@
         <v>8983</v>
       </c>
       <c r="B203" t="s">
+        <v>378</v>
+      </c>
+      <c r="C203" t="s">
         <v>379</v>
-      </c>
-      <c r="C203" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -5497,10 +5509,10 @@
         <v>1677</v>
       </c>
       <c r="B204" t="s">
+        <v>380</v>
+      </c>
+      <c r="C204" t="s">
         <v>381</v>
-      </c>
-      <c r="C204" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -5508,10 +5520,10 @@
         <v>2508</v>
       </c>
       <c r="B205" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C205" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -5519,10 +5531,10 @@
         <v>1175</v>
       </c>
       <c r="B206" t="s">
+        <v>383</v>
+      </c>
+      <c r="C206" t="s">
         <v>384</v>
-      </c>
-      <c r="C206" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -5530,10 +5542,10 @@
         <v>2613</v>
       </c>
       <c r="B207" t="s">
+        <v>385</v>
+      </c>
+      <c r="C207" t="s">
         <v>386</v>
-      </c>
-      <c r="C207" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -5541,10 +5553,10 @@
         <v>2755</v>
       </c>
       <c r="B208" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C208" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -5552,10 +5564,10 @@
         <v>23</v>
       </c>
       <c r="B209" t="s">
+        <v>388</v>
+      </c>
+      <c r="C209" t="s">
         <v>389</v>
-      </c>
-      <c r="C209" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -5563,10 +5575,10 @@
         <v>2616</v>
       </c>
       <c r="B210" t="s">
+        <v>390</v>
+      </c>
+      <c r="C210" t="s">
         <v>391</v>
-      </c>
-      <c r="C210" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -5574,10 +5586,10 @@
         <v>8980</v>
       </c>
       <c r="B211" t="s">
+        <v>392</v>
+      </c>
+      <c r="C211" t="s">
         <v>393</v>
-      </c>
-      <c r="C211" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -5585,10 +5597,10 @@
         <v>1664</v>
       </c>
       <c r="B212" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C212" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -5596,10 +5608,10 @@
         <v>4492</v>
       </c>
       <c r="B213" t="s">
+        <v>395</v>
+      </c>
+      <c r="C213" t="s">
         <v>396</v>
-      </c>
-      <c r="C213" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -5607,10 +5619,10 @@
         <v>721</v>
       </c>
       <c r="B214" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C214" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -5618,10 +5630,10 @@
         <v>4333</v>
       </c>
       <c r="B215" t="s">
+        <v>398</v>
+      </c>
+      <c r="C215" t="s">
         <v>399</v>
-      </c>
-      <c r="C215" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -5629,10 +5641,10 @@
         <v>2127</v>
       </c>
       <c r="B216" t="s">
+        <v>400</v>
+      </c>
+      <c r="C216" t="s">
         <v>401</v>
-      </c>
-      <c r="C216" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -5640,10 +5652,10 @@
         <v>2018</v>
       </c>
       <c r="B217" t="s">
+        <v>402</v>
+      </c>
+      <c r="C217" t="s">
         <v>403</v>
-      </c>
-      <c r="C217" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -5665,7 +5677,7 @@
         <v>406</v>
       </c>
       <c r="C219" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -5753,7 +5765,7 @@
         <v>420</v>
       </c>
       <c r="C227" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -5764,7 +5776,7 @@
         <v>421</v>
       </c>
       <c r="C228" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -5819,7 +5831,7 @@
         <v>430</v>
       </c>
       <c r="C233" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -5863,7 +5875,7 @@
         <v>435</v>
       </c>
       <c r="C237" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -5940,7 +5952,7 @@
         <v>447</v>
       </c>
       <c r="C244" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -5951,7 +5963,7 @@
         <v>448</v>
       </c>
       <c r="C245" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -5973,7 +5985,7 @@
         <v>451</v>
       </c>
       <c r="C247" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -5995,7 +6007,7 @@
         <v>454</v>
       </c>
       <c r="C249" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6072,7 +6084,7 @@
         <v>463</v>
       </c>
       <c r="C256" t="s">
-        <v>256</v>
+        <v>176</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6094,7 +6106,7 @@
         <v>466</v>
       </c>
       <c r="C258" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -6102,10 +6114,10 @@
         <v>243</v>
       </c>
       <c r="B259" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C259" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -6113,7 +6125,7 @@
         <v>331</v>
       </c>
       <c r="B260" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>
@@ -6124,7 +6136,7 @@
         <v>1881</v>
       </c>
       <c r="B261" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C261" t="s">
         <v>129</v>
@@ -6135,10 +6147,10 @@
         <v>2274</v>
       </c>
       <c r="B262" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C262" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -6146,10 +6158,10 @@
         <v>3653</v>
       </c>
       <c r="B263" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C263" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -6157,10 +6169,10 @@
         <v>1982</v>
       </c>
       <c r="B264" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C264" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -6168,10 +6180,10 @@
         <v>1309</v>
       </c>
       <c r="B265" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C265" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -6179,7 +6191,7 @@
         <v>8454</v>
       </c>
       <c r="B266" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C266" t="s">
         <v>79</v>
@@ -6190,10 +6202,10 @@
         <v>750</v>
       </c>
       <c r="B267" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C267" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -6201,10 +6213,10 @@
         <v>4804</v>
       </c>
       <c r="B268" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C268" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -6212,10 +6224,10 @@
         <v>1118</v>
       </c>
       <c r="B269" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C269" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -6223,10 +6235,10 @@
         <v>6519</v>
       </c>
       <c r="B270" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C270" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -6234,10 +6246,10 @@
         <v>1768</v>
       </c>
       <c r="B271" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C271" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -6245,10 +6257,10 @@
         <v>406</v>
       </c>
       <c r="B272" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C272" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -6256,10 +6268,10 @@
         <v>2886</v>
       </c>
       <c r="B273" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C273" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -6267,10 +6279,10 @@
         <v>3548</v>
       </c>
       <c r="B274" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C274" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -6278,7 +6290,7 @@
         <v>320</v>
       </c>
       <c r="B275" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C275" t="s">
         <v>8</v>
@@ -6289,10 +6301,10 @@
         <v>497</v>
       </c>
       <c r="B276" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C276" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -6300,10 +6312,10 @@
         <v>2847</v>
       </c>
       <c r="B277" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C277" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -6311,7 +6323,7 @@
         <v>3604</v>
       </c>
       <c r="B278" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C278" t="s">
         <v>8</v>
@@ -6322,7 +6334,7 @@
         <v>14732</v>
       </c>
       <c r="B279" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C279" t="s">
         <v>20</v>
@@ -6333,10 +6345,10 @@
         <v>2636</v>
       </c>
       <c r="B280" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C280" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -6344,10 +6356,10 @@
         <v>1659</v>
       </c>
       <c r="B281" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C281" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -6355,10 +6367,10 @@
         <v>3851</v>
       </c>
       <c r="B282" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C282" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -6366,10 +6378,10 @@
         <v>2013</v>
       </c>
       <c r="B283" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C283" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -6377,10 +6389,10 @@
         <v>228</v>
       </c>
       <c r="B284" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C284" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -6388,7 +6400,7 @@
         <v>13511</v>
       </c>
       <c r="B285" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C285" t="s">
         <v>20</v>
@@ -6399,10 +6411,10 @@
         <v>2537</v>
       </c>
       <c r="B286" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C286" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -6410,7 +6422,7 @@
         <v>4481</v>
       </c>
       <c r="B287" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C287" t="s">
         <v>107</v>
@@ -6421,10 +6433,10 @@
         <v>4030</v>
       </c>
       <c r="B288" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C288" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -6432,10 +6444,10 @@
         <v>4505</v>
       </c>
       <c r="B289" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C289" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -6443,10 +6455,10 @@
         <v>390</v>
       </c>
       <c r="B290" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C290" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -6454,10 +6466,10 @@
         <v>3</v>
       </c>
       <c r="B291" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C291" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -6465,7 +6477,7 @@
         <v>20559</v>
       </c>
       <c r="B292" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C292" t="s">
         <v>20</v>
@@ -6476,10 +6488,10 @@
         <v>2662</v>
       </c>
       <c r="B293" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C293" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -6487,10 +6499,10 @@
         <v>5272</v>
       </c>
       <c r="B294" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C294" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -6498,10 +6510,10 @@
         <v>3512</v>
       </c>
       <c r="B295" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C295" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -6509,10 +6521,10 @@
         <v>12136</v>
       </c>
       <c r="B296" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C296" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -6520,10 +6532,10 @@
         <v>154</v>
       </c>
       <c r="B297" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C297" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -6531,10 +6543,10 @@
         <v>1429</v>
       </c>
       <c r="B298" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C298" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -6542,7 +6554,7 @@
         <v>12582</v>
       </c>
       <c r="B299" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C299" t="s">
         <v>129</v>
@@ -6553,10 +6565,10 @@
         <v>2603</v>
       </c>
       <c r="B300" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C300" t="s">
-        <v>325</v>
+        <v>529</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -6564,10 +6576,10 @@
         <v>2553</v>
       </c>
       <c r="B301" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C301" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -6575,10 +6587,10 @@
         <v>848</v>
       </c>
       <c r="B302" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C302" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -6586,7 +6598,7 @@
         <v>3861</v>
       </c>
       <c r="B303" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C303" t="s">
         <v>405</v>
@@ -6597,10 +6609,10 @@
         <v>958</v>
       </c>
       <c r="B304" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C304" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -6608,10 +6620,10 @@
         <v>2041</v>
       </c>
       <c r="B305" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C305" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -6619,10 +6631,10 @@
         <v>1337</v>
       </c>
       <c r="B306" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C306" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -6630,10 +6642,10 @@
         <v>304</v>
       </c>
       <c r="B307" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C307" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -6641,10 +6653,10 @@
         <v>4499</v>
       </c>
       <c r="B308" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C308" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -6652,10 +6664,10 @@
         <v>5758</v>
       </c>
       <c r="B309" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C309" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -6663,10 +6675,10 @@
         <v>3102</v>
       </c>
       <c r="B310" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C310" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -6674,10 +6686,10 @@
         <v>3175</v>
       </c>
       <c r="B311" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C311" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -6685,10 +6697,10 @@
         <v>670</v>
       </c>
       <c r="B312" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C312" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -6696,10 +6708,10 @@
         <v>847</v>
       </c>
       <c r="B313" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C313" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -6707,10 +6719,10 @@
         <v>5175</v>
       </c>
       <c r="B314" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C314" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -6718,7 +6730,7 @@
         <v>3137</v>
       </c>
       <c r="B315" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C315" t="s">
         <v>20</v>
@@ -6729,10 +6741,10 @@
         <v>583</v>
       </c>
       <c r="B316" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C316" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -6740,10 +6752,10 @@
         <v>2434</v>
       </c>
       <c r="B317" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C317" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -6751,10 +6763,10 @@
         <v>4503</v>
       </c>
       <c r="B318" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C318" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -6762,10 +6774,10 @@
         <v>4985</v>
       </c>
       <c r="B319" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C319" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -6773,10 +6785,10 @@
         <v>24797</v>
       </c>
       <c r="B320" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C320" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -6784,10 +6796,10 @@
         <v>4179</v>
       </c>
       <c r="B321" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C321" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -6795,10 +6807,10 @@
         <v>2928</v>
       </c>
       <c r="B322" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C322" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -6806,10 +6818,10 @@
         <v>598</v>
       </c>
       <c r="B323" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C323" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -6817,10 +6829,10 @@
         <v>1565</v>
       </c>
       <c r="B324" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C324" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -6828,10 +6840,10 @@
         <v>10079</v>
       </c>
       <c r="B325" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C325" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -6839,10 +6851,10 @@
         <v>245</v>
       </c>
       <c r="B326" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C326" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -6850,10 +6862,10 @@
         <v>1335</v>
       </c>
       <c r="B327" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C327" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -6861,7 +6873,7 @@
         <v>4123</v>
       </c>
       <c r="B328" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C328" t="s">
         <v>145</v>
@@ -6872,10 +6884,10 @@
         <v>523</v>
       </c>
       <c r="B329" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C329" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -6883,10 +6895,10 @@
         <v>3448</v>
       </c>
       <c r="B330" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C330" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -6894,10 +6906,10 @@
         <v>2289</v>
       </c>
       <c r="B331" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C331" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -6905,10 +6917,10 @@
         <v>2991</v>
       </c>
       <c r="B332" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C332" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -6916,7 +6928,7 @@
         <v>3404</v>
       </c>
       <c r="B333" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C333" t="s">
         <v>20</v>
@@ -6927,10 +6939,10 @@
         <v>1497</v>
       </c>
       <c r="B334" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C334" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -6938,10 +6950,10 @@
         <v>4403</v>
       </c>
       <c r="B335" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C335" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -6949,10 +6961,10 @@
         <v>22542</v>
       </c>
       <c r="B336" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C336" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -6960,10 +6972,10 @@
         <v>2845</v>
       </c>
       <c r="B337" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C337" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -6971,10 +6983,10 @@
         <v>3807</v>
       </c>
       <c r="B338" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C338" t="s">
-        <v>378</v>
+        <v>589</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -6982,10 +6994,10 @@
         <v>19680</v>
       </c>
       <c r="B339" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C339" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -6993,10 +7005,10 @@
         <v>8245</v>
       </c>
       <c r="B340" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C340" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -7004,10 +7016,10 @@
         <v>79</v>
       </c>
       <c r="B341" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C341" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -7015,10 +7027,10 @@
         <v>1505</v>
       </c>
       <c r="B342" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C342" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -7026,10 +7038,10 @@
         <v>1909</v>
       </c>
       <c r="B343" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C343" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -7037,10 +7049,10 @@
         <v>3982</v>
       </c>
       <c r="B344" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C344" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -7048,10 +7060,10 @@
         <v>4286</v>
       </c>
       <c r="B345" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C345" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -7059,10 +7071,10 @@
         <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C346" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -7070,10 +7082,10 @@
         <v>5865</v>
       </c>
       <c r="B347" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C347" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -7081,10 +7093,10 @@
         <v>3394</v>
       </c>
       <c r="B348" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C348" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -7092,10 +7104,10 @@
         <v>329</v>
       </c>
       <c r="B349" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C349" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -7103,10 +7115,10 @@
         <v>1045</v>
       </c>
       <c r="B350" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C350" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -7114,10 +7126,10 @@
         <v>755</v>
       </c>
       <c r="B351" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C351" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -7125,7 +7137,7 @@
         <v>2522</v>
       </c>
       <c r="B352" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C352" t="s">
         <v>8</v>
@@ -7136,7 +7148,7 @@
         <v>2072</v>
       </c>
       <c r="B353" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C353" t="s">
         <v>444</v>
@@ -7147,7 +7159,7 @@
         <v>1558</v>
       </c>
       <c r="B354" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C354" t="s">
         <v>129</v>
@@ -7158,7 +7170,7 @@
         <v>1217</v>
       </c>
       <c r="B355" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C355" t="s">
         <v>8</v>
@@ -7169,10 +7181,10 @@
         <v>20486</v>
       </c>
       <c r="B356" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C356" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -7180,10 +7192,10 @@
         <v>1253</v>
       </c>
       <c r="B357" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C357" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -7191,10 +7203,10 @@
         <v>4252</v>
       </c>
       <c r="B358" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C358" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -7202,10 +7214,10 @@
         <v>293</v>
       </c>
       <c r="B359" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C359" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -7213,10 +7225,10 @@
         <v>2980</v>
       </c>
       <c r="B360" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C360" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -7224,10 +7236,10 @@
         <v>2024</v>
       </c>
       <c r="B361" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C361" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -7235,10 +7247,10 @@
         <v>2047</v>
       </c>
       <c r="B362" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C362" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -7246,7 +7258,7 @@
         <v>8868</v>
       </c>
       <c r="B363" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C363" t="s">
         <v>79</v>
@@ -7257,10 +7269,10 @@
         <v>2012</v>
       </c>
       <c r="B364" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C364" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -7268,7 +7280,7 @@
         <v>4666</v>
       </c>
       <c r="B365" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C365" t="s">
         <v>145</v>
@@ -7279,10 +7291,10 @@
         <v>448</v>
       </c>
       <c r="B366" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C366" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -7290,10 +7302,10 @@
         <v>1495</v>
       </c>
       <c r="B367" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C367" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -7301,10 +7313,10 @@
         <v>14716</v>
       </c>
       <c r="B368" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C368" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -7312,10 +7324,10 @@
         <v>4487</v>
       </c>
       <c r="B369" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -7323,10 +7335,10 @@
         <v>128</v>
       </c>
       <c r="B370" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C370" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -7334,10 +7346,10 @@
         <v>8707</v>
       </c>
       <c r="B371" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C371" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -7345,10 +7357,10 @@
         <v>4148</v>
       </c>
       <c r="B372" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C372" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -7356,10 +7368,10 @@
         <v>14164</v>
       </c>
       <c r="B373" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C373" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -7367,10 +7379,10 @@
         <v>1151</v>
       </c>
       <c r="B374" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C374" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -7378,10 +7390,10 @@
         <v>3247</v>
       </c>
       <c r="B375" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C375" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -7389,10 +7401,10 @@
         <v>11071</v>
       </c>
       <c r="B376" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C376" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -7400,10 +7412,10 @@
         <v>51423</v>
       </c>
       <c r="B377" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C377" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -7411,7 +7423,7 @@
         <v>2239</v>
       </c>
       <c r="B378" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C378" t="s">
         <v>129</v>
@@ -7422,10 +7434,10 @@
         <v>13492</v>
       </c>
       <c r="B379" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C379" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -7433,10 +7445,10 @@
         <v>13274</v>
       </c>
       <c r="B380" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C380" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -7444,7 +7456,7 @@
         <v>2705</v>
       </c>
       <c r="B381" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C381" t="s">
         <v>129</v>
@@ -7455,10 +7467,10 @@
         <v>1740</v>
       </c>
       <c r="B382" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C382" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -7466,7 +7478,7 @@
         <v>23396</v>
       </c>
       <c r="B383" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C383" t="s">
         <v>8</v>
@@ -7477,7 +7489,7 @@
         <v>25183</v>
       </c>
       <c r="B384" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C384" t="s">
         <v>79</v>
@@ -7488,7 +7500,7 @@
         <v>174</v>
       </c>
       <c r="B385" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C385" t="s">
         <v>129</v>
@@ -7499,10 +7511,10 @@
         <v>4245</v>
       </c>
       <c r="B386" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C386" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -7510,10 +7522,10 @@
         <v>49481</v>
       </c>
       <c r="B387" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C387" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -7521,10 +7533,10 @@
         <v>5101</v>
       </c>
       <c r="B388" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C388" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -7532,10 +7544,10 @@
         <v>20479</v>
       </c>
       <c r="B389" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C389" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -7543,10 +7555,10 @@
         <v>14805</v>
       </c>
       <c r="B390" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C390" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -7554,10 +7566,10 @@
         <v>3121</v>
       </c>
       <c r="B391" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C391" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -7565,10 +7577,10 @@
         <v>75</v>
       </c>
       <c r="B392" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C392" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -7576,10 +7588,10 @@
         <v>8658</v>
       </c>
       <c r="B393" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C393" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -7587,7 +7599,7 @@
         <v>3388</v>
       </c>
       <c r="B394" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C394" t="s">
         <v>153</v>
@@ -7598,10 +7610,10 @@
         <v>29</v>
       </c>
       <c r="B395" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C395" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -7609,10 +7621,10 @@
         <v>3420</v>
       </c>
       <c r="B396" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C396" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -7620,10 +7632,10 @@
         <v>9662</v>
       </c>
       <c r="B397" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C397" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -7631,10 +7643,10 @@
         <v>3680</v>
       </c>
       <c r="B398" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C398" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -7642,10 +7654,10 @@
         <v>1866</v>
       </c>
       <c r="B399" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C399" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -7653,10 +7665,10 @@
         <v>1455</v>
       </c>
       <c r="B400" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C400" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -7664,10 +7676,10 @@
         <v>5220</v>
       </c>
       <c r="B401" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C401" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -7675,7 +7687,7 @@
         <v>2935</v>
       </c>
       <c r="B402" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -7686,10 +7698,10 @@
         <v>20607</v>
       </c>
       <c r="B403" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C403" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -7697,10 +7709,10 @@
         <v>4260</v>
       </c>
       <c r="B404" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C404" t="s">
-        <v>510</v>
+        <v>679</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -7708,7 +7720,7 @@
         <v>172</v>
       </c>
       <c r="B405" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C405" t="s">
         <v>129</v>
@@ -7719,7 +7731,7 @@
         <v>3135</v>
       </c>
       <c r="B406" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C406" t="s">
         <v>20</v>
@@ -7730,10 +7742,10 @@
         <v>495</v>
       </c>
       <c r="B407" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C407" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -7741,10 +7753,10 @@
         <v>8246</v>
       </c>
       <c r="B408" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C408" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -7752,10 +7764,10 @@
         <v>32</v>
       </c>
       <c r="B409" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C409" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -7763,7 +7775,7 @@
         <v>785</v>
       </c>
       <c r="B410" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C410" t="s">
         <v>79</v>
@@ -7774,10 +7786,10 @@
         <v>363</v>
       </c>
       <c r="B411" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C411" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -7785,7 +7797,7 @@
         <v>4437</v>
       </c>
       <c r="B412" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C412" t="s">
         <v>456</v>
@@ -7796,10 +7808,10 @@
         <v>5514</v>
       </c>
       <c r="B413" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C413" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -7807,10 +7819,10 @@
         <v>3281</v>
       </c>
       <c r="B414" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C414" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -7818,10 +7830,10 @@
         <v>3734</v>
       </c>
       <c r="B415" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C415" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -7829,10 +7841,10 @@
         <v>24334</v>
       </c>
       <c r="B416" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C416" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -7840,10 +7852,10 @@
         <v>1196</v>
       </c>
       <c r="B417" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C417" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -7851,10 +7863,10 @@
         <v>522</v>
       </c>
       <c r="B418" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C418" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -7862,10 +7874,10 @@
         <v>1835</v>
       </c>
       <c r="B419" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -7873,10 +7885,10 @@
         <v>886</v>
       </c>
       <c r="B420" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C420" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -7884,10 +7896,10 @@
         <v>16286</v>
       </c>
       <c r="B421" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C421" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -7895,10 +7907,10 @@
         <v>2323</v>
       </c>
       <c r="B422" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C422" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -7906,7 +7918,7 @@
         <v>9167</v>
       </c>
       <c r="B423" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C423" t="s">
         <v>145</v>
@@ -7917,10 +7929,10 @@
         <v>24626</v>
       </c>
       <c r="B424" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C424" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -7928,10 +7940,10 @@
         <v>8171</v>
       </c>
       <c r="B425" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C425" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -7939,10 +7951,10 @@
         <v>122</v>
       </c>
       <c r="B426" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C426" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -7950,10 +7962,10 @@
         <v>10766</v>
       </c>
       <c r="B427" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C427" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -7961,10 +7973,10 @@
         <v>66104</v>
       </c>
       <c r="B428" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C428" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -7972,10 +7984,10 @@
         <v>4472</v>
       </c>
       <c r="B429" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C429" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -7983,10 +7995,10 @@
         <v>54312</v>
       </c>
       <c r="B430" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C430" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -7994,10 +8006,10 @@
         <v>50234</v>
       </c>
       <c r="B431" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C431" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -8005,10 +8017,10 @@
         <v>3063</v>
       </c>
       <c r="B432" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C432" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -8016,10 +8028,10 @@
         <v>19589</v>
       </c>
       <c r="B433" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C433" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -8027,10 +8039,10 @@
         <v>5859</v>
       </c>
       <c r="B434" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C434" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -8038,7 +8050,7 @@
         <v>328</v>
       </c>
       <c r="B435" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C435" t="s">
         <v>8</v>
@@ -8049,10 +8061,10 @@
         <v>16431</v>
       </c>
       <c r="B436" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C436" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -8060,7 +8072,7 @@
         <v>3513</v>
       </c>
       <c r="B437" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C437" t="s">
         <v>145</v>
@@ -8071,10 +8083,10 @@
         <v>7975</v>
       </c>
       <c r="B438" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C438" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -8082,7 +8094,7 @@
         <v>337</v>
       </c>
       <c r="B439" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C439" t="s">
         <v>8</v>
@@ -8093,10 +8105,10 @@
         <v>1533</v>
       </c>
       <c r="B440" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C440" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -8104,7 +8116,7 @@
         <v>342</v>
       </c>
       <c r="B441" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C441" t="s">
         <v>8</v>
@@ -8115,7 +8127,7 @@
         <v>2940</v>
       </c>
       <c r="B442" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C442" t="s">
         <v>8</v>
@@ -8126,7 +8138,7 @@
         <v>1210</v>
       </c>
       <c r="B443" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C443" t="s">
         <v>8</v>
@@ -8137,10 +8149,10 @@
         <v>19620</v>
       </c>
       <c r="B444" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C444" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -8148,7 +8160,7 @@
         <v>2117</v>
       </c>
       <c r="B445" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C445" t="s">
         <v>8</v>
@@ -8159,10 +8171,10 @@
         <v>319</v>
       </c>
       <c r="B446" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C446" t="s">
-        <v>724</v>
+        <v>8</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -8170,7 +8182,7 @@
         <v>3447</v>
       </c>
       <c r="B447" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C447" t="s">
         <v>8</v>
@@ -8181,7 +8193,7 @@
         <v>5110</v>
       </c>
       <c r="B448" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C448" t="s">
         <v>107</v>
@@ -8192,10 +8204,10 @@
         <v>2654</v>
       </c>
       <c r="B449" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C449" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -8203,10 +8215,10 @@
         <v>2653</v>
       </c>
       <c r="B450" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C450" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -8214,10 +8226,10 @@
         <v>3543</v>
       </c>
       <c r="B451" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C451" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -8225,10 +8237,10 @@
         <v>65970</v>
       </c>
       <c r="B452" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C452" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -8236,10 +8248,10 @@
         <v>4911</v>
       </c>
       <c r="B453" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C453" t="s">
-        <v>167</v>
+        <v>32</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -8247,10 +8259,10 @@
         <v>1072</v>
       </c>
       <c r="B454" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C454" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -8258,10 +8270,10 @@
         <v>11044</v>
       </c>
       <c r="B455" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C455" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -8269,7 +8281,7 @@
         <v>4138</v>
       </c>
       <c r="B456" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C456" t="s">
         <v>20</v>
@@ -8280,7 +8292,7 @@
         <v>3664</v>
       </c>
       <c r="B457" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C457" t="s">
         <v>8</v>
@@ -8291,7 +8303,7 @@
         <v>3446</v>
       </c>
       <c r="B458" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C458" t="s">
         <v>8</v>
@@ -8302,10 +8314,10 @@
         <v>5051</v>
       </c>
       <c r="B459" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C459" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -8313,10 +8325,10 @@
         <v>16723</v>
       </c>
       <c r="B460" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C460" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -8324,7 +8336,7 @@
         <v>1580</v>
       </c>
       <c r="B461" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C461" t="s">
         <v>8</v>
@@ -8335,10 +8347,10 @@
         <v>2818</v>
       </c>
       <c r="B462" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C462" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -8346,10 +8358,10 @@
         <v>5575</v>
       </c>
       <c r="B463" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C463" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -8357,10 +8369,10 @@
         <v>13344</v>
       </c>
       <c r="B464" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C464" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
